--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101138</v>
+        <v>120101230</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800993</v>
+        <v>800950</v>
       </c>
       <c r="R2" t="n">
-        <v>7497292</v>
+        <v>7497212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +756,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107773</v>
+        <v>120107787</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800947</v>
+        <v>800951</v>
       </c>
       <c r="R3" t="n">
-        <v>7497009</v>
+        <v>7496943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,13 +867,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107790</v>
+        <v>120101248</v>
       </c>
       <c r="B4" t="n">
-        <v>57937</v>
+        <v>57421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,20 +908,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,14 +931,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800951</v>
+        <v>800950</v>
       </c>
       <c r="R4" t="n">
-        <v>7496943</v>
+        <v>7497212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101084</v>
+        <v>120101138</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,26 +1026,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801019</v>
+        <v>800993</v>
       </c>
       <c r="R5" t="n">
-        <v>7497303</v>
+        <v>7497292</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,13 +1096,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101230</v>
+        <v>120101125</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800950</v>
+        <v>801014</v>
       </c>
       <c r="R6" t="n">
-        <v>7497212</v>
+        <v>7497308</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101219</v>
+        <v>120107790</v>
       </c>
       <c r="B7" t="n">
-        <v>90916</v>
+        <v>57937</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,26 +1247,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1506</v>
+        <v>102125</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800950</v>
+        <v>800951</v>
       </c>
       <c r="R7" t="n">
-        <v>7497212</v>
+        <v>7496943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1327,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120101090</v>
+        <v>120107796</v>
       </c>
       <c r="B8" t="n">
-        <v>90957</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,25 +1357,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801014</v>
+        <v>800927</v>
       </c>
       <c r="R8" t="n">
-        <v>7497308</v>
+        <v>7496884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101248</v>
+        <v>120101064</v>
       </c>
       <c r="B9" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,39 +1463,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1486,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800950</v>
+        <v>801077</v>
       </c>
       <c r="R9" t="n">
-        <v>7497212</v>
+        <v>7497320</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,6 +1538,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,7 +1557,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101125</v>
+        <v>120107773</v>
       </c>
       <c r="B10" t="n">
         <v>78526</v>
@@ -1591,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801014</v>
+        <v>800947</v>
       </c>
       <c r="R10" t="n">
-        <v>7497308</v>
+        <v>7497009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1663,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101064</v>
+        <v>120101084</v>
       </c>
       <c r="B11" t="n">
         <v>78526</v>
@@ -1697,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801077</v>
+        <v>801019</v>
       </c>
       <c r="R11" t="n">
-        <v>7497320</v>
+        <v>7497303</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107796</v>
+        <v>120101219</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>90916</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,25 +1781,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800927</v>
+        <v>800950</v>
       </c>
       <c r="R12" t="n">
-        <v>7496884</v>
+        <v>7497212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101206</v>
+        <v>120101090</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>90957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,25 +2001,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2023,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801001</v>
+        <v>801014</v>
       </c>
       <c r="R14" t="n">
-        <v>7497266</v>
+        <v>7497308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101100</v>
+        <v>120101206</v>
       </c>
       <c r="B15" t="n">
-        <v>91290</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1105</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2129,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801014</v>
+        <v>801001</v>
       </c>
       <c r="R15" t="n">
-        <v>7497308</v>
+        <v>7497266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2189,121 +2198,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>120107787</v>
-      </c>
-      <c r="B16" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Isopalo, T lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>800951</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7496943</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101230</v>
+        <v>120107787</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800950</v>
+        <v>800951</v>
       </c>
       <c r="R2" t="n">
-        <v>7497212</v>
+        <v>7496943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,13 +761,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107787</v>
+        <v>120101230</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +802,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800951</v>
+        <v>800950</v>
       </c>
       <c r="R3" t="n">
-        <v>7496943</v>
+        <v>7497212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,17 +871,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107787</v>
+        <v>120107790</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101230</v>
+        <v>120101248</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>57421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +805,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101248</v>
+        <v>120101219</v>
       </c>
       <c r="B4" t="n">
-        <v>57421</v>
+        <v>90916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,39 +915,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -992,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101138</v>
+        <v>120107787</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1058,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800993</v>
+        <v>800951</v>
       </c>
       <c r="R5" t="n">
-        <v>7497292</v>
+        <v>7496943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1231,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120107790</v>
+        <v>120107796</v>
       </c>
       <c r="B7" t="n">
-        <v>57937</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,39 +1242,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102125</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800951</v>
+        <v>800927</v>
       </c>
       <c r="R7" t="n">
-        <v>7496943</v>
+        <v>7496884</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,6 +1317,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107796</v>
+        <v>120101064</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,21 +1352,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800927</v>
+        <v>801077</v>
       </c>
       <c r="R8" t="n">
-        <v>7496884</v>
+        <v>7497320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1442,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101064</v>
+        <v>120107773</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1494,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801077</v>
+        <v>800947</v>
       </c>
       <c r="R9" t="n">
-        <v>7497320</v>
+        <v>7497009</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120107773</v>
+        <v>120101090</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90957</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800947</v>
+        <v>801014</v>
       </c>
       <c r="R10" t="n">
-        <v>7497009</v>
+        <v>7497308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101084</v>
+        <v>120101143</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,26 +1670,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801019</v>
+        <v>800993</v>
       </c>
       <c r="R11" t="n">
-        <v>7497303</v>
+        <v>7497292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101219</v>
+        <v>120101138</v>
       </c>
       <c r="B12" t="n">
-        <v>90916</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,30 +1780,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1812,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800950</v>
+        <v>800993</v>
       </c>
       <c r="R12" t="n">
-        <v>7497212</v>
+        <v>7497292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,13 +1854,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1875,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101143</v>
+        <v>120101084</v>
       </c>
       <c r="B13" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,35 +1899,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800993</v>
+        <v>801019</v>
       </c>
       <c r="R13" t="n">
-        <v>7497292</v>
+        <v>7497303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,6 +1970,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101090</v>
+        <v>120101206</v>
       </c>
       <c r="B14" t="n">
-        <v>90957</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,25 +2001,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801014</v>
+        <v>801001</v>
       </c>
       <c r="R14" t="n">
-        <v>7497308</v>
+        <v>7497266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101206</v>
+        <v>120101230</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801001</v>
+        <v>800950</v>
       </c>
       <c r="R15" t="n">
-        <v>7497266</v>
+        <v>7497212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107790</v>
+        <v>120107773</v>
       </c>
       <c r="B2" t="n">
-        <v>57937</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800951</v>
+        <v>800947</v>
       </c>
       <c r="R2" t="n">
-        <v>7496943</v>
+        <v>7497009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101248</v>
+        <v>120107796</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800950</v>
+        <v>800927</v>
       </c>
       <c r="R3" t="n">
-        <v>7497212</v>
+        <v>7496884</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101219</v>
+        <v>120101138</v>
       </c>
       <c r="B4" t="n">
-        <v>90916</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +899,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800950</v>
+        <v>800993</v>
       </c>
       <c r="R4" t="n">
-        <v>7497212</v>
+        <v>7497292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,13 +973,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107787</v>
+        <v>120101064</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,31 +1018,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800951</v>
+        <v>801077</v>
       </c>
       <c r="R5" t="n">
-        <v>7496943</v>
+        <v>7497320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,17 +1083,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101125</v>
+        <v>120107787</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,26 +1124,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1167,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801014</v>
+        <v>800951</v>
       </c>
       <c r="R6" t="n">
-        <v>7497308</v>
+        <v>7496943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,13 +1194,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1230,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120107796</v>
+        <v>120101090</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>90957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1235,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800927</v>
+        <v>801014</v>
       </c>
       <c r="R7" t="n">
-        <v>7496884</v>
+        <v>7497308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120101064</v>
+        <v>120101143</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,26 +1345,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801077</v>
+        <v>800993</v>
       </c>
       <c r="R8" t="n">
-        <v>7497320</v>
+        <v>7497292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1425,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107773</v>
+        <v>120107790</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57937</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,30 +1455,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800947</v>
+        <v>800951</v>
       </c>
       <c r="R9" t="n">
-        <v>7497009</v>
+        <v>7496943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1539,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101090</v>
+        <v>120101219</v>
       </c>
       <c r="B10" t="n">
-        <v>90957</v>
+        <v>90916</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,25 +1569,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801014</v>
+        <v>800950</v>
       </c>
       <c r="R10" t="n">
-        <v>7497308</v>
+        <v>7497212</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101143</v>
+        <v>120101206</v>
       </c>
       <c r="B11" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,35 +1679,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800993</v>
+        <v>801001</v>
       </c>
       <c r="R11" t="n">
-        <v>7497292</v>
+        <v>7497266</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,6 +1750,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1768,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101138</v>
+        <v>120101125</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,31 +1785,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1816,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800993</v>
+        <v>801014</v>
       </c>
       <c r="R12" t="n">
-        <v>7497292</v>
+        <v>7497308</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,17 +1850,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101084</v>
+        <v>120101248</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,30 +1887,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1926,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801019</v>
+        <v>800950</v>
       </c>
       <c r="R13" t="n">
-        <v>7497303</v>
+        <v>7497212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1971,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101206</v>
+        <v>120101084</v>
       </c>
       <c r="B14" t="n">
         <v>78526</v>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801001</v>
+        <v>801019</v>
       </c>
       <c r="R14" t="n">
-        <v>7497266</v>
+        <v>7497303</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101125</v>
+        <v>120101248</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57421</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,30 +1781,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1812,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801014</v>
+        <v>800950</v>
       </c>
       <c r="R12" t="n">
-        <v>7497308</v>
+        <v>7497212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1856,7 +1865,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1875,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101248</v>
+        <v>120101125</v>
       </c>
       <c r="B13" t="n">
-        <v>57421</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,39 +1895,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800950</v>
+        <v>801014</v>
       </c>
       <c r="R13" t="n">
-        <v>7497212</v>
+        <v>7497308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,6 +1970,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,6 +2199,4854 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120259855</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>800995</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7496971</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120259777</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>801236</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7497261</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120259875</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>801071</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7497222</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120259821</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>800977</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7496685</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120259859</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>658</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>800998</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7497020</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120259863</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>800990</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7497009</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120259822</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>658</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>800977</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7496685</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120259793</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>801114</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7497155</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120259818</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>801003</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7496768</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120259874</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>801042</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7497202</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120259803</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>801068</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7497037</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120259801</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>801083</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7497051</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120259872</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90509</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>112</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>801033</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7497193</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120259805</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>864</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>801066</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7497007</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120259792</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>801191</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7497171</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120259802</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>801083</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7497051</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120259800</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>801083</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7497051</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120259795</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>801088</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7497114</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120259851</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>800967</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7496843</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120259867</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90916</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>800977</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7497131</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120259796</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57421</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>801096</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7497061</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120259878</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>801127</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7497259</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120259866</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>800977</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7497131</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120259840</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>800979</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7496643</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120259857</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56514</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>801071</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7496976</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120259809</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>801023</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7496816</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120259827</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>800970</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7496679</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120259864</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>801011</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7497112</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120259799</v>
+      </c>
+      <c r="B44" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>801083</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7497051</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120259786</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>801231</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7497243</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120259789</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>801215</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7497216</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120259854</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90558</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>800995</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7496971</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120259808</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>801023</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7496816</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120259804</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>801070</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7497010</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120259871</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90957</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>801033</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7497193</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120259880</v>
+      </c>
+      <c r="B51" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>801127</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7497259</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120259838</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>800964</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7496622</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120259791</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>801191</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7497194</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120259852</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>800990</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7496945</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120259856</v>
+      </c>
+      <c r="B55" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>801071</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7496976</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120259865</v>
+      </c>
+      <c r="B56" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>801011</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7497112</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120259814</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>801003</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7496768</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120259850</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90527</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>800956</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7496826</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120259794</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>801089</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7497153</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120259842</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>800999</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7496673</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101064</v>
+        <v>120107787</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,26 +1018,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801077</v>
+        <v>800951</v>
       </c>
       <c r="R5" t="n">
-        <v>7497320</v>
+        <v>7496943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,13 +1088,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107787</v>
+        <v>120101064</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,31 +1133,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800951</v>
+        <v>801077</v>
       </c>
       <c r="R6" t="n">
-        <v>7496943</v>
+        <v>7497320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,17 +1198,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107773</v>
+        <v>120107787</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800947</v>
+        <v>800951</v>
       </c>
       <c r="R2" t="n">
-        <v>7497009</v>
+        <v>7496943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,13 +761,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107796</v>
+        <v>120101125</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800927</v>
+        <v>801014</v>
       </c>
       <c r="R3" t="n">
-        <v>7496884</v>
+        <v>7497308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101138</v>
+        <v>120107790</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,20 +908,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -920,12 +929,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -935,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800993</v>
+        <v>800951</v>
       </c>
       <c r="R4" t="n">
-        <v>7497292</v>
+        <v>7496943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,11 +984,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107787</v>
+        <v>120101090</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90975</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,35 +1022,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800951</v>
+        <v>801014</v>
       </c>
       <c r="R5" t="n">
-        <v>7496943</v>
+        <v>7497308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,17 +1091,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101064</v>
+        <v>120101206</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801077</v>
+        <v>801001</v>
       </c>
       <c r="R6" t="n">
-        <v>7497320</v>
+        <v>7497266</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101090</v>
+        <v>120101084</v>
       </c>
       <c r="B7" t="n">
-        <v>90957</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,25 +1234,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801014</v>
+        <v>801019</v>
       </c>
       <c r="R7" t="n">
-        <v>7497308</v>
+        <v>7497303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1331,7 @@
         <v>120101143</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1443,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107790</v>
+        <v>120101219</v>
       </c>
       <c r="B9" t="n">
-        <v>57937</v>
+        <v>90934</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,35 +1458,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102125</v>
+        <v>1506</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1495,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800951</v>
+        <v>800950</v>
       </c>
       <c r="R9" t="n">
-        <v>7496943</v>
+        <v>7497212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,6 +1529,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101219</v>
+        <v>120101138</v>
       </c>
       <c r="B10" t="n">
-        <v>90916</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,30 +1560,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800950</v>
+        <v>800993</v>
       </c>
       <c r="R10" t="n">
-        <v>7497212</v>
+        <v>7497292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,13 +1634,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101206</v>
+        <v>120101064</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801001</v>
+        <v>801077</v>
       </c>
       <c r="R11" t="n">
-        <v>7497266</v>
+        <v>7497320</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101248</v>
+        <v>120107773</v>
       </c>
       <c r="B12" t="n">
-        <v>57421</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,39 +1781,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1821,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800950</v>
+        <v>800947</v>
       </c>
       <c r="R12" t="n">
-        <v>7497212</v>
+        <v>7497009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,6 +1856,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1883,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101125</v>
+        <v>120101230</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>90975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,25 +1887,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1926,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801014</v>
+        <v>800950</v>
       </c>
       <c r="R13" t="n">
-        <v>7497308</v>
+        <v>7497212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101084</v>
+        <v>120101248</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>57431</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,30 +1993,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2032,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801019</v>
+        <v>800950</v>
       </c>
       <c r="R14" t="n">
-        <v>7497303</v>
+        <v>7497212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,7 +2077,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101230</v>
+        <v>120107796</v>
       </c>
       <c r="B15" t="n">
-        <v>90957</v>
+        <v>90598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2107,25 +2107,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4217</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800950</v>
+        <v>800927</v>
       </c>
       <c r="R15" t="n">
-        <v>7497212</v>
+        <v>7496884</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259855</v>
+        <v>120259878</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800995</v>
+        <v>801127</v>
       </c>
       <c r="R16" t="n">
-        <v>7496971</v>
+        <v>7497259</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259777</v>
+        <v>120259857</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>56524</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,26 +2323,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2350,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801236</v>
+        <v>801071</v>
       </c>
       <c r="R17" t="n">
-        <v>7497261</v>
+        <v>7496976</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2403,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2413,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259875</v>
+        <v>120259854</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,21 +2437,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801071</v>
+        <v>800995</v>
       </c>
       <c r="R18" t="n">
-        <v>7497222</v>
+        <v>7496971</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259821</v>
+        <v>120259875</v>
       </c>
       <c r="B19" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2543,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800977</v>
+        <v>801071</v>
       </c>
       <c r="R19" t="n">
-        <v>7496685</v>
+        <v>7497222</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259859</v>
+        <v>120259850</v>
       </c>
       <c r="B20" t="n">
-        <v>90846</v>
+        <v>90545</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,25 +2645,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2668,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800998</v>
+        <v>800956</v>
       </c>
       <c r="R20" t="n">
-        <v>7497020</v>
+        <v>7496826</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259863</v>
+        <v>120259800</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,31 +2755,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2779,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800990</v>
+        <v>801083</v>
       </c>
       <c r="R21" t="n">
-        <v>7497009</v>
+        <v>7497051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2817,17 +2820,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2846,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259822</v>
+        <v>120259838</v>
       </c>
       <c r="B22" t="n">
-        <v>90846</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,21 +2861,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2888,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800977</v>
+        <v>800964</v>
       </c>
       <c r="R22" t="n">
-        <v>7496685</v>
+        <v>7496622</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,10 +2951,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259793</v>
+        <v>120259799</v>
       </c>
       <c r="B23" t="n">
-        <v>90846</v>
+        <v>90576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,21 +2967,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2995,10 +2994,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801114</v>
+        <v>801083</v>
       </c>
       <c r="R23" t="n">
-        <v>7497155</v>
+        <v>7497051</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3058,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259818</v>
+        <v>120259871</v>
       </c>
       <c r="B24" t="n">
-        <v>57421</v>
+        <v>90975</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3074,35 +3073,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3110,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801003</v>
+        <v>801033</v>
       </c>
       <c r="R24" t="n">
-        <v>7496768</v>
+        <v>7497193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3154,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3172,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259874</v>
+        <v>120259880</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3215,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801042</v>
+        <v>801127</v>
       </c>
       <c r="R25" t="n">
-        <v>7497202</v>
+        <v>7497259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3278,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259803</v>
+        <v>120259863</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3326,10 +3317,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>801068</v>
+        <v>800990</v>
       </c>
       <c r="R26" t="n">
-        <v>7497037</v>
+        <v>7497009</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,7 +3357,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259801</v>
+        <v>120259818</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>57431</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3405,30 +3396,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801083</v>
+        <v>801003</v>
       </c>
       <c r="R27" t="n">
-        <v>7497051</v>
+        <v>7496768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3480,7 +3480,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3499,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259872</v>
+        <v>120259821</v>
       </c>
       <c r="B28" t="n">
-        <v>90509</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,21 +3514,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3542,10 +3541,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801033</v>
+        <v>800977</v>
       </c>
       <c r="R28" t="n">
-        <v>7497193</v>
+        <v>7496685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3607,7 @@
         <v>120259805</v>
       </c>
       <c r="B29" t="n">
-        <v>78608</v>
+        <v>78624</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3714,7 +3713,7 @@
         <v>120259792</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3817,10 +3816,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259802</v>
+        <v>120259865</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3860,10 +3859,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801083</v>
+        <v>801011</v>
       </c>
       <c r="R31" t="n">
-        <v>7497051</v>
+        <v>7497112</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3923,10 +3922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259800</v>
+        <v>120259822</v>
       </c>
       <c r="B32" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3939,21 +3938,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3966,10 +3965,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801083</v>
+        <v>800977</v>
       </c>
       <c r="R32" t="n">
-        <v>7497051</v>
+        <v>7496685</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4029,10 +4028,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259795</v>
+        <v>120259801</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4072,10 +4071,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801088</v>
+        <v>801083</v>
       </c>
       <c r="R33" t="n">
-        <v>7497114</v>
+        <v>7497051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4135,10 +4134,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259851</v>
+        <v>120259791</v>
       </c>
       <c r="B34" t="n">
-        <v>90558</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4151,21 +4150,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4178,10 +4177,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800967</v>
+        <v>801191</v>
       </c>
       <c r="R34" t="n">
-        <v>7496843</v>
+        <v>7497194</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4241,10 +4240,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259867</v>
+        <v>120259789</v>
       </c>
       <c r="B35" t="n">
-        <v>90916</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4253,25 +4252,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4284,10 +4283,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800977</v>
+        <v>801215</v>
       </c>
       <c r="R35" t="n">
-        <v>7497131</v>
+        <v>7497216</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,10 +4346,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259796</v>
+        <v>120259793</v>
       </c>
       <c r="B36" t="n">
-        <v>57421</v>
+        <v>90864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4359,39 +4358,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4399,10 +4389,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801096</v>
+        <v>801114</v>
       </c>
       <c r="R36" t="n">
-        <v>7497061</v>
+        <v>7497155</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4443,6 +4433,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4461,10 +4452,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259878</v>
+        <v>120259808</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4477,26 +4468,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4504,10 +4500,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801127</v>
+        <v>801023</v>
       </c>
       <c r="R37" t="n">
-        <v>7497259</v>
+        <v>7496816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4542,13 +4538,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4567,10 +4567,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259866</v>
+        <v>120259809</v>
       </c>
       <c r="B38" t="n">
-        <v>90846</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800977</v>
+        <v>801023</v>
       </c>
       <c r="R38" t="n">
-        <v>7497131</v>
+        <v>7496816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4676,7 +4676,7 @@
         <v>120259840</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259857</v>
+        <v>120259777</v>
       </c>
       <c r="B40" t="n">
-        <v>56514</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4795,35 +4795,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4831,10 +4822,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801071</v>
+        <v>801236</v>
       </c>
       <c r="R40" t="n">
-        <v>7496976</v>
+        <v>7497261</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,6 +4866,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4893,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259809</v>
+        <v>120259874</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4909,21 +4901,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4936,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801023</v>
+        <v>801042</v>
       </c>
       <c r="R41" t="n">
-        <v>7496816</v>
+        <v>7497202</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4999,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259827</v>
+        <v>120259856</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5015,31 +5007,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5047,10 +5034,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800970</v>
+        <v>801071</v>
       </c>
       <c r="R42" t="n">
-        <v>7496679</v>
+        <v>7496976</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5085,17 +5072,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5117,7 +5100,7 @@
         <v>120259864</v>
       </c>
       <c r="B43" t="n">
-        <v>90846</v>
+        <v>90864</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5220,10 +5203,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259799</v>
+        <v>120259866</v>
       </c>
       <c r="B44" t="n">
-        <v>90558</v>
+        <v>90864</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5236,21 +5219,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5263,10 +5246,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801083</v>
+        <v>800977</v>
       </c>
       <c r="R44" t="n">
-        <v>7497051</v>
+        <v>7497131</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5326,10 +5309,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259786</v>
+        <v>120259855</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5342,31 +5325,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5374,10 +5352,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>801231</v>
+        <v>800995</v>
       </c>
       <c r="R45" t="n">
-        <v>7497243</v>
+        <v>7496971</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5412,17 +5390,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5441,10 +5415,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259789</v>
+        <v>120259803</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5457,26 +5431,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5484,10 +5463,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>801215</v>
+        <v>801068</v>
       </c>
       <c r="R46" t="n">
-        <v>7497216</v>
+        <v>7497037</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5522,13 +5501,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5547,10 +5530,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259854</v>
+        <v>120259827</v>
       </c>
       <c r="B47" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5563,26 +5546,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5590,10 +5578,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800995</v>
+        <v>800970</v>
       </c>
       <c r="R47" t="n">
-        <v>7496971</v>
+        <v>7496679</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5628,13 +5616,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5653,10 +5645,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259808</v>
+        <v>120259804</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5669,31 +5661,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5701,10 +5688,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>801023</v>
+        <v>801070</v>
       </c>
       <c r="R48" t="n">
-        <v>7496816</v>
+        <v>7497010</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5739,17 +5726,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5768,10 +5751,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259804</v>
+        <v>120259859</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>90864</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5784,21 +5767,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5811,10 +5794,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>801070</v>
+        <v>800998</v>
       </c>
       <c r="R49" t="n">
-        <v>7497010</v>
+        <v>7497020</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5874,10 +5857,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259871</v>
+        <v>120259867</v>
       </c>
       <c r="B50" t="n">
-        <v>90957</v>
+        <v>90934</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5886,25 +5869,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5917,10 +5900,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>801033</v>
+        <v>800977</v>
       </c>
       <c r="R50" t="n">
-        <v>7497193</v>
+        <v>7497131</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,10 +5963,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259880</v>
+        <v>120259842</v>
       </c>
       <c r="B51" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5996,21 +5979,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6023,10 +6006,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>801127</v>
+        <v>800999</v>
       </c>
       <c r="R51" t="n">
-        <v>7497259</v>
+        <v>7496673</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6086,10 +6069,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259838</v>
+        <v>120259795</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6129,10 +6112,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800964</v>
+        <v>801088</v>
       </c>
       <c r="R52" t="n">
-        <v>7496622</v>
+        <v>7497114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6192,10 +6175,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259791</v>
+        <v>120259796</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6204,30 +6187,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6235,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>801191</v>
+        <v>801096</v>
       </c>
       <c r="R53" t="n">
-        <v>7497194</v>
+        <v>7497061</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6279,7 +6271,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6298,7 +6289,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259852</v>
+        <v>120259802</v>
       </c>
       <c r="B54" t="n">
         <v>90580</v>
@@ -6314,21 +6305,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6341,10 +6332,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800990</v>
+        <v>801083</v>
       </c>
       <c r="R54" t="n">
-        <v>7496945</v>
+        <v>7497051</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6404,10 +6395,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259856</v>
+        <v>120259852</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6447,10 +6438,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801071</v>
+        <v>800990</v>
       </c>
       <c r="R55" t="n">
-        <v>7496976</v>
+        <v>7496945</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6510,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259865</v>
+        <v>120259786</v>
       </c>
       <c r="B56" t="n">
-        <v>90562</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6526,26 +6517,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6553,10 +6549,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801011</v>
+        <v>801231</v>
       </c>
       <c r="R56" t="n">
-        <v>7497112</v>
+        <v>7497243</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6591,13 +6587,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259814</v>
+        <v>120259794</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6632,26 +6632,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6659,10 +6664,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801003</v>
+        <v>801089</v>
       </c>
       <c r="R57" t="n">
-        <v>7496768</v>
+        <v>7497153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6697,13 +6702,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6722,7 +6731,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259850</v>
+        <v>120259872</v>
       </c>
       <c r="B58" t="n">
         <v>90527</v>
@@ -6734,25 +6743,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6765,10 +6774,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800956</v>
+        <v>801033</v>
       </c>
       <c r="R58" t="n">
-        <v>7496826</v>
+        <v>7497193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6828,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259794</v>
+        <v>120259851</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6844,31 +6853,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6876,10 +6880,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>801089</v>
+        <v>800967</v>
       </c>
       <c r="R59" t="n">
-        <v>7497153</v>
+        <v>7496843</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6914,17 +6918,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259842</v>
+        <v>120259814</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>90598</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800999</v>
+        <v>801003</v>
       </c>
       <c r="R60" t="n">
-        <v>7496673</v>
+        <v>7496768</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -2739,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259800</v>
+        <v>120259838</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801083</v>
+        <v>800964</v>
       </c>
       <c r="R21" t="n">
-        <v>7497051</v>
+        <v>7496622</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259838</v>
+        <v>120259800</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800964</v>
+        <v>801083</v>
       </c>
       <c r="R22" t="n">
-        <v>7496622</v>
+        <v>7497051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107787</v>
+        <v>120107790</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101125</v>
+        <v>120107773</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -833,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801014</v>
+        <v>800947</v>
       </c>
       <c r="R3" t="n">
-        <v>7497308</v>
+        <v>7497009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107790</v>
+        <v>120101248</v>
       </c>
       <c r="B4" t="n">
-        <v>57947</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -931,14 +930,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -948,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800951</v>
+        <v>800950</v>
       </c>
       <c r="R4" t="n">
-        <v>7496943</v>
+        <v>7497212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101090</v>
+        <v>120101084</v>
       </c>
       <c r="B5" t="n">
-        <v>90975</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801014</v>
+        <v>801019</v>
       </c>
       <c r="R5" t="n">
-        <v>7497308</v>
+        <v>7497303</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101206</v>
+        <v>120107787</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,26 +1131,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801001</v>
+        <v>800951</v>
       </c>
       <c r="R6" t="n">
-        <v>7497266</v>
+        <v>7496943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,13 +1201,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1222,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101084</v>
+        <v>120101064</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1265,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801019</v>
+        <v>801077</v>
       </c>
       <c r="R7" t="n">
-        <v>7497303</v>
+        <v>7497320</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120101143</v>
+        <v>120107796</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,35 +1352,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800993</v>
+        <v>800927</v>
       </c>
       <c r="R8" t="n">
-        <v>7497292</v>
+        <v>7496884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101138</v>
+        <v>120101125</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,31 +1564,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800993</v>
+        <v>801014</v>
       </c>
       <c r="R10" t="n">
-        <v>7497292</v>
+        <v>7497308</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,17 +1629,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101064</v>
+        <v>120101143</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,26 +1670,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801077</v>
+        <v>800993</v>
       </c>
       <c r="R11" t="n">
-        <v>7497320</v>
+        <v>7497292</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1750,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107773</v>
+        <v>120101090</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,25 +1780,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800947</v>
+        <v>801014</v>
       </c>
       <c r="R12" t="n">
-        <v>7497009</v>
+        <v>7497308</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,10 +1980,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101248</v>
+        <v>120101138</v>
       </c>
       <c r="B14" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,20 +1992,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2014,16 +2013,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2033,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800950</v>
+        <v>800993</v>
       </c>
       <c r="R14" t="n">
-        <v>7497212</v>
+        <v>7497292</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,6 +2064,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120107796</v>
+        <v>120101206</v>
       </c>
       <c r="B15" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,21 +2111,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800927</v>
+        <v>801001</v>
       </c>
       <c r="R15" t="n">
-        <v>7496884</v>
+        <v>7497266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259878</v>
+        <v>120259851</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,21 +2217,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801127</v>
+        <v>800967</v>
       </c>
       <c r="R16" t="n">
-        <v>7497259</v>
+        <v>7496843</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259857</v>
+        <v>120259854</v>
       </c>
       <c r="B17" t="n">
-        <v>56524</v>
+        <v>90576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,35 +2323,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801071</v>
+        <v>800995</v>
       </c>
       <c r="R17" t="n">
-        <v>7496976</v>
+        <v>7496971</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,6 +2394,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2421,7 +2413,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259854</v>
+        <v>120259799</v>
       </c>
       <c r="B18" t="n">
         <v>90576</v>
@@ -2464,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800995</v>
+        <v>801083</v>
       </c>
       <c r="R18" t="n">
-        <v>7496971</v>
+        <v>7497051</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2527,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259875</v>
+        <v>120259880</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2543,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801071</v>
+        <v>801127</v>
       </c>
       <c r="R19" t="n">
-        <v>7497222</v>
+        <v>7497259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2633,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259850</v>
+        <v>120259791</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
+        <v>90598</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,25 +2637,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800956</v>
+        <v>801191</v>
       </c>
       <c r="R20" t="n">
-        <v>7496826</v>
+        <v>7497194</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2731,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259838</v>
+        <v>120259777</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2782,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800964</v>
+        <v>801236</v>
       </c>
       <c r="R21" t="n">
-        <v>7496622</v>
+        <v>7497261</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259800</v>
+        <v>120259786</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,26 +2853,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2888,10 +2885,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801083</v>
+        <v>801231</v>
       </c>
       <c r="R22" t="n">
-        <v>7497051</v>
+        <v>7497243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,13 +2923,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2951,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259799</v>
+        <v>120259794</v>
       </c>
       <c r="B23" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2967,26 +2968,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2994,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801083</v>
+        <v>801089</v>
       </c>
       <c r="R23" t="n">
-        <v>7497051</v>
+        <v>7497153</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3032,13 +3038,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3057,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259871</v>
+        <v>120259805</v>
       </c>
       <c r="B24" t="n">
-        <v>90975</v>
+        <v>78624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,25 +3079,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801033</v>
+        <v>801066</v>
       </c>
       <c r="R24" t="n">
-        <v>7497193</v>
+        <v>7497007</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,7 +3173,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259880</v>
+        <v>120259800</v>
       </c>
       <c r="B25" t="n">
         <v>90598</v>
@@ -3206,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801127</v>
+        <v>801083</v>
       </c>
       <c r="R25" t="n">
-        <v>7497259</v>
+        <v>7497051</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259863</v>
+        <v>120259808</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3317,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800990</v>
+        <v>801023</v>
       </c>
       <c r="R26" t="n">
-        <v>7497009</v>
+        <v>7496816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3357,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,10 +3394,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259818</v>
+        <v>120259875</v>
       </c>
       <c r="B27" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3396,39 +3406,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3436,10 +3437,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801003</v>
+        <v>801071</v>
       </c>
       <c r="R27" t="n">
-        <v>7496768</v>
+        <v>7497222</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3480,6 +3481,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3498,10 +3500,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259821</v>
+        <v>120259867</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>90934</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3510,25 +3512,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3544,7 +3546,7 @@
         <v>800977</v>
       </c>
       <c r="R28" t="n">
-        <v>7496685</v>
+        <v>7497131</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3604,10 +3606,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120259805</v>
+        <v>120259865</v>
       </c>
       <c r="B29" t="n">
-        <v>78624</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3620,21 +3622,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3647,10 +3649,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801066</v>
+        <v>801011</v>
       </c>
       <c r="R29" t="n">
-        <v>7497007</v>
+        <v>7497112</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3710,10 +3712,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120259792</v>
+        <v>120259874</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3726,21 +3728,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3753,10 +3755,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>801191</v>
+        <v>801042</v>
       </c>
       <c r="R30" t="n">
-        <v>7497171</v>
+        <v>7497202</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3816,10 +3818,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259865</v>
+        <v>120259796</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>57431</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3828,30 +3830,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3859,10 +3870,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801011</v>
+        <v>801096</v>
       </c>
       <c r="R31" t="n">
-        <v>7497112</v>
+        <v>7497061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,7 +3914,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3922,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259822</v>
+        <v>120259827</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3938,26 +3948,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3965,10 +3980,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800977</v>
+        <v>800970</v>
       </c>
       <c r="R32" t="n">
-        <v>7496685</v>
+        <v>7496679</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4003,13 +4018,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4028,10 +4047,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259801</v>
+        <v>120259856</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4044,21 +4063,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4071,10 +4090,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801083</v>
+        <v>801071</v>
       </c>
       <c r="R33" t="n">
-        <v>7497051</v>
+        <v>7496976</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4134,10 +4153,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259791</v>
+        <v>120259789</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4150,21 +4169,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4177,10 +4196,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801191</v>
+        <v>801215</v>
       </c>
       <c r="R34" t="n">
-        <v>7497194</v>
+        <v>7497216</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4240,10 +4259,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259789</v>
+        <v>120259821</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4256,21 +4275,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4283,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801215</v>
+        <v>800977</v>
       </c>
       <c r="R35" t="n">
-        <v>7497216</v>
+        <v>7496685</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4346,7 +4365,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259793</v>
+        <v>120259864</v>
       </c>
       <c r="B36" t="n">
         <v>90864</v>
@@ -4389,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801114</v>
+        <v>801011</v>
       </c>
       <c r="R36" t="n">
-        <v>7497155</v>
+        <v>7497112</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,10 +4471,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259808</v>
+        <v>120259840</v>
       </c>
       <c r="B37" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4468,31 +4487,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4500,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801023</v>
+        <v>800979</v>
       </c>
       <c r="R37" t="n">
-        <v>7496816</v>
+        <v>7496643</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4538,17 +4552,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4567,7 +4577,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259809</v>
+        <v>120259792</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -4610,10 +4620,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>801023</v>
+        <v>801191</v>
       </c>
       <c r="R38" t="n">
-        <v>7496816</v>
+        <v>7497171</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4673,10 +4683,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259840</v>
+        <v>120259804</v>
       </c>
       <c r="B39" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4689,21 +4699,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4716,10 +4726,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800979</v>
+        <v>801070</v>
       </c>
       <c r="R39" t="n">
-        <v>7496643</v>
+        <v>7497010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4779,7 +4789,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259777</v>
+        <v>120259795</v>
       </c>
       <c r="B40" t="n">
         <v>78542</v>
@@ -4822,10 +4832,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801236</v>
+        <v>801088</v>
       </c>
       <c r="R40" t="n">
-        <v>7497261</v>
+        <v>7497114</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,10 +4895,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259874</v>
+        <v>120259801</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,21 +4911,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4928,10 +4938,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801042</v>
+        <v>801083</v>
       </c>
       <c r="R41" t="n">
-        <v>7497202</v>
+        <v>7497051</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4991,10 +5001,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259856</v>
+        <v>120259863</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5007,26 +5017,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5034,10 +5049,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801071</v>
+        <v>800990</v>
       </c>
       <c r="R42" t="n">
-        <v>7496976</v>
+        <v>7497009</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5072,13 +5087,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5097,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259864</v>
+        <v>120259814</v>
       </c>
       <c r="B43" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5113,21 +5132,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5140,10 +5159,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801011</v>
+        <v>801003</v>
       </c>
       <c r="R43" t="n">
-        <v>7497112</v>
+        <v>7496768</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5203,10 +5222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259866</v>
+        <v>120259852</v>
       </c>
       <c r="B44" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5219,21 +5238,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5246,10 +5265,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800977</v>
+        <v>800990</v>
       </c>
       <c r="R44" t="n">
-        <v>7497131</v>
+        <v>7496945</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5309,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259855</v>
+        <v>120259822</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5325,21 +5344,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5352,10 +5371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800995</v>
+        <v>800977</v>
       </c>
       <c r="R45" t="n">
-        <v>7496971</v>
+        <v>7496685</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5415,10 +5434,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259803</v>
+        <v>120259857</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5431,16 +5450,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5448,12 +5467,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5463,10 +5486,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>801068</v>
+        <v>801071</v>
       </c>
       <c r="R46" t="n">
-        <v>7497037</v>
+        <v>7496976</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5499,11 +5522,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5530,10 +5548,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259827</v>
+        <v>120259838</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5546,31 +5564,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5578,10 +5591,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800970</v>
+        <v>800964</v>
       </c>
       <c r="R47" t="n">
-        <v>7496679</v>
+        <v>7496622</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5616,17 +5629,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5645,10 +5654,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259804</v>
+        <v>120259872</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>90527</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5661,21 +5670,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5688,10 +5697,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>801070</v>
+        <v>801033</v>
       </c>
       <c r="R48" t="n">
-        <v>7497010</v>
+        <v>7497193</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5751,10 +5760,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259859</v>
+        <v>120259855</v>
       </c>
       <c r="B49" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5767,21 +5776,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5794,10 +5803,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800998</v>
+        <v>800995</v>
       </c>
       <c r="R49" t="n">
-        <v>7497020</v>
+        <v>7496971</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5857,10 +5866,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259867</v>
+        <v>120259842</v>
       </c>
       <c r="B50" t="n">
-        <v>90934</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5869,25 +5878,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5900,10 +5909,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800977</v>
+        <v>800999</v>
       </c>
       <c r="R50" t="n">
-        <v>7497131</v>
+        <v>7496673</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5963,10 +5972,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259842</v>
+        <v>120259803</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5979,26 +5988,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6006,10 +6020,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800999</v>
+        <v>801068</v>
       </c>
       <c r="R51" t="n">
-        <v>7496673</v>
+        <v>7497037</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6044,13 +6058,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6069,10 +6087,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259795</v>
+        <v>120259802</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6085,21 +6103,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6112,10 +6130,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>801088</v>
+        <v>801083</v>
       </c>
       <c r="R52" t="n">
-        <v>7497114</v>
+        <v>7497051</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6175,10 +6193,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259796</v>
+        <v>120259859</v>
       </c>
       <c r="B53" t="n">
-        <v>57431</v>
+        <v>90864</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6187,39 +6205,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6227,10 +6236,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>801096</v>
+        <v>800998</v>
       </c>
       <c r="R53" t="n">
-        <v>7497061</v>
+        <v>7497020</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6271,6 +6280,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6289,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259802</v>
+        <v>120259878</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,21 +6315,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6332,10 +6342,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>801083</v>
+        <v>801127</v>
       </c>
       <c r="R54" t="n">
-        <v>7497051</v>
+        <v>7497259</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6395,10 +6405,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259852</v>
+        <v>120259809</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6411,21 +6421,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6438,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800990</v>
+        <v>801023</v>
       </c>
       <c r="R55" t="n">
-        <v>7496945</v>
+        <v>7496816</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6501,10 +6511,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259786</v>
+        <v>120259866</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6517,31 +6527,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6549,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801231</v>
+        <v>800977</v>
       </c>
       <c r="R56" t="n">
-        <v>7497243</v>
+        <v>7497131</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6587,17 +6592,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6616,10 +6617,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259794</v>
+        <v>120259793</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6632,31 +6633,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6664,10 +6660,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801089</v>
+        <v>801114</v>
       </c>
       <c r="R57" t="n">
-        <v>7497153</v>
+        <v>7497155</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6702,17 +6698,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6731,10 +6723,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259872</v>
+        <v>120259818</v>
       </c>
       <c r="B58" t="n">
-        <v>90527</v>
+        <v>57431</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6743,30 +6735,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>112</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6774,10 +6775,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>801033</v>
+        <v>801003</v>
       </c>
       <c r="R58" t="n">
-        <v>7497193</v>
+        <v>7496768</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,7 +6819,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259851</v>
+        <v>120259871</v>
       </c>
       <c r="B59" t="n">
-        <v>90576</v>
+        <v>90975</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6849,25 +6849,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>4217</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800967</v>
+        <v>801033</v>
       </c>
       <c r="R59" t="n">
-        <v>7496843</v>
+        <v>7497193</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259814</v>
+        <v>120259850</v>
       </c>
       <c r="B60" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6955,25 +6955,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>801003</v>
+        <v>800956</v>
       </c>
       <c r="R60" t="n">
-        <v>7496768</v>
+        <v>7496826</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -6299,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259878</v>
+        <v>120259866</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6315,21 +6315,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>801127</v>
+        <v>800977</v>
       </c>
       <c r="R54" t="n">
-        <v>7497259</v>
+        <v>7497131</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259809</v>
+        <v>120259793</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801023</v>
+        <v>801114</v>
       </c>
       <c r="R55" t="n">
-        <v>7496816</v>
+        <v>7497155</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259866</v>
+        <v>120259878</v>
       </c>
       <c r="B56" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6527,21 +6527,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6554,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800977</v>
+        <v>801127</v>
       </c>
       <c r="R56" t="n">
-        <v>7497131</v>
+        <v>7497259</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259793</v>
+        <v>120259809</v>
       </c>
       <c r="B57" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6633,21 +6633,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801114</v>
+        <v>801023</v>
       </c>
       <c r="R57" t="n">
-        <v>7497155</v>
+        <v>7496816</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107790</v>
+        <v>120107796</v>
       </c>
       <c r="B2" t="n">
-        <v>57947</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800951</v>
+        <v>800927</v>
       </c>
       <c r="R2" t="n">
-        <v>7496943</v>
+        <v>7496884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120107773</v>
+        <v>120101090</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800947</v>
+        <v>801014</v>
       </c>
       <c r="R3" t="n">
-        <v>7497009</v>
+        <v>7497308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101248</v>
+        <v>120107790</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>57947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,20 +899,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>102125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,14 +922,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800950</v>
+        <v>800951</v>
       </c>
       <c r="R4" t="n">
-        <v>7497212</v>
+        <v>7496943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101084</v>
+        <v>120107787</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,26 +1017,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1052,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801019</v>
+        <v>800951</v>
       </c>
       <c r="R5" t="n">
-        <v>7497303</v>
+        <v>7496943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,13 +1087,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,7 +1116,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107787</v>
+        <v>120101138</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1163,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800951</v>
+        <v>800993</v>
       </c>
       <c r="R6" t="n">
-        <v>7496943</v>
+        <v>7497292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101064</v>
+        <v>120101084</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1273,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801077</v>
+        <v>801019</v>
       </c>
       <c r="R7" t="n">
-        <v>7497320</v>
+        <v>7497303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1336,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107796</v>
+        <v>120101143</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,26 +1353,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800927</v>
+        <v>800993</v>
       </c>
       <c r="R8" t="n">
-        <v>7496884</v>
+        <v>7497292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,7 +1433,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101219</v>
+        <v>120101230</v>
       </c>
       <c r="B9" t="n">
-        <v>90934</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1463,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1506</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1654,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101143</v>
+        <v>120101248</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>57431</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,25 +1675,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1696,7 +1705,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1706,10 +1715,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800993</v>
+        <v>800950</v>
       </c>
       <c r="R11" t="n">
-        <v>7497292</v>
+        <v>7497212</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101090</v>
+        <v>120107773</v>
       </c>
       <c r="B12" t="n">
-        <v>90975</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,25 +1789,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801014</v>
+        <v>800947</v>
       </c>
       <c r="R12" t="n">
-        <v>7497308</v>
+        <v>7497009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101230</v>
+        <v>120101219</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>90934</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1886,25 +1895,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101138</v>
+        <v>120101206</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,31 +2005,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2028,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800993</v>
+        <v>801001</v>
       </c>
       <c r="R14" t="n">
-        <v>7497292</v>
+        <v>7497266</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,17 +2070,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101206</v>
+        <v>120101064</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801001</v>
+        <v>801077</v>
       </c>
       <c r="R15" t="n">
-        <v>7497266</v>
+        <v>7497320</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259851</v>
+        <v>120259795</v>
       </c>
       <c r="B16" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,21 +2217,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800967</v>
+        <v>801088</v>
       </c>
       <c r="R16" t="n">
-        <v>7496843</v>
+        <v>7497114</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259854</v>
+        <v>120259874</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800995</v>
+        <v>801042</v>
       </c>
       <c r="R17" t="n">
-        <v>7496971</v>
+        <v>7497202</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259799</v>
+        <v>120259791</v>
       </c>
       <c r="B18" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,21 +2429,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801083</v>
+        <v>801191</v>
       </c>
       <c r="R18" t="n">
-        <v>7497051</v>
+        <v>7497194</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259880</v>
+        <v>120259867</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>90934</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2531,25 +2531,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801127</v>
+        <v>800977</v>
       </c>
       <c r="R19" t="n">
-        <v>7497259</v>
+        <v>7497131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259791</v>
+        <v>120259840</v>
       </c>
       <c r="B20" t="n">
         <v>90598</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801191</v>
+        <v>800979</v>
       </c>
       <c r="R20" t="n">
-        <v>7497194</v>
+        <v>7496643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259777</v>
+        <v>120259821</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801236</v>
+        <v>800977</v>
       </c>
       <c r="R21" t="n">
-        <v>7497261</v>
+        <v>7496685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259786</v>
+        <v>120259864</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,31 +2853,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2885,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801231</v>
+        <v>801011</v>
       </c>
       <c r="R22" t="n">
-        <v>7497243</v>
+        <v>7497112</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2923,17 +2918,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2952,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259794</v>
+        <v>120259852</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,31 +2959,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801089</v>
+        <v>800990</v>
       </c>
       <c r="R23" t="n">
-        <v>7497153</v>
+        <v>7496945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,17 +3024,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3067,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259805</v>
+        <v>120259871</v>
       </c>
       <c r="B24" t="n">
-        <v>78624</v>
+        <v>90975</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,25 +3061,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>4217</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3110,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801066</v>
+        <v>801033</v>
       </c>
       <c r="R24" t="n">
-        <v>7497007</v>
+        <v>7497193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3173,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259800</v>
+        <v>120259822</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3189,21 +3171,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3216,10 +3198,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801083</v>
+        <v>800977</v>
       </c>
       <c r="R25" t="n">
-        <v>7497051</v>
+        <v>7496685</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3261,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259808</v>
+        <v>120259802</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,31 +3277,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3327,10 +3304,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>801023</v>
+        <v>801083</v>
       </c>
       <c r="R26" t="n">
-        <v>7496816</v>
+        <v>7497051</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3365,17 +3342,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3394,7 +3367,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259875</v>
+        <v>120259809</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3437,10 +3410,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801071</v>
+        <v>801023</v>
       </c>
       <c r="R27" t="n">
-        <v>7497222</v>
+        <v>7496816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3500,10 +3473,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259867</v>
+        <v>120259878</v>
       </c>
       <c r="B28" t="n">
-        <v>90934</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3512,25 +3485,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3543,10 +3516,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800977</v>
+        <v>801127</v>
       </c>
       <c r="R28" t="n">
-        <v>7497131</v>
+        <v>7497259</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,10 +3579,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120259865</v>
+        <v>120259777</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3622,21 +3595,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3649,10 +3622,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801011</v>
+        <v>801236</v>
       </c>
       <c r="R29" t="n">
-        <v>7497112</v>
+        <v>7497261</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3712,10 +3685,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120259874</v>
+        <v>120259863</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3728,26 +3701,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3755,10 +3733,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>801042</v>
+        <v>800990</v>
       </c>
       <c r="R30" t="n">
-        <v>7497202</v>
+        <v>7497009</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3793,13 +3771,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3818,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259796</v>
+        <v>120259854</v>
       </c>
       <c r="B31" t="n">
-        <v>57431</v>
+        <v>90576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3830,39 +3812,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3870,10 +3843,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>801096</v>
+        <v>800995</v>
       </c>
       <c r="R31" t="n">
-        <v>7497061</v>
+        <v>7496971</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3914,6 +3887,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3932,10 +3906,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259827</v>
+        <v>120259838</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3948,31 +3922,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3980,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800970</v>
+        <v>800964</v>
       </c>
       <c r="R32" t="n">
-        <v>7496679</v>
+        <v>7496622</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4018,17 +3987,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4153,7 +4118,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259789</v>
+        <v>120259801</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -4196,10 +4161,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801215</v>
+        <v>801083</v>
       </c>
       <c r="R34" t="n">
-        <v>7497216</v>
+        <v>7497051</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4259,10 +4224,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259821</v>
+        <v>120259855</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4275,21 +4240,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4302,10 +4267,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800977</v>
+        <v>800995</v>
       </c>
       <c r="R35" t="n">
-        <v>7496685</v>
+        <v>7496971</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,10 +4330,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259864</v>
+        <v>120259857</v>
       </c>
       <c r="B36" t="n">
-        <v>90864</v>
+        <v>56524</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4381,26 +4346,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4408,10 +4382,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801011</v>
+        <v>801071</v>
       </c>
       <c r="R36" t="n">
-        <v>7497112</v>
+        <v>7496976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4452,7 +4426,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4471,10 +4444,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259840</v>
+        <v>120259818</v>
       </c>
       <c r="B37" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4483,30 +4456,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4514,10 +4496,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800979</v>
+        <v>801003</v>
       </c>
       <c r="R37" t="n">
-        <v>7496643</v>
+        <v>7496768</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4558,7 +4540,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4577,10 +4558,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259792</v>
+        <v>120259851</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4593,21 +4574,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4620,10 +4601,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>801191</v>
+        <v>800967</v>
       </c>
       <c r="R38" t="n">
-        <v>7497171</v>
+        <v>7496843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4683,7 +4664,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259804</v>
+        <v>120259792</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -4726,10 +4707,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801070</v>
+        <v>801191</v>
       </c>
       <c r="R39" t="n">
-        <v>7497010</v>
+        <v>7497171</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4789,10 +4770,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259795</v>
+        <v>120259880</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4805,21 +4786,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4832,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801088</v>
+        <v>801127</v>
       </c>
       <c r="R40" t="n">
-        <v>7497114</v>
+        <v>7497259</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4895,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259801</v>
+        <v>120259796</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4907,30 +4888,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4938,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801083</v>
+        <v>801096</v>
       </c>
       <c r="R41" t="n">
-        <v>7497051</v>
+        <v>7497061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,7 +4972,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5001,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259863</v>
+        <v>120259804</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5017,31 +5006,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5049,10 +5033,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800990</v>
+        <v>801070</v>
       </c>
       <c r="R42" t="n">
-        <v>7497009</v>
+        <v>7497010</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5087,17 +5071,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5116,10 +5096,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259814</v>
+        <v>120259808</v>
       </c>
       <c r="B43" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5132,26 +5112,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5159,10 +5144,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801003</v>
+        <v>801023</v>
       </c>
       <c r="R43" t="n">
-        <v>7496768</v>
+        <v>7496816</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5197,13 +5182,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5222,10 +5211,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259852</v>
+        <v>120259805</v>
       </c>
       <c r="B44" t="n">
-        <v>90598</v>
+        <v>78624</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5238,21 +5227,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5265,10 +5254,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800990</v>
+        <v>801066</v>
       </c>
       <c r="R44" t="n">
-        <v>7496945</v>
+        <v>7497007</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5328,10 +5317,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259822</v>
+        <v>120259786</v>
       </c>
       <c r="B45" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5344,26 +5333,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5371,10 +5365,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800977</v>
+        <v>801231</v>
       </c>
       <c r="R45" t="n">
-        <v>7496685</v>
+        <v>7497243</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5409,13 +5403,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5434,10 +5432,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259857</v>
+        <v>120259799</v>
       </c>
       <c r="B46" t="n">
-        <v>56524</v>
+        <v>90576</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5450,35 +5448,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5486,10 +5475,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>801071</v>
+        <v>801083</v>
       </c>
       <c r="R46" t="n">
-        <v>7496976</v>
+        <v>7497051</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,6 +5519,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5548,10 +5538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259838</v>
+        <v>120259866</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5564,21 +5554,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5591,10 +5581,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800964</v>
+        <v>800977</v>
       </c>
       <c r="R47" t="n">
-        <v>7496622</v>
+        <v>7497131</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5654,10 +5644,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259872</v>
+        <v>120259875</v>
       </c>
       <c r="B48" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5670,21 +5660,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5697,10 +5687,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>801033</v>
+        <v>801071</v>
       </c>
       <c r="R48" t="n">
-        <v>7497193</v>
+        <v>7497222</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5760,7 +5750,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259855</v>
+        <v>120259842</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -5803,10 +5793,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800995</v>
+        <v>800999</v>
       </c>
       <c r="R49" t="n">
-        <v>7496971</v>
+        <v>7496673</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5866,10 +5856,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259842</v>
+        <v>120259793</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5882,21 +5872,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5909,10 +5899,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800999</v>
+        <v>801114</v>
       </c>
       <c r="R50" t="n">
-        <v>7496673</v>
+        <v>7497155</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5972,10 +5962,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259803</v>
+        <v>120259872</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5988,31 +5978,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6020,10 +6005,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>801068</v>
+        <v>801033</v>
       </c>
       <c r="R51" t="n">
-        <v>7497037</v>
+        <v>7497193</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6058,17 +6043,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6087,10 +6068,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259802</v>
+        <v>120259827</v>
       </c>
       <c r="B52" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6103,26 +6084,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6130,10 +6116,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>801083</v>
+        <v>800970</v>
       </c>
       <c r="R52" t="n">
-        <v>7497051</v>
+        <v>7496679</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6168,13 +6154,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6193,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259859</v>
+        <v>120259850</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6205,25 +6195,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6236,10 +6226,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800998</v>
+        <v>800956</v>
       </c>
       <c r="R53" t="n">
-        <v>7497020</v>
+        <v>7496826</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6289,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259866</v>
+        <v>120259859</v>
       </c>
       <c r="B54" t="n">
         <v>90864</v>
@@ -6342,10 +6332,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800977</v>
+        <v>800998</v>
       </c>
       <c r="R54" t="n">
-        <v>7497131</v>
+        <v>7497020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6405,10 +6395,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259793</v>
+        <v>120259865</v>
       </c>
       <c r="B55" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6421,21 +6411,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6448,10 +6438,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801114</v>
+        <v>801011</v>
       </c>
       <c r="R55" t="n">
-        <v>7497155</v>
+        <v>7497112</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6511,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259878</v>
+        <v>120259814</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6527,21 +6517,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6554,10 +6544,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801127</v>
+        <v>801003</v>
       </c>
       <c r="R56" t="n">
-        <v>7497259</v>
+        <v>7496768</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6617,10 +6607,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259809</v>
+        <v>120259800</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6633,21 +6623,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6660,10 +6650,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801023</v>
+        <v>801083</v>
       </c>
       <c r="R57" t="n">
-        <v>7496816</v>
+        <v>7497051</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6723,10 +6713,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259818</v>
+        <v>120259789</v>
       </c>
       <c r="B58" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6735,39 +6725,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6775,10 +6756,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>801003</v>
+        <v>801215</v>
       </c>
       <c r="R58" t="n">
-        <v>7496768</v>
+        <v>7497216</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6819,6 +6800,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6837,10 +6819,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259871</v>
+        <v>120259803</v>
       </c>
       <c r="B59" t="n">
-        <v>90975</v>
+        <v>57320</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6849,30 +6831,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6880,10 +6867,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>801033</v>
+        <v>801068</v>
       </c>
       <c r="R59" t="n">
-        <v>7497193</v>
+        <v>7497037</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6918,13 +6905,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6943,10 +6934,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259850</v>
+        <v>120259794</v>
       </c>
       <c r="B60" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6955,30 +6946,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6986,10 +6982,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800956</v>
+        <v>801089</v>
       </c>
       <c r="R60" t="n">
-        <v>7496826</v>
+        <v>7497153</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7024,13 +7020,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -4876,10 +4876,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259796</v>
+        <v>120259804</v>
       </c>
       <c r="B41" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4888,39 +4888,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4928,10 +4919,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801096</v>
+        <v>801070</v>
       </c>
       <c r="R41" t="n">
-        <v>7497061</v>
+        <v>7497010</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,6 +4963,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4990,10 +4982,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259804</v>
+        <v>120259808</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5006,26 +4998,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5033,10 +5030,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801070</v>
+        <v>801023</v>
       </c>
       <c r="R42" t="n">
-        <v>7497010</v>
+        <v>7496816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5071,13 +5068,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5096,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259808</v>
+        <v>120259796</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5108,20 +5109,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5129,12 +5130,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5144,10 +5149,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801023</v>
+        <v>801096</v>
       </c>
       <c r="R43" t="n">
-        <v>7496816</v>
+        <v>7497061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5180,11 +5185,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107796</v>
+        <v>120101064</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800927</v>
+        <v>801077</v>
       </c>
       <c r="R2" t="n">
-        <v>7496884</v>
+        <v>7497320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101090</v>
+        <v>120101248</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>57431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801014</v>
+        <v>800950</v>
       </c>
       <c r="R3" t="n">
-        <v>7497308</v>
+        <v>7497212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107790</v>
+        <v>120101206</v>
       </c>
       <c r="B4" t="n">
-        <v>57947</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,39 +907,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800951</v>
+        <v>801001</v>
       </c>
       <c r="R4" t="n">
-        <v>7496943</v>
+        <v>7497266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,6 +982,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107787</v>
+        <v>120107790</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>57947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,20 +1013,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1034,12 +1034,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1085,11 +1089,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101138</v>
+        <v>120107796</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,31 +1131,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1164,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800993</v>
+        <v>800927</v>
       </c>
       <c r="R6" t="n">
-        <v>7497292</v>
+        <v>7496884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,17 +1196,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1231,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101084</v>
+        <v>120101230</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,25 +1233,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1274,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801019</v>
+        <v>800950</v>
       </c>
       <c r="R7" t="n">
-        <v>7497303</v>
+        <v>7497212</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1451,7 +1441,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101230</v>
+        <v>120101090</v>
       </c>
       <c r="B9" t="n">
         <v>90975</v>
@@ -1494,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800950</v>
+        <v>801014</v>
       </c>
       <c r="R9" t="n">
-        <v>7497212</v>
+        <v>7497308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1547,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101125</v>
+        <v>120101084</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1600,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801014</v>
+        <v>801019</v>
       </c>
       <c r="R10" t="n">
-        <v>7497308</v>
+        <v>7497303</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101248</v>
+        <v>120101125</v>
       </c>
       <c r="B11" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,39 +1665,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800950</v>
+        <v>801014</v>
       </c>
       <c r="R11" t="n">
-        <v>7497212</v>
+        <v>7497308</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1740,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107773</v>
+        <v>120101219</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90934</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,25 +1771,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800947</v>
+        <v>800950</v>
       </c>
       <c r="R12" t="n">
-        <v>7497009</v>
+        <v>7497212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101219</v>
+        <v>120101138</v>
       </c>
       <c r="B13" t="n">
-        <v>90934</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,30 +1877,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1926,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800950</v>
+        <v>800993</v>
       </c>
       <c r="R13" t="n">
-        <v>7497212</v>
+        <v>7497292</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,13 +1951,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1989,7 +1980,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101206</v>
+        <v>120107773</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2032,10 +2023,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801001</v>
+        <v>800947</v>
       </c>
       <c r="R14" t="n">
-        <v>7497266</v>
+        <v>7497009</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101064</v>
+        <v>120107787</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2111,26 +2102,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2138,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801077</v>
+        <v>800951</v>
       </c>
       <c r="R15" t="n">
-        <v>7497320</v>
+        <v>7496943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2176,13 +2172,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259795</v>
+        <v>120259818</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,30 +2213,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2244,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801088</v>
+        <v>801003</v>
       </c>
       <c r="R16" t="n">
-        <v>7497114</v>
+        <v>7496768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2297,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2307,10 +2315,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259874</v>
+        <v>120259801</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801042</v>
+        <v>801083</v>
       </c>
       <c r="R17" t="n">
-        <v>7497202</v>
+        <v>7497051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2421,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259791</v>
+        <v>120259880</v>
       </c>
       <c r="B18" t="n">
         <v>90598</v>
@@ -2456,10 +2464,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801191</v>
+        <v>801127</v>
       </c>
       <c r="R18" t="n">
-        <v>7497194</v>
+        <v>7497259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259867</v>
+        <v>120259856</v>
       </c>
       <c r="B19" t="n">
-        <v>90934</v>
+        <v>90598</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2531,25 +2539,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800977</v>
+        <v>801071</v>
       </c>
       <c r="R19" t="n">
-        <v>7497131</v>
+        <v>7496976</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2633,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259840</v>
+        <v>120259796</v>
       </c>
       <c r="B20" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,30 +2645,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2668,10 +2685,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800979</v>
+        <v>801096</v>
       </c>
       <c r="R20" t="n">
-        <v>7496643</v>
+        <v>7497061</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2729,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2731,10 +2747,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259821</v>
+        <v>120259814</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,21 +2763,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800977</v>
+        <v>801003</v>
       </c>
       <c r="R21" t="n">
-        <v>7496685</v>
+        <v>7496768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2853,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259864</v>
+        <v>120259786</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,26 +2869,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2880,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801011</v>
+        <v>801231</v>
       </c>
       <c r="R22" t="n">
-        <v>7497112</v>
+        <v>7497243</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,13 +2939,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2943,10 +2968,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259852</v>
+        <v>120259827</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2959,26 +2984,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2986,10 +3016,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800990</v>
+        <v>800970</v>
       </c>
       <c r="R23" t="n">
-        <v>7496945</v>
+        <v>7496679</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,13 +3054,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3049,10 +3083,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259871</v>
+        <v>120259872</v>
       </c>
       <c r="B24" t="n">
-        <v>90975</v>
+        <v>90527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3061,25 +3095,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4217</v>
+        <v>112</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3155,10 +3189,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259822</v>
+        <v>120259842</v>
       </c>
       <c r="B25" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,21 +3205,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3198,10 +3232,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800977</v>
+        <v>800999</v>
       </c>
       <c r="R25" t="n">
-        <v>7496685</v>
+        <v>7496673</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3261,10 +3295,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259802</v>
+        <v>120259850</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3273,25 +3307,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3304,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>801083</v>
+        <v>800956</v>
       </c>
       <c r="R26" t="n">
-        <v>7497051</v>
+        <v>7496826</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,10 +3401,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259809</v>
+        <v>120259800</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3383,21 +3417,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3410,10 +3444,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801023</v>
+        <v>801083</v>
       </c>
       <c r="R27" t="n">
-        <v>7496816</v>
+        <v>7497051</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3473,10 +3507,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259878</v>
+        <v>120259822</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3489,21 +3523,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3516,10 +3550,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801127</v>
+        <v>800977</v>
       </c>
       <c r="R28" t="n">
-        <v>7497259</v>
+        <v>7496685</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3579,10 +3613,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120259777</v>
+        <v>120259874</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3595,21 +3629,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3622,10 +3656,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801236</v>
+        <v>801042</v>
       </c>
       <c r="R29" t="n">
-        <v>7497261</v>
+        <v>7497202</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3685,10 +3719,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120259863</v>
+        <v>120259871</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90975</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3697,35 +3731,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3733,10 +3762,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800990</v>
+        <v>801033</v>
       </c>
       <c r="R30" t="n">
-        <v>7497009</v>
+        <v>7497193</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3771,17 +3800,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3800,10 +3825,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259854</v>
+        <v>120259863</v>
       </c>
       <c r="B31" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,26 +3841,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3843,10 +3873,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800995</v>
+        <v>800990</v>
       </c>
       <c r="R31" t="n">
-        <v>7496971</v>
+        <v>7497009</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3881,13 +3911,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3906,10 +3940,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259838</v>
+        <v>120259793</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3922,21 +3956,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3949,10 +3983,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800964</v>
+        <v>801114</v>
       </c>
       <c r="R32" t="n">
-        <v>7496622</v>
+        <v>7497155</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4012,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259856</v>
+        <v>120259802</v>
       </c>
       <c r="B33" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4028,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4055,10 +4089,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801071</v>
+        <v>801083</v>
       </c>
       <c r="R33" t="n">
-        <v>7496976</v>
+        <v>7497051</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4118,7 +4152,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259801</v>
+        <v>120259795</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -4161,10 +4195,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801083</v>
+        <v>801088</v>
       </c>
       <c r="R34" t="n">
-        <v>7497051</v>
+        <v>7497114</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4224,10 +4258,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259855</v>
+        <v>120259857</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4240,26 +4274,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4267,10 +4310,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800995</v>
+        <v>801071</v>
       </c>
       <c r="R35" t="n">
-        <v>7496971</v>
+        <v>7496976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4311,7 +4354,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4330,10 +4372,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259857</v>
+        <v>120259851</v>
       </c>
       <c r="B36" t="n">
-        <v>56524</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4346,35 +4388,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4382,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801071</v>
+        <v>800967</v>
       </c>
       <c r="R36" t="n">
-        <v>7496976</v>
+        <v>7496843</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4426,6 +4459,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4444,10 +4478,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259818</v>
+        <v>120259875</v>
       </c>
       <c r="B37" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4456,39 +4490,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4496,10 +4521,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801003</v>
+        <v>801071</v>
       </c>
       <c r="R37" t="n">
-        <v>7496768</v>
+        <v>7497222</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4540,6 +4565,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4558,10 +4584,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259851</v>
+        <v>120259855</v>
       </c>
       <c r="B38" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4574,21 +4600,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4601,10 +4627,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800967</v>
+        <v>800995</v>
       </c>
       <c r="R38" t="n">
-        <v>7496843</v>
+        <v>7496971</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4690,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259792</v>
+        <v>120259804</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -4707,10 +4733,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801191</v>
+        <v>801070</v>
       </c>
       <c r="R39" t="n">
-        <v>7497171</v>
+        <v>7497010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4770,10 +4796,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259880</v>
+        <v>120259866</v>
       </c>
       <c r="B40" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4786,21 +4812,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4813,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801127</v>
+        <v>800977</v>
       </c>
       <c r="R40" t="n">
-        <v>7497259</v>
+        <v>7497131</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4876,10 +4902,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259804</v>
+        <v>120259854</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4892,21 +4918,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4919,10 +4945,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801070</v>
+        <v>800995</v>
       </c>
       <c r="R41" t="n">
-        <v>7497010</v>
+        <v>7496971</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4982,10 +5008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259808</v>
+        <v>120259840</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4998,31 +5024,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5030,10 +5051,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801023</v>
+        <v>800979</v>
       </c>
       <c r="R42" t="n">
-        <v>7496816</v>
+        <v>7496643</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5068,17 +5089,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5097,10 +5114,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259796</v>
+        <v>120259803</v>
       </c>
       <c r="B43" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5109,20 +5126,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5130,16 +5147,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5149,10 +5162,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801096</v>
+        <v>801068</v>
       </c>
       <c r="R43" t="n">
-        <v>7497061</v>
+        <v>7497037</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5185,6 +5198,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5211,10 +5229,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259805</v>
+        <v>120259808</v>
       </c>
       <c r="B44" t="n">
-        <v>78624</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5227,26 +5245,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5254,10 +5277,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801066</v>
+        <v>801023</v>
       </c>
       <c r="R44" t="n">
-        <v>7497007</v>
+        <v>7496816</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,13 +5315,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5317,10 +5344,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259786</v>
+        <v>120259792</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5333,31 +5360,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5365,10 +5387,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>801231</v>
+        <v>801191</v>
       </c>
       <c r="R45" t="n">
-        <v>7497243</v>
+        <v>7497171</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5403,17 +5425,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5432,10 +5450,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259799</v>
+        <v>120259838</v>
       </c>
       <c r="B46" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5448,21 +5466,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5475,10 +5493,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>801083</v>
+        <v>800964</v>
       </c>
       <c r="R46" t="n">
-        <v>7497051</v>
+        <v>7496622</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5538,10 +5556,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259866</v>
+        <v>120259852</v>
       </c>
       <c r="B47" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5554,21 +5572,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5581,10 +5599,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800977</v>
+        <v>800990</v>
       </c>
       <c r="R47" t="n">
-        <v>7497131</v>
+        <v>7496945</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5644,7 +5662,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259875</v>
+        <v>120259777</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -5687,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>801071</v>
+        <v>801236</v>
       </c>
       <c r="R48" t="n">
-        <v>7497222</v>
+        <v>7497261</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5750,10 +5768,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259842</v>
+        <v>120259805</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5766,21 +5784,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5793,10 +5811,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800999</v>
+        <v>801066</v>
       </c>
       <c r="R49" t="n">
-        <v>7496673</v>
+        <v>7497007</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5856,7 +5874,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259793</v>
+        <v>120259864</v>
       </c>
       <c r="B50" t="n">
         <v>90864</v>
@@ -5899,10 +5917,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>801114</v>
+        <v>801011</v>
       </c>
       <c r="R50" t="n">
-        <v>7497155</v>
+        <v>7497112</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5962,10 +5980,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259872</v>
+        <v>120259809</v>
       </c>
       <c r="B51" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5978,21 +5996,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6005,10 +6023,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>801033</v>
+        <v>801023</v>
       </c>
       <c r="R51" t="n">
-        <v>7497193</v>
+        <v>7496816</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6068,10 +6086,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259827</v>
+        <v>120259865</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6084,31 +6102,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6116,10 +6129,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800970</v>
+        <v>801011</v>
       </c>
       <c r="R52" t="n">
-        <v>7496679</v>
+        <v>7497112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6154,17 +6167,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6183,10 +6192,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259850</v>
+        <v>120259799</v>
       </c>
       <c r="B53" t="n">
-        <v>90545</v>
+        <v>90576</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6195,25 +6204,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6226,10 +6235,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800956</v>
+        <v>801083</v>
       </c>
       <c r="R53" t="n">
-        <v>7496826</v>
+        <v>7497051</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6289,10 +6298,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259859</v>
+        <v>120259794</v>
       </c>
       <c r="B54" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,26 +6314,31 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6332,10 +6346,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800998</v>
+        <v>801089</v>
       </c>
       <c r="R54" t="n">
-        <v>7497020</v>
+        <v>7497153</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6370,13 +6384,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6395,10 +6413,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259865</v>
+        <v>120259791</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6411,21 +6429,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6438,10 +6456,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801011</v>
+        <v>801191</v>
       </c>
       <c r="R55" t="n">
-        <v>7497112</v>
+        <v>7497194</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6501,10 +6519,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259814</v>
+        <v>120259878</v>
       </c>
       <c r="B56" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6517,21 +6535,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6544,10 +6562,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801003</v>
+        <v>801127</v>
       </c>
       <c r="R56" t="n">
-        <v>7496768</v>
+        <v>7497259</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6607,10 +6625,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259800</v>
+        <v>120259821</v>
       </c>
       <c r="B57" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6623,21 +6641,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6650,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801083</v>
+        <v>800977</v>
       </c>
       <c r="R57" t="n">
-        <v>7497051</v>
+        <v>7496685</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6819,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259803</v>
+        <v>120259867</v>
       </c>
       <c r="B59" t="n">
-        <v>57320</v>
+        <v>90934</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6831,35 +6849,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6867,10 +6880,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>801068</v>
+        <v>800977</v>
       </c>
       <c r="R59" t="n">
-        <v>7497037</v>
+        <v>7497131</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6905,17 +6918,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6934,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259794</v>
+        <v>120259859</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6950,31 +6959,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6982,10 +6986,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>801089</v>
+        <v>800998</v>
       </c>
       <c r="R60" t="n">
-        <v>7497153</v>
+        <v>7497020</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7020,17 +7024,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101064</v>
+        <v>120101230</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801077</v>
+        <v>800950</v>
       </c>
       <c r="R2" t="n">
-        <v>7497320</v>
+        <v>7497212</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101248</v>
+        <v>120101084</v>
       </c>
       <c r="B3" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800950</v>
+        <v>801019</v>
       </c>
       <c r="R3" t="n">
-        <v>7497212</v>
+        <v>7497303</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1001,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107790</v>
+        <v>120107773</v>
       </c>
       <c r="B5" t="n">
-        <v>57947</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,39 +1005,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800951</v>
+        <v>800947</v>
       </c>
       <c r="R5" t="n">
-        <v>7496943</v>
+        <v>7497009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,6 +1080,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107796</v>
+        <v>120101219</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>90934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800927</v>
+        <v>800950</v>
       </c>
       <c r="R6" t="n">
-        <v>7496884</v>
+        <v>7497212</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101230</v>
+        <v>120101138</v>
       </c>
       <c r="B7" t="n">
-        <v>90975</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,30 +1217,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800950</v>
+        <v>800993</v>
       </c>
       <c r="R7" t="n">
-        <v>7497212</v>
+        <v>7497292</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,13 +1291,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1327,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120101143</v>
+        <v>120107787</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,33 +1336,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1379,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800993</v>
+        <v>800951</v>
       </c>
       <c r="R8" t="n">
-        <v>7497292</v>
+        <v>7496943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1404,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101090</v>
+        <v>120101125</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1547,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101084</v>
+        <v>120101143</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,26 +1557,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801019</v>
+        <v>800993</v>
       </c>
       <c r="R10" t="n">
-        <v>7497303</v>
+        <v>7497292</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,7 +1637,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1653,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120101125</v>
+        <v>120107790</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,30 +1667,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1696,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801014</v>
+        <v>800951</v>
       </c>
       <c r="R11" t="n">
-        <v>7497308</v>
+        <v>7496943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1751,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101219</v>
+        <v>120107796</v>
       </c>
       <c r="B12" t="n">
-        <v>90934</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,25 +1781,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800950</v>
+        <v>800927</v>
       </c>
       <c r="R12" t="n">
-        <v>7497212</v>
+        <v>7496884</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101138</v>
+        <v>120101090</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90975</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,35 +1887,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1913,10 +1918,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800993</v>
+        <v>801014</v>
       </c>
       <c r="R13" t="n">
-        <v>7497292</v>
+        <v>7497308</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,17 +1956,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1980,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120107773</v>
+        <v>120101064</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2023,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800947</v>
+        <v>801077</v>
       </c>
       <c r="R14" t="n">
-        <v>7497009</v>
+        <v>7497320</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2086,10 +2087,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120107787</v>
+        <v>120101248</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>57431</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2098,20 +2099,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2119,12 +2120,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800951</v>
+        <v>800950</v>
       </c>
       <c r="R15" t="n">
-        <v>7496943</v>
+        <v>7497212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,11 +2175,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259818</v>
+        <v>120259801</v>
       </c>
       <c r="B16" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,39 +2213,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2253,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801003</v>
+        <v>801083</v>
       </c>
       <c r="R16" t="n">
-        <v>7496768</v>
+        <v>7497051</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,6 +2288,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2315,7 +2307,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259801</v>
+        <v>120259878</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2358,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801083</v>
+        <v>801127</v>
       </c>
       <c r="R17" t="n">
-        <v>7497051</v>
+        <v>7497259</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2421,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259880</v>
+        <v>120259872</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>90527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2437,21 +2429,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2464,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801127</v>
+        <v>801033</v>
       </c>
       <c r="R18" t="n">
-        <v>7497259</v>
+        <v>7497193</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259796</v>
+        <v>120259793</v>
       </c>
       <c r="B20" t="n">
-        <v>57431</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2645,39 +2637,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2685,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801096</v>
+        <v>801114</v>
       </c>
       <c r="R20" t="n">
-        <v>7497061</v>
+        <v>7497155</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2729,6 +2712,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2747,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259814</v>
+        <v>120259777</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2763,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2790,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801003</v>
+        <v>801236</v>
       </c>
       <c r="R21" t="n">
-        <v>7496768</v>
+        <v>7497261</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259786</v>
+        <v>120259855</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2869,31 +2853,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2901,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801231</v>
+        <v>800995</v>
       </c>
       <c r="R22" t="n">
-        <v>7497243</v>
+        <v>7496971</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2939,17 +2918,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2968,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259827</v>
+        <v>120259867</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90934</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2980,35 +2955,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3016,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800970</v>
+        <v>800977</v>
       </c>
       <c r="R23" t="n">
-        <v>7496679</v>
+        <v>7497131</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3054,17 +3024,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3083,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259872</v>
+        <v>120259864</v>
       </c>
       <c r="B24" t="n">
-        <v>90527</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3099,21 +3065,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3126,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801033</v>
+        <v>801011</v>
       </c>
       <c r="R24" t="n">
-        <v>7497193</v>
+        <v>7497112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3189,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259842</v>
+        <v>120259808</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3205,26 +3171,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3232,10 +3203,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800999</v>
+        <v>801023</v>
       </c>
       <c r="R25" t="n">
-        <v>7496673</v>
+        <v>7496816</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3270,13 +3241,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3295,10 +3270,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259850</v>
+        <v>120259809</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3307,25 +3282,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3338,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800956</v>
+        <v>801023</v>
       </c>
       <c r="R26" t="n">
-        <v>7496826</v>
+        <v>7496816</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3401,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259800</v>
+        <v>120259866</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3417,21 +3392,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3444,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801083</v>
+        <v>800977</v>
       </c>
       <c r="R27" t="n">
-        <v>7497051</v>
+        <v>7497131</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259822</v>
+        <v>120259789</v>
       </c>
       <c r="B28" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3523,21 +3498,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3550,10 +3525,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800977</v>
+        <v>801215</v>
       </c>
       <c r="R28" t="n">
-        <v>7496685</v>
+        <v>7497216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3613,10 +3588,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120259874</v>
+        <v>120259854</v>
       </c>
       <c r="B29" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3629,21 +3604,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3631,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801042</v>
+        <v>800995</v>
       </c>
       <c r="R29" t="n">
-        <v>7497202</v>
+        <v>7496971</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3719,10 +3694,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120259871</v>
+        <v>120259840</v>
       </c>
       <c r="B30" t="n">
-        <v>90975</v>
+        <v>90598</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3731,25 +3706,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4217</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3762,10 +3737,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>801033</v>
+        <v>800979</v>
       </c>
       <c r="R30" t="n">
-        <v>7497193</v>
+        <v>7496643</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3825,10 +3800,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259863</v>
+        <v>120259852</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3841,31 +3816,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3876,7 +3846,7 @@
         <v>800990</v>
       </c>
       <c r="R31" t="n">
-        <v>7497009</v>
+        <v>7496945</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3911,17 +3881,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3940,10 +3906,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259793</v>
+        <v>120259880</v>
       </c>
       <c r="B32" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,21 +3922,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3983,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801114</v>
+        <v>801127</v>
       </c>
       <c r="R32" t="n">
-        <v>7497155</v>
+        <v>7497259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4046,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259802</v>
+        <v>120259875</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,21 +4028,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4089,10 +4055,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801083</v>
+        <v>801071</v>
       </c>
       <c r="R33" t="n">
-        <v>7497051</v>
+        <v>7497222</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4152,10 +4118,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259795</v>
+        <v>120259786</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4168,26 +4134,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4195,10 +4166,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801088</v>
+        <v>801231</v>
       </c>
       <c r="R34" t="n">
-        <v>7497114</v>
+        <v>7497243</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,13 +4204,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259857</v>
+        <v>120259796</v>
       </c>
       <c r="B35" t="n">
-        <v>56524</v>
+        <v>57431</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4270,20 +4245,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>103031</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4293,7 +4268,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4310,10 +4285,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801071</v>
+        <v>801096</v>
       </c>
       <c r="R35" t="n">
-        <v>7496976</v>
+        <v>7497061</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4372,10 +4347,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259851</v>
+        <v>120259795</v>
       </c>
       <c r="B36" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4388,21 +4363,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4415,10 +4390,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800967</v>
+        <v>801088</v>
       </c>
       <c r="R36" t="n">
-        <v>7496843</v>
+        <v>7497114</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4478,10 +4453,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259875</v>
+        <v>120259857</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4494,26 +4469,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4524,7 +4508,7 @@
         <v>801071</v>
       </c>
       <c r="R37" t="n">
-        <v>7497222</v>
+        <v>7496976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4565,7 +4549,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4584,10 +4567,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259855</v>
+        <v>120259799</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4600,21 +4583,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4627,10 +4610,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800995</v>
+        <v>801083</v>
       </c>
       <c r="R38" t="n">
-        <v>7496971</v>
+        <v>7497051</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4690,10 +4673,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259804</v>
+        <v>120259850</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4702,25 +4685,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4733,10 +4716,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801070</v>
+        <v>800956</v>
       </c>
       <c r="R39" t="n">
-        <v>7497010</v>
+        <v>7496826</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4796,7 +4779,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259866</v>
+        <v>120259822</v>
       </c>
       <c r="B40" t="n">
         <v>90864</v>
@@ -4842,7 +4825,7 @@
         <v>800977</v>
       </c>
       <c r="R40" t="n">
-        <v>7497131</v>
+        <v>7496685</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4902,10 +4885,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259854</v>
+        <v>120259800</v>
       </c>
       <c r="B41" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4918,21 +4901,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4945,10 +4928,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800995</v>
+        <v>801083</v>
       </c>
       <c r="R41" t="n">
-        <v>7496971</v>
+        <v>7497051</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,10 +4991,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259840</v>
+        <v>120259863</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5024,26 +5007,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5051,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800979</v>
+        <v>800990</v>
       </c>
       <c r="R42" t="n">
-        <v>7496643</v>
+        <v>7497009</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5089,13 +5077,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5114,10 +5106,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259803</v>
+        <v>120259792</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5130,31 +5122,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5162,10 +5149,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801068</v>
+        <v>801191</v>
       </c>
       <c r="R43" t="n">
-        <v>7497037</v>
+        <v>7497171</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5200,17 +5187,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5229,10 +5212,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259808</v>
+        <v>120259804</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5245,31 +5228,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5277,10 +5255,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801023</v>
+        <v>801070</v>
       </c>
       <c r="R44" t="n">
-        <v>7496816</v>
+        <v>7497010</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5315,17 +5293,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5344,10 +5318,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259792</v>
+        <v>120259865</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5360,21 +5334,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5387,10 +5361,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>801191</v>
+        <v>801011</v>
       </c>
       <c r="R45" t="n">
-        <v>7497171</v>
+        <v>7497112</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5450,10 +5424,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259838</v>
+        <v>120259805</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>78624</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5466,21 +5440,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5493,10 +5467,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800964</v>
+        <v>801066</v>
       </c>
       <c r="R46" t="n">
-        <v>7496622</v>
+        <v>7497007</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5556,7 +5530,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259852</v>
+        <v>120259791</v>
       </c>
       <c r="B47" t="n">
         <v>90598</v>
@@ -5599,10 +5573,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800990</v>
+        <v>801191</v>
       </c>
       <c r="R47" t="n">
-        <v>7496945</v>
+        <v>7497194</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5662,10 +5636,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259777</v>
+        <v>120259818</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5674,30 +5648,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5705,10 +5688,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>801236</v>
+        <v>801003</v>
       </c>
       <c r="R48" t="n">
-        <v>7497261</v>
+        <v>7496768</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5749,7 +5732,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5768,10 +5750,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259805</v>
+        <v>120259794</v>
       </c>
       <c r="B49" t="n">
-        <v>78624</v>
+        <v>57320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5784,26 +5766,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5811,10 +5798,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>801066</v>
+        <v>801089</v>
       </c>
       <c r="R49" t="n">
-        <v>7497007</v>
+        <v>7497153</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5849,13 +5836,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5874,10 +5865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259864</v>
+        <v>120259838</v>
       </c>
       <c r="B50" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5890,21 +5881,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5917,10 +5908,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>801011</v>
+        <v>800964</v>
       </c>
       <c r="R50" t="n">
-        <v>7497112</v>
+        <v>7496622</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5980,7 +5971,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259809</v>
+        <v>120259842</v>
       </c>
       <c r="B51" t="n">
         <v>78542</v>
@@ -6023,10 +6014,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>801023</v>
+        <v>800999</v>
       </c>
       <c r="R51" t="n">
-        <v>7496816</v>
+        <v>7496673</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6086,10 +6077,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259865</v>
+        <v>120259851</v>
       </c>
       <c r="B52" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6102,21 +6093,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6129,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>801011</v>
+        <v>800967</v>
       </c>
       <c r="R52" t="n">
-        <v>7497112</v>
+        <v>7496843</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6192,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259799</v>
+        <v>120259859</v>
       </c>
       <c r="B53" t="n">
-        <v>90576</v>
+        <v>90864</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6208,21 +6199,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6235,10 +6226,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>801083</v>
+        <v>800998</v>
       </c>
       <c r="R53" t="n">
-        <v>7497051</v>
+        <v>7497020</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6298,10 +6289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259794</v>
+        <v>120259874</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6314,31 +6305,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6346,10 +6332,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>801089</v>
+        <v>801042</v>
       </c>
       <c r="R54" t="n">
-        <v>7497153</v>
+        <v>7497202</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6384,17 +6370,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6413,7 +6395,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259791</v>
+        <v>120259814</v>
       </c>
       <c r="B55" t="n">
         <v>90598</v>
@@ -6456,10 +6438,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801191</v>
+        <v>801003</v>
       </c>
       <c r="R55" t="n">
-        <v>7497194</v>
+        <v>7496768</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6519,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259878</v>
+        <v>120259803</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6535,26 +6517,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6562,10 +6549,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801127</v>
+        <v>801068</v>
       </c>
       <c r="R56" t="n">
-        <v>7497259</v>
+        <v>7497037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6600,13 +6587,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6625,10 +6616,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259821</v>
+        <v>120259827</v>
       </c>
       <c r="B57" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6641,26 +6632,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6668,10 +6664,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800977</v>
+        <v>800970</v>
       </c>
       <c r="R57" t="n">
-        <v>7496685</v>
+        <v>7496679</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6706,13 +6702,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259789</v>
+        <v>120259871</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6743,25 +6743,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>801215</v>
+        <v>801033</v>
       </c>
       <c r="R58" t="n">
-        <v>7497216</v>
+        <v>7497193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259867</v>
+        <v>120259802</v>
       </c>
       <c r="B59" t="n">
-        <v>90934</v>
+        <v>90580</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6849,25 +6849,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800977</v>
+        <v>801083</v>
       </c>
       <c r="R59" t="n">
-        <v>7497131</v>
+        <v>7497051</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259859</v>
+        <v>120259821</v>
       </c>
       <c r="B60" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800998</v>
+        <v>800977</v>
       </c>
       <c r="R60" t="n">
-        <v>7497020</v>
+        <v>7496685</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120107773</v>
+        <v>120101219</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90934</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800947</v>
+        <v>800950</v>
       </c>
       <c r="R5" t="n">
-        <v>7497009</v>
+        <v>7497212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101219</v>
+        <v>120107773</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800950</v>
+        <v>800947</v>
       </c>
       <c r="R6" t="n">
-        <v>7497212</v>
+        <v>7497009</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107787</v>
+        <v>120101125</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,31 +1336,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800951</v>
+        <v>801014</v>
       </c>
       <c r="R8" t="n">
-        <v>7496943</v>
+        <v>7497308</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,17 +1401,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1435,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101125</v>
+        <v>120107787</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,26 +1442,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1478,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801014</v>
+        <v>800951</v>
       </c>
       <c r="R9" t="n">
-        <v>7497308</v>
+        <v>7496943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,13 +1512,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259793</v>
+        <v>120259777</v>
       </c>
       <c r="B20" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801114</v>
+        <v>801236</v>
       </c>
       <c r="R20" t="n">
-        <v>7497155</v>
+        <v>7497261</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259777</v>
+        <v>120259855</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801236</v>
+        <v>800995</v>
       </c>
       <c r="R21" t="n">
-        <v>7497261</v>
+        <v>7496971</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259855</v>
+        <v>120259793</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800995</v>
+        <v>801114</v>
       </c>
       <c r="R22" t="n">
-        <v>7496971</v>
+        <v>7497155</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259880</v>
+        <v>120259875</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3922,21 +3922,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801127</v>
+        <v>801071</v>
       </c>
       <c r="R32" t="n">
-        <v>7497259</v>
+        <v>7497222</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4012,10 +4012,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259875</v>
+        <v>120259786</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4028,26 +4028,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4055,10 +4060,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801071</v>
+        <v>801231</v>
       </c>
       <c r="R33" t="n">
-        <v>7497222</v>
+        <v>7497243</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4093,13 +4098,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4118,10 +4127,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259786</v>
+        <v>120259880</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4134,31 +4143,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4166,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801231</v>
+        <v>801127</v>
       </c>
       <c r="R34" t="n">
-        <v>7497243</v>
+        <v>7497259</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4204,17 +4208,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259857</v>
+        <v>120259799</v>
       </c>
       <c r="B37" t="n">
-        <v>56524</v>
+        <v>90576</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,35 +4469,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4505,10 +4496,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801071</v>
+        <v>801083</v>
       </c>
       <c r="R37" t="n">
-        <v>7496976</v>
+        <v>7497051</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4549,6 +4540,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4567,10 +4559,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259799</v>
+        <v>120259850</v>
       </c>
       <c r="B38" t="n">
-        <v>90576</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4579,25 +4571,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4610,10 +4602,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>801083</v>
+        <v>800956</v>
       </c>
       <c r="R38" t="n">
-        <v>7497051</v>
+        <v>7496826</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4673,10 +4665,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259850</v>
+        <v>120259857</v>
       </c>
       <c r="B39" t="n">
-        <v>90545</v>
+        <v>56524</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4685,30 +4677,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4716,10 +4717,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800956</v>
+        <v>801071</v>
       </c>
       <c r="R39" t="n">
-        <v>7496826</v>
+        <v>7496976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4760,7 +4761,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -6077,10 +6077,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259851</v>
+        <v>120259871</v>
       </c>
       <c r="B52" t="n">
-        <v>90576</v>
+        <v>90975</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6089,25 +6089,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>4217</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800967</v>
+        <v>801033</v>
       </c>
       <c r="R52" t="n">
-        <v>7496843</v>
+        <v>7497193</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6183,10 +6183,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259859</v>
+        <v>120259851</v>
       </c>
       <c r="B53" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6226,10 +6226,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800998</v>
+        <v>800967</v>
       </c>
       <c r="R53" t="n">
-        <v>7497020</v>
+        <v>7496843</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6289,10 +6289,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259874</v>
+        <v>120259859</v>
       </c>
       <c r="B54" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6305,21 +6305,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>801042</v>
+        <v>800998</v>
       </c>
       <c r="R54" t="n">
-        <v>7497202</v>
+        <v>7497020</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6395,7 +6395,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259814</v>
+        <v>120259874</v>
       </c>
       <c r="B55" t="n">
         <v>90598</v>
@@ -6438,10 +6438,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801003</v>
+        <v>801042</v>
       </c>
       <c r="R55" t="n">
-        <v>7496768</v>
+        <v>7497202</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6501,10 +6501,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259803</v>
+        <v>120259814</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6517,31 +6517,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6549,10 +6544,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801068</v>
+        <v>801003</v>
       </c>
       <c r="R56" t="n">
-        <v>7497037</v>
+        <v>7496768</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6587,17 +6582,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6616,7 +6607,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259827</v>
+        <v>120259803</v>
       </c>
       <c r="B57" t="n">
         <v>57320</v>
@@ -6664,10 +6655,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800970</v>
+        <v>801068</v>
       </c>
       <c r="R57" t="n">
-        <v>7496679</v>
+        <v>7497037</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6731,10 +6722,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259871</v>
+        <v>120259827</v>
       </c>
       <c r="B58" t="n">
-        <v>90975</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6743,30 +6734,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6774,10 +6770,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>801033</v>
+        <v>800970</v>
       </c>
       <c r="R58" t="n">
-        <v>7497193</v>
+        <v>7496679</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6812,13 +6808,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120101230</v>
+        <v>120107773</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800950</v>
+        <v>800947</v>
       </c>
       <c r="R2" t="n">
-        <v>7497212</v>
+        <v>7497009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101084</v>
+        <v>120101138</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801019</v>
+        <v>800993</v>
       </c>
       <c r="R3" t="n">
-        <v>7497303</v>
+        <v>7497292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,13 +867,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120101206</v>
+        <v>120107787</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +912,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801001</v>
+        <v>800951</v>
       </c>
       <c r="R4" t="n">
-        <v>7497266</v>
+        <v>7496943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,13 +982,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101219</v>
+        <v>120101064</v>
       </c>
       <c r="B5" t="n">
-        <v>90934</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800950</v>
+        <v>801077</v>
       </c>
       <c r="R5" t="n">
-        <v>7497212</v>
+        <v>7497320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120107773</v>
+        <v>120101248</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,30 +1129,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800947</v>
+        <v>800950</v>
       </c>
       <c r="R6" t="n">
-        <v>7497009</v>
+        <v>7497212</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1213,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101138</v>
+        <v>120101143</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,29 +1247,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1289,11 +1319,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120101125</v>
+        <v>120101090</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,25 +1357,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120107787</v>
+        <v>120101125</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,31 +1467,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800951</v>
+        <v>801014</v>
       </c>
       <c r="R9" t="n">
-        <v>7496943</v>
+        <v>7497308</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,17 +1532,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1541,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101143</v>
+        <v>120101206</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,35 +1573,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1593,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800993</v>
+        <v>801001</v>
       </c>
       <c r="R10" t="n">
-        <v>7497292</v>
+        <v>7497266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,6 +1644,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120107796</v>
+        <v>120101230</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>90975</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,25 +1789,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800927</v>
+        <v>800950</v>
       </c>
       <c r="R12" t="n">
-        <v>7496884</v>
+        <v>7497212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1875,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101090</v>
+        <v>120101219</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>90934</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,25 +1895,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>1506</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1918,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801014</v>
+        <v>800950</v>
       </c>
       <c r="R13" t="n">
-        <v>7497308</v>
+        <v>7497212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120101064</v>
+        <v>120107796</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1997,21 +2005,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2024,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801077</v>
+        <v>800927</v>
       </c>
       <c r="R14" t="n">
-        <v>7497320</v>
+        <v>7496884</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2087,10 +2095,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101248</v>
+        <v>120101084</v>
       </c>
       <c r="B15" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,39 +2107,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2139,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800950</v>
+        <v>801019</v>
       </c>
       <c r="R15" t="n">
-        <v>7497212</v>
+        <v>7497303</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,6 +2182,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259801</v>
+        <v>120259840</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,21 +2217,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>801083</v>
+        <v>800979</v>
       </c>
       <c r="R16" t="n">
-        <v>7497051</v>
+        <v>7496643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259878</v>
+        <v>120259791</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801127</v>
+        <v>801191</v>
       </c>
       <c r="R17" t="n">
-        <v>7497259</v>
+        <v>7497194</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259872</v>
+        <v>120259856</v>
       </c>
       <c r="B18" t="n">
-        <v>90527</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,21 +2429,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801033</v>
+        <v>801071</v>
       </c>
       <c r="R18" t="n">
-        <v>7497193</v>
+        <v>7496976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259856</v>
+        <v>120259872</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>90527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801071</v>
+        <v>801033</v>
       </c>
       <c r="R19" t="n">
-        <v>7496976</v>
+        <v>7497193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259777</v>
+        <v>120259865</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801236</v>
+        <v>801011</v>
       </c>
       <c r="R20" t="n">
-        <v>7497261</v>
+        <v>7497112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259855</v>
+        <v>120259864</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,21 +2747,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800995</v>
+        <v>801011</v>
       </c>
       <c r="R21" t="n">
-        <v>7496971</v>
+        <v>7497112</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259793</v>
+        <v>120259855</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>801114</v>
+        <v>800995</v>
       </c>
       <c r="R22" t="n">
-        <v>7497155</v>
+        <v>7496971</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259867</v>
+        <v>120259796</v>
       </c>
       <c r="B23" t="n">
-        <v>90934</v>
+        <v>57431</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2955,30 +2955,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2986,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800977</v>
+        <v>801096</v>
       </c>
       <c r="R23" t="n">
-        <v>7497131</v>
+        <v>7497061</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,7 +3039,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3049,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259864</v>
+        <v>120259854</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3065,21 +3073,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3092,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801011</v>
+        <v>800995</v>
       </c>
       <c r="R24" t="n">
-        <v>7497112</v>
+        <v>7496971</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259808</v>
+        <v>120259850</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,35 +3175,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3203,10 +3206,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>801023</v>
+        <v>800956</v>
       </c>
       <c r="R25" t="n">
-        <v>7496816</v>
+        <v>7496826</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3241,17 +3244,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3270,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259809</v>
+        <v>120259859</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,21 +3285,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3313,10 +3312,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>801023</v>
+        <v>800998</v>
       </c>
       <c r="R26" t="n">
-        <v>7496816</v>
+        <v>7497020</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3376,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259866</v>
+        <v>120259878</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3392,21 +3391,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3419,10 +3418,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800977</v>
+        <v>801127</v>
       </c>
       <c r="R27" t="n">
-        <v>7497131</v>
+        <v>7497259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259789</v>
+        <v>120259808</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,26 +3497,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3525,10 +3529,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801215</v>
+        <v>801023</v>
       </c>
       <c r="R28" t="n">
-        <v>7497216</v>
+        <v>7496816</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,13 +3567,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3588,10 +3596,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120259854</v>
+        <v>120259786</v>
       </c>
       <c r="B29" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,26 +3612,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3631,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800995</v>
+        <v>801231</v>
       </c>
       <c r="R29" t="n">
-        <v>7496971</v>
+        <v>7497243</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,13 +3682,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3694,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120259840</v>
+        <v>120259863</v>
       </c>
       <c r="B30" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,26 +3727,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3737,10 +3759,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800979</v>
+        <v>800990</v>
       </c>
       <c r="R30" t="n">
-        <v>7496643</v>
+        <v>7497009</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3775,13 +3797,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3800,10 +3826,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259852</v>
+        <v>120259821</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,21 +3842,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3843,10 +3869,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800990</v>
+        <v>800977</v>
       </c>
       <c r="R31" t="n">
-        <v>7496945</v>
+        <v>7496685</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3906,10 +3932,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259875</v>
+        <v>120259800</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3922,21 +3948,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3949,10 +3975,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801071</v>
+        <v>801083</v>
       </c>
       <c r="R32" t="n">
-        <v>7497222</v>
+        <v>7497051</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4012,10 +4038,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259786</v>
+        <v>120259795</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4028,31 +4054,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4060,10 +4081,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801231</v>
+        <v>801088</v>
       </c>
       <c r="R33" t="n">
-        <v>7497243</v>
+        <v>7497114</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4098,17 +4119,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4127,10 +4144,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259880</v>
+        <v>120259792</v>
       </c>
       <c r="B34" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,21 +4160,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4170,10 +4187,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801127</v>
+        <v>801191</v>
       </c>
       <c r="R34" t="n">
-        <v>7497259</v>
+        <v>7497171</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259796</v>
+        <v>120259857</v>
       </c>
       <c r="B35" t="n">
-        <v>57431</v>
+        <v>56524</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4245,20 +4262,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4268,7 +4285,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4285,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801096</v>
+        <v>801071</v>
       </c>
       <c r="R35" t="n">
-        <v>7497061</v>
+        <v>7496976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4347,10 +4364,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259795</v>
+        <v>120259874</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4363,21 +4380,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4390,10 +4407,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801088</v>
+        <v>801042</v>
       </c>
       <c r="R36" t="n">
-        <v>7497114</v>
+        <v>7497202</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4453,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259799</v>
+        <v>120259842</v>
       </c>
       <c r="B37" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4469,21 +4486,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4496,10 +4513,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>801083</v>
+        <v>800999</v>
       </c>
       <c r="R37" t="n">
-        <v>7497051</v>
+        <v>7496673</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4559,10 +4576,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259850</v>
+        <v>120259822</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4571,25 +4588,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4602,10 +4619,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800956</v>
+        <v>800977</v>
       </c>
       <c r="R38" t="n">
-        <v>7496826</v>
+        <v>7496685</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4665,10 +4682,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259857</v>
+        <v>120259799</v>
       </c>
       <c r="B39" t="n">
-        <v>56524</v>
+        <v>90576</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4681,35 +4698,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4717,10 +4725,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801071</v>
+        <v>801083</v>
       </c>
       <c r="R39" t="n">
-        <v>7496976</v>
+        <v>7497051</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4761,6 +4769,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4779,7 +4788,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259822</v>
+        <v>120259866</v>
       </c>
       <c r="B40" t="n">
         <v>90864</v>
@@ -4825,7 +4834,7 @@
         <v>800977</v>
       </c>
       <c r="R40" t="n">
-        <v>7496685</v>
+        <v>7497131</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4885,10 +4894,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259800</v>
+        <v>120259818</v>
       </c>
       <c r="B41" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4897,30 +4906,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4928,10 +4946,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801083</v>
+        <v>801003</v>
       </c>
       <c r="R41" t="n">
-        <v>7497051</v>
+        <v>7496768</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4972,7 +4990,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4991,10 +5008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259863</v>
+        <v>120259802</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5007,31 +5024,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5039,10 +5051,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800990</v>
+        <v>801083</v>
       </c>
       <c r="R42" t="n">
-        <v>7497009</v>
+        <v>7497051</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5077,17 +5089,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5106,7 +5114,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259792</v>
+        <v>120259875</v>
       </c>
       <c r="B43" t="n">
         <v>78542</v>
@@ -5149,10 +5157,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801191</v>
+        <v>801071</v>
       </c>
       <c r="R43" t="n">
-        <v>7497171</v>
+        <v>7497222</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5212,10 +5220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259804</v>
+        <v>120259794</v>
       </c>
       <c r="B44" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5228,26 +5236,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5255,10 +5268,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801070</v>
+        <v>801089</v>
       </c>
       <c r="R44" t="n">
-        <v>7497010</v>
+        <v>7497153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5293,13 +5306,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5318,10 +5335,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259865</v>
+        <v>120259809</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5334,21 +5351,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5361,10 +5378,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>801011</v>
+        <v>801023</v>
       </c>
       <c r="R45" t="n">
-        <v>7497112</v>
+        <v>7496816</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5424,10 +5441,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259805</v>
+        <v>120259801</v>
       </c>
       <c r="B46" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5440,21 +5457,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5467,10 +5484,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>801066</v>
+        <v>801083</v>
       </c>
       <c r="R46" t="n">
-        <v>7497007</v>
+        <v>7497051</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,10 +5547,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259791</v>
+        <v>120259851</v>
       </c>
       <c r="B47" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5546,21 +5563,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5573,10 +5590,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>801191</v>
+        <v>800967</v>
       </c>
       <c r="R47" t="n">
-        <v>7497194</v>
+        <v>7496843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5636,10 +5653,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259818</v>
+        <v>120259814</v>
       </c>
       <c r="B48" t="n">
-        <v>57431</v>
+        <v>90598</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5648,39 +5665,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5732,6 +5740,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5750,10 +5759,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259794</v>
+        <v>120259805</v>
       </c>
       <c r="B49" t="n">
-        <v>57320</v>
+        <v>78624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5766,31 +5775,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5798,10 +5802,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>801089</v>
+        <v>801066</v>
       </c>
       <c r="R49" t="n">
-        <v>7497153</v>
+        <v>7497007</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5836,17 +5840,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259838</v>
+        <v>120259880</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5881,21 +5881,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800964</v>
+        <v>801127</v>
       </c>
       <c r="R50" t="n">
-        <v>7496622</v>
+        <v>7497259</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5971,10 +5971,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259842</v>
+        <v>120259803</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5987,26 +5987,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800999</v>
+        <v>801068</v>
       </c>
       <c r="R51" t="n">
-        <v>7496673</v>
+        <v>7497037</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6052,13 +6057,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6077,10 +6086,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259871</v>
+        <v>120259827</v>
       </c>
       <c r="B52" t="n">
-        <v>90975</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6089,30 +6098,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6120,10 +6134,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>801033</v>
+        <v>800970</v>
       </c>
       <c r="R52" t="n">
-        <v>7497193</v>
+        <v>7496679</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6158,13 +6172,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6183,10 +6201,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259851</v>
+        <v>120259804</v>
       </c>
       <c r="B53" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6199,21 +6217,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6226,10 +6244,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800967</v>
+        <v>801070</v>
       </c>
       <c r="R53" t="n">
-        <v>7496843</v>
+        <v>7497010</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6289,7 +6307,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259859</v>
+        <v>120259793</v>
       </c>
       <c r="B54" t="n">
         <v>90864</v>
@@ -6332,10 +6350,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800998</v>
+        <v>801114</v>
       </c>
       <c r="R54" t="n">
-        <v>7497020</v>
+        <v>7497155</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6395,10 +6413,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259874</v>
+        <v>120259871</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>90975</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6407,25 +6425,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6438,10 +6456,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801042</v>
+        <v>801033</v>
       </c>
       <c r="R55" t="n">
-        <v>7497202</v>
+        <v>7497193</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6501,10 +6519,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259814</v>
+        <v>120259867</v>
       </c>
       <c r="B56" t="n">
-        <v>90598</v>
+        <v>90934</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6513,25 +6531,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6544,10 +6562,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801003</v>
+        <v>800977</v>
       </c>
       <c r="R56" t="n">
-        <v>7496768</v>
+        <v>7497131</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6607,10 +6625,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259803</v>
+        <v>120259852</v>
       </c>
       <c r="B57" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6623,31 +6641,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6655,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801068</v>
+        <v>800990</v>
       </c>
       <c r="R57" t="n">
-        <v>7497037</v>
+        <v>7496945</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6693,17 +6706,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6722,10 +6731,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259827</v>
+        <v>120259789</v>
       </c>
       <c r="B58" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6738,31 +6747,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6770,10 +6774,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800970</v>
+        <v>801215</v>
       </c>
       <c r="R58" t="n">
-        <v>7496679</v>
+        <v>7497216</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6808,17 +6812,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259802</v>
+        <v>120259777</v>
       </c>
       <c r="B59" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6853,21 +6853,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>801083</v>
+        <v>801236</v>
       </c>
       <c r="R59" t="n">
-        <v>7497051</v>
+        <v>7497261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259821</v>
+        <v>120259838</v>
       </c>
       <c r="B60" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6959,21 +6959,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800977</v>
+        <v>800964</v>
       </c>
       <c r="R60" t="n">
-        <v>7496685</v>
+        <v>7496622</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120107773</v>
+        <v>120101064</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800947</v>
+        <v>801077</v>
       </c>
       <c r="R2" t="n">
-        <v>7497009</v>
+        <v>7497320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120101138</v>
+        <v>120101230</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,35 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800993</v>
+        <v>800950</v>
       </c>
       <c r="R3" t="n">
-        <v>7497292</v>
+        <v>7497212</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,17 +862,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120107787</v>
+        <v>120101219</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90934</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +899,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800951</v>
+        <v>800950</v>
       </c>
       <c r="R4" t="n">
-        <v>7496943</v>
+        <v>7497212</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,17 +968,13 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120101064</v>
+        <v>120101248</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,30 +1005,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801077</v>
+        <v>800950</v>
       </c>
       <c r="R5" t="n">
-        <v>7497320</v>
+        <v>7497212</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120101248</v>
+        <v>120107790</v>
       </c>
       <c r="B6" t="n">
-        <v>57431</v>
+        <v>57947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,20 +1119,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>102125</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1152,14 +1142,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1169,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800950</v>
+        <v>800951</v>
       </c>
       <c r="R6" t="n">
-        <v>7497212</v>
+        <v>7496943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120101143</v>
+        <v>120101138</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,33 +1237,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1319,6 +1305,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120101090</v>
+        <v>120107787</v>
       </c>
       <c r="B8" t="n">
-        <v>90975</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,30 +1348,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801014</v>
+        <v>800951</v>
       </c>
       <c r="R8" t="n">
-        <v>7497308</v>
+        <v>7496943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1426,13 +1422,17 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101125</v>
+        <v>120101143</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,26 +1467,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1494,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801014</v>
+        <v>800993</v>
       </c>
       <c r="R9" t="n">
-        <v>7497308</v>
+        <v>7497292</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,7 +1547,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120101206</v>
+        <v>120107773</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1600,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801001</v>
+        <v>800947</v>
       </c>
       <c r="R10" t="n">
-        <v>7497266</v>
+        <v>7497009</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120107790</v>
+        <v>120107796</v>
       </c>
       <c r="B11" t="n">
-        <v>57947</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,39 +1683,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102125</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1715,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800951</v>
+        <v>800927</v>
       </c>
       <c r="R11" t="n">
-        <v>7496943</v>
+        <v>7496884</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1759,6 +1758,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120101230</v>
+        <v>120101084</v>
       </c>
       <c r="B12" t="n">
-        <v>90975</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,25 +1789,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800950</v>
+        <v>801019</v>
       </c>
       <c r="R12" t="n">
-        <v>7497212</v>
+        <v>7497303</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,10 +1883,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120101219</v>
+        <v>120101206</v>
       </c>
       <c r="B13" t="n">
-        <v>90934</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1895,25 +1895,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800950</v>
+        <v>801001</v>
       </c>
       <c r="R13" t="n">
-        <v>7497212</v>
+        <v>7497266</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120107796</v>
+        <v>120101090</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>90975</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,25 +2001,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800927</v>
+        <v>801014</v>
       </c>
       <c r="R14" t="n">
-        <v>7496884</v>
+        <v>7497308</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120101084</v>
+        <v>120101125</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801019</v>
+        <v>801014</v>
       </c>
       <c r="R15" t="n">
-        <v>7497303</v>
+        <v>7497308</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120259840</v>
+        <v>120259805</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>78624</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,21 +2217,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800979</v>
+        <v>801066</v>
       </c>
       <c r="R16" t="n">
-        <v>7496643</v>
+        <v>7497007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120259791</v>
+        <v>120259802</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>801191</v>
+        <v>801083</v>
       </c>
       <c r="R17" t="n">
-        <v>7497194</v>
+        <v>7497051</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120259856</v>
+        <v>120259852</v>
       </c>
       <c r="B18" t="n">
         <v>90598</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801071</v>
+        <v>800990</v>
       </c>
       <c r="R18" t="n">
-        <v>7496976</v>
+        <v>7496945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120259872</v>
+        <v>120259842</v>
       </c>
       <c r="B19" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>801033</v>
+        <v>800999</v>
       </c>
       <c r="R19" t="n">
-        <v>7497193</v>
+        <v>7496673</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259865</v>
+        <v>120259822</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2641,21 +2641,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>801011</v>
+        <v>800977</v>
       </c>
       <c r="R20" t="n">
-        <v>7497112</v>
+        <v>7496685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259864</v>
+        <v>120259867</v>
       </c>
       <c r="B21" t="n">
-        <v>90864</v>
+        <v>90934</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,25 +2743,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801011</v>
+        <v>800977</v>
       </c>
       <c r="R21" t="n">
-        <v>7497112</v>
+        <v>7497131</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120259855</v>
+        <v>120259789</v>
       </c>
       <c r="B22" t="n">
         <v>78542</v>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800995</v>
+        <v>801215</v>
       </c>
       <c r="R22" t="n">
-        <v>7496971</v>
+        <v>7497216</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259796</v>
+        <v>120259808</v>
       </c>
       <c r="B23" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2955,20 +2955,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2976,16 +2976,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2995,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801096</v>
+        <v>801023</v>
       </c>
       <c r="R23" t="n">
-        <v>7497061</v>
+        <v>7496816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3031,6 +3027,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259854</v>
+        <v>120259864</v>
       </c>
       <c r="B24" t="n">
-        <v>90576</v>
+        <v>90864</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3073,21 +3074,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800995</v>
+        <v>801011</v>
       </c>
       <c r="R24" t="n">
-        <v>7496971</v>
+        <v>7497112</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3163,10 +3164,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120259850</v>
+        <v>120259854</v>
       </c>
       <c r="B25" t="n">
-        <v>90545</v>
+        <v>90576</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3175,25 +3176,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3206,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800956</v>
+        <v>800995</v>
       </c>
       <c r="R25" t="n">
-        <v>7496826</v>
+        <v>7496971</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3269,10 +3270,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120259859</v>
+        <v>120259799</v>
       </c>
       <c r="B26" t="n">
-        <v>90864</v>
+        <v>90576</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3285,21 +3286,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3312,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800998</v>
+        <v>801083</v>
       </c>
       <c r="R26" t="n">
-        <v>7497020</v>
+        <v>7497051</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,10 +3376,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259878</v>
+        <v>120259814</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,21 +3392,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3418,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801127</v>
+        <v>801003</v>
       </c>
       <c r="R27" t="n">
-        <v>7497259</v>
+        <v>7496768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3481,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120259808</v>
+        <v>120259856</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,31 +3498,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3529,10 +3525,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>801023</v>
+        <v>801071</v>
       </c>
       <c r="R28" t="n">
-        <v>7496816</v>
+        <v>7496976</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3567,17 +3563,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3596,7 +3588,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120259786</v>
+        <v>120259794</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>801231</v>
+        <v>801089</v>
       </c>
       <c r="R29" t="n">
-        <v>7497243</v>
+        <v>7497153</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120259863</v>
+        <v>120259801</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,31 +3719,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3759,10 +3746,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800990</v>
+        <v>801083</v>
       </c>
       <c r="R30" t="n">
-        <v>7497009</v>
+        <v>7497051</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3797,17 +3784,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3826,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120259821</v>
+        <v>120259838</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3842,21 +3825,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3869,10 +3852,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800977</v>
+        <v>800964</v>
       </c>
       <c r="R31" t="n">
-        <v>7496685</v>
+        <v>7496622</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3932,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120259800</v>
+        <v>120259855</v>
       </c>
       <c r="B32" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3948,21 +3931,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3975,10 +3958,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>801083</v>
+        <v>800995</v>
       </c>
       <c r="R32" t="n">
-        <v>7497051</v>
+        <v>7496971</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4038,10 +4021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120259795</v>
+        <v>120259880</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4054,21 +4037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4081,10 +4064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>801088</v>
+        <v>801127</v>
       </c>
       <c r="R33" t="n">
-        <v>7497114</v>
+        <v>7497259</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4144,7 +4127,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259792</v>
+        <v>120259777</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -4187,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801191</v>
+        <v>801236</v>
       </c>
       <c r="R34" t="n">
-        <v>7497171</v>
+        <v>7497261</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259857</v>
+        <v>120259872</v>
       </c>
       <c r="B35" t="n">
-        <v>56524</v>
+        <v>90527</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4266,35 +4249,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>112</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4302,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801071</v>
+        <v>801033</v>
       </c>
       <c r="R35" t="n">
-        <v>7496976</v>
+        <v>7497193</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4346,6 +4320,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4364,10 +4339,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120259874</v>
+        <v>120259851</v>
       </c>
       <c r="B36" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4380,21 +4355,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4407,10 +4382,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>801042</v>
+        <v>800967</v>
       </c>
       <c r="R36" t="n">
-        <v>7497202</v>
+        <v>7496843</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4470,10 +4445,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120259842</v>
+        <v>120259871</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90975</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4482,25 +4457,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4513,10 +4488,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800999</v>
+        <v>801033</v>
       </c>
       <c r="R37" t="n">
-        <v>7496673</v>
+        <v>7497193</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4576,10 +4551,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120259822</v>
+        <v>120259804</v>
       </c>
       <c r="B38" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4592,21 +4567,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4619,10 +4594,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800977</v>
+        <v>801070</v>
       </c>
       <c r="R38" t="n">
-        <v>7496685</v>
+        <v>7497010</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4682,10 +4657,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259799</v>
+        <v>120259850</v>
       </c>
       <c r="B39" t="n">
-        <v>90576</v>
+        <v>90545</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4694,25 +4669,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4725,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>801083</v>
+        <v>800956</v>
       </c>
       <c r="R39" t="n">
-        <v>7497051</v>
+        <v>7496826</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4788,7 +4763,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259866</v>
+        <v>120259793</v>
       </c>
       <c r="B40" t="n">
         <v>90864</v>
@@ -4831,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800977</v>
+        <v>801114</v>
       </c>
       <c r="R40" t="n">
-        <v>7497131</v>
+        <v>7497155</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4894,10 +4869,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120259818</v>
+        <v>120259857</v>
       </c>
       <c r="B41" t="n">
-        <v>57431</v>
+        <v>56524</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4906,20 +4881,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4929,14 +4904,14 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4946,10 +4921,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>801003</v>
+        <v>801071</v>
       </c>
       <c r="R41" t="n">
-        <v>7496768</v>
+        <v>7496976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5008,7 +4983,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120259802</v>
+        <v>120259865</v>
       </c>
       <c r="B42" t="n">
         <v>90580</v>
@@ -5051,10 +5026,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>801083</v>
+        <v>801011</v>
       </c>
       <c r="R42" t="n">
-        <v>7497051</v>
+        <v>7497112</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5114,10 +5089,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120259875</v>
+        <v>120259786</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5130,26 +5105,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5157,10 +5137,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>801071</v>
+        <v>801231</v>
       </c>
       <c r="R43" t="n">
-        <v>7497222</v>
+        <v>7497243</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,13 +5175,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5220,7 +5204,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259794</v>
+        <v>120259863</v>
       </c>
       <c r="B44" t="n">
         <v>57320</v>
@@ -5268,10 +5252,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>801089</v>
+        <v>800990</v>
       </c>
       <c r="R44" t="n">
-        <v>7497153</v>
+        <v>7497009</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5308,7 +5292,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5335,10 +5319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259809</v>
+        <v>120259840</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5351,21 +5335,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5378,10 +5362,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>801023</v>
+        <v>800979</v>
       </c>
       <c r="R45" t="n">
-        <v>7496816</v>
+        <v>7496643</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5441,10 +5425,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120259801</v>
+        <v>120259827</v>
       </c>
       <c r="B46" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5457,26 +5441,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5484,10 +5473,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>801083</v>
+        <v>800970</v>
       </c>
       <c r="R46" t="n">
-        <v>7497051</v>
+        <v>7496679</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5522,13 +5511,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5547,10 +5540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120259851</v>
+        <v>120259875</v>
       </c>
       <c r="B47" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5563,21 +5556,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5590,10 +5583,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800967</v>
+        <v>801071</v>
       </c>
       <c r="R47" t="n">
-        <v>7496843</v>
+        <v>7497222</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5653,10 +5646,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120259814</v>
+        <v>120259818</v>
       </c>
       <c r="B48" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5665,30 +5658,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5740,7 +5742,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5759,10 +5760,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120259805</v>
+        <v>120259792</v>
       </c>
       <c r="B49" t="n">
-        <v>78624</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5775,21 +5776,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5802,10 +5803,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>801066</v>
+        <v>801191</v>
       </c>
       <c r="R49" t="n">
-        <v>7497007</v>
+        <v>7497171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5865,10 +5866,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120259880</v>
+        <v>120259859</v>
       </c>
       <c r="B50" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5881,21 +5882,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5908,10 +5909,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>801127</v>
+        <v>800998</v>
       </c>
       <c r="R50" t="n">
-        <v>7497259</v>
+        <v>7497020</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5971,10 +5972,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120259803</v>
+        <v>120259800</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5987,31 +5988,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6019,10 +6015,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>801068</v>
+        <v>801083</v>
       </c>
       <c r="R51" t="n">
-        <v>7497037</v>
+        <v>7497051</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6057,17 +6053,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6086,10 +6078,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120259827</v>
+        <v>120259795</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6102,31 +6094,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6134,10 +6121,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800970</v>
+        <v>801088</v>
       </c>
       <c r="R52" t="n">
-        <v>7496679</v>
+        <v>7497114</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6172,17 +6159,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6201,10 +6184,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259804</v>
+        <v>120259803</v>
       </c>
       <c r="B53" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6217,26 +6200,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6244,10 +6232,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>801070</v>
+        <v>801068</v>
       </c>
       <c r="R53" t="n">
-        <v>7497010</v>
+        <v>7497037</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6282,13 +6270,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6307,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259793</v>
+        <v>120259821</v>
       </c>
       <c r="B54" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6323,21 +6315,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6350,10 +6342,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>801114</v>
+        <v>800977</v>
       </c>
       <c r="R54" t="n">
-        <v>7497155</v>
+        <v>7496685</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6413,10 +6405,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259871</v>
+        <v>120259874</v>
       </c>
       <c r="B55" t="n">
-        <v>90975</v>
+        <v>90598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6425,25 +6417,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4217</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6456,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801033</v>
+        <v>801042</v>
       </c>
       <c r="R55" t="n">
-        <v>7497193</v>
+        <v>7497202</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6519,10 +6511,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259867</v>
+        <v>120259796</v>
       </c>
       <c r="B56" t="n">
-        <v>90934</v>
+        <v>57431</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6531,30 +6523,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1506</v>
+        <v>103031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6562,10 +6563,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800977</v>
+        <v>801096</v>
       </c>
       <c r="R56" t="n">
-        <v>7497131</v>
+        <v>7497061</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6606,7 +6607,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6625,10 +6625,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259852</v>
+        <v>120259878</v>
       </c>
       <c r="B57" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6641,21 +6641,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800990</v>
+        <v>801127</v>
       </c>
       <c r="R57" t="n">
-        <v>7496945</v>
+        <v>7497259</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6731,10 +6731,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120259789</v>
+        <v>120259866</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>801215</v>
+        <v>800977</v>
       </c>
       <c r="R58" t="n">
-        <v>7497216</v>
+        <v>7497131</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6837,10 +6837,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120259777</v>
+        <v>120259791</v>
       </c>
       <c r="B59" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6853,21 +6853,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>801236</v>
+        <v>801191</v>
       </c>
       <c r="R59" t="n">
-        <v>7497261</v>
+        <v>7497194</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120259838</v>
+        <v>120259809</v>
       </c>
       <c r="B60" t="n">
         <v>78542</v>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800964</v>
+        <v>801023</v>
       </c>
       <c r="R60" t="n">
-        <v>7496622</v>
+        <v>7496816</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -1336,10 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120107787</v>
+        <v>120101143</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,29 +1352,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1384,10 +1388,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800951</v>
+        <v>800993</v>
       </c>
       <c r="R8" t="n">
-        <v>7496943</v>
+        <v>7497292</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,11 +1424,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120101143</v>
+        <v>120107787</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,33 +1466,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1503,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800993</v>
+        <v>800951</v>
       </c>
       <c r="R9" t="n">
-        <v>7497292</v>
+        <v>7496943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,6 +1534,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2625,10 +2625,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120259822</v>
+        <v>120259867</v>
       </c>
       <c r="B20" t="n">
-        <v>90864</v>
+        <v>90934</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2637,25 +2637,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,7 +2671,7 @@
         <v>800977</v>
       </c>
       <c r="R20" t="n">
-        <v>7496685</v>
+        <v>7497131</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120259867</v>
+        <v>120259822</v>
       </c>
       <c r="B21" t="n">
-        <v>90934</v>
+        <v>90864</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,25 +2743,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1506</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
         <v>800977</v>
       </c>
       <c r="R21" t="n">
-        <v>7497131</v>
+        <v>7496685</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,10 +2943,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120259808</v>
+        <v>120259864</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2959,31 +2959,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>801023</v>
+        <v>801011</v>
       </c>
       <c r="R23" t="n">
-        <v>7496816</v>
+        <v>7497112</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,17 +3024,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3058,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120259864</v>
+        <v>120259814</v>
       </c>
       <c r="B24" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3074,21 +3065,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3101,10 +3092,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>801011</v>
+        <v>801003</v>
       </c>
       <c r="R24" t="n">
-        <v>7497112</v>
+        <v>7496768</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3376,10 +3367,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120259814</v>
+        <v>120259808</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3392,26 +3383,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3419,10 +3415,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>801003</v>
+        <v>801023</v>
       </c>
       <c r="R27" t="n">
-        <v>7496768</v>
+        <v>7496816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3457,13 +3453,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4127,10 +4127,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120259777</v>
+        <v>120259872</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>90527</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4143,21 +4143,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>801236</v>
+        <v>801033</v>
       </c>
       <c r="R34" t="n">
-        <v>7497261</v>
+        <v>7497193</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4233,10 +4233,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120259872</v>
+        <v>120259777</v>
       </c>
       <c r="B35" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4249,21 +4249,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>801033</v>
+        <v>801236</v>
       </c>
       <c r="R35" t="n">
-        <v>7497193</v>
+        <v>7497261</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120259850</v>
+        <v>120259793</v>
       </c>
       <c r="B39" t="n">
-        <v>90545</v>
+        <v>90864</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4669,25 +4669,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800956</v>
+        <v>801114</v>
       </c>
       <c r="R39" t="n">
-        <v>7496826</v>
+        <v>7497155</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4763,10 +4763,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120259793</v>
+        <v>120259850</v>
       </c>
       <c r="B40" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4775,25 +4775,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>801114</v>
+        <v>800956</v>
       </c>
       <c r="R40" t="n">
-        <v>7497155</v>
+        <v>7496826</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120259863</v>
+        <v>120259840</v>
       </c>
       <c r="B44" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5220,31 +5220,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5252,10 +5247,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800990</v>
+        <v>800979</v>
       </c>
       <c r="R44" t="n">
-        <v>7497009</v>
+        <v>7496643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5290,17 +5285,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5319,10 +5310,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120259840</v>
+        <v>120259863</v>
       </c>
       <c r="B45" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5335,26 +5326,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5362,10 +5358,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800979</v>
+        <v>800990</v>
       </c>
       <c r="R45" t="n">
-        <v>7496643</v>
+        <v>7497009</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5400,13 +5396,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6184,10 +6184,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120259803</v>
+        <v>120259821</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6200,31 +6200,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6232,10 +6227,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>801068</v>
+        <v>800977</v>
       </c>
       <c r="R53" t="n">
-        <v>7497037</v>
+        <v>7496685</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6270,17 +6265,13 @@
           <t>2024-10-05</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Skalad gran</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6299,10 +6290,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120259821</v>
+        <v>120259874</v>
       </c>
       <c r="B54" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6315,21 +6306,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6342,10 +6333,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800977</v>
+        <v>801042</v>
       </c>
       <c r="R54" t="n">
-        <v>7496685</v>
+        <v>7497202</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6405,10 +6396,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120259874</v>
+        <v>120259803</v>
       </c>
       <c r="B55" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6421,26 +6412,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6448,10 +6444,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>801042</v>
+        <v>801068</v>
       </c>
       <c r="R55" t="n">
-        <v>7497202</v>
+        <v>7497037</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6486,13 +6482,17 @@
           <t>2024-10-05</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6511,10 +6511,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120259796</v>
+        <v>120259878</v>
       </c>
       <c r="B56" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6523,39 +6523,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6563,10 +6554,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>801096</v>
+        <v>801127</v>
       </c>
       <c r="R56" t="n">
-        <v>7497061</v>
+        <v>7497259</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6607,6 +6598,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6625,10 +6617,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120259878</v>
+        <v>120259796</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6637,30 +6629,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6668,10 +6669,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>801127</v>
+        <v>801096</v>
       </c>
       <c r="R57" t="n">
-        <v>7497259</v>
+        <v>7497061</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,7 +6713,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>120107790</v>
       </c>
       <c r="B5" t="n">
-        <v>57947</v>
+        <v>57985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -996,11 +996,11 @@
         <v>120107790</v>
       </c>
       <c r="B5" t="n">
-        <v>58003</v>
+        <v>58008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1010,11 +1010,6 @@
       </c>
       <c r="E5" t="n">
         <v>102125</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallbit</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>120107790</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,6 +1010,11 @@
       </c>
       <c r="E5" t="n">
         <v>102125</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>120107790</v>
       </c>
       <c r="B5" t="n">
-        <v>58012</v>
+        <v>58013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9207,6 +9207,1223 @@
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128075283</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91345</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>800993</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7497195</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128075448</v>
+      </c>
+      <c r="B82" t="n">
+        <v>82870</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>800955</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7496889</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128076540</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>800955</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7496889</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128072442</v>
+      </c>
+      <c r="B84" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>801008</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7497233</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128071713</v>
+      </c>
+      <c r="B85" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>801071</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7497222</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128075835</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91645</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>658</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>800955</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7496889</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128072277</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91718</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>800949</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7497208</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128076088</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91718</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>800955</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7496889</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>128074981</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>800993</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7497195</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>128074767</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>800993</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7497195</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar.</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128075662</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Isopalo, Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>800955</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7496889</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9209,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128075283</v>
+        <v>128075448</v>
       </c>
       <c r="B81" t="n">
-        <v>91345</v>
+        <v>82870</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,21 +9220,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>800993</v>
+        <v>800955</v>
       </c>
       <c r="R81" t="n">
-        <v>7497195</v>
+        <v>7496889</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128075448</v>
+        <v>128075283</v>
       </c>
       <c r="B82" t="n">
-        <v>82870</v>
+        <v>91345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>800955</v>
+        <v>800993</v>
       </c>
       <c r="R82" t="n">
-        <v>7496889</v>
+        <v>7497195</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9423,10 +9423,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128076540</v>
+        <v>128072442</v>
       </c>
       <c r="B83" t="n">
-        <v>57832</v>
+        <v>56855</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9434,43 +9434,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>800955</v>
+        <v>801008</v>
       </c>
       <c r="R83" t="n">
-        <v>7496889</v>
+        <v>7497233</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9502,7 +9493,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9512,7 +9503,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9539,10 +9530,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128072442</v>
+        <v>128076540</v>
       </c>
       <c r="B84" t="n">
-        <v>56855</v>
+        <v>57832</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9550,34 +9541,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>801008</v>
+        <v>800955</v>
       </c>
       <c r="R84" t="n">
-        <v>7497233</v>
+        <v>7496889</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9209,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128075448</v>
+        <v>128075283</v>
       </c>
       <c r="B81" t="n">
-        <v>82870</v>
+        <v>91346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,21 +9220,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>800955</v>
+        <v>800993</v>
       </c>
       <c r="R81" t="n">
-        <v>7496889</v>
+        <v>7497195</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128075283</v>
+        <v>128075448</v>
       </c>
       <c r="B82" t="n">
-        <v>91345</v>
+        <v>82870</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>800993</v>
+        <v>800955</v>
       </c>
       <c r="R82" t="n">
-        <v>7497195</v>
+        <v>7496889</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9772,7 +9772,7 @@
         <v>128075835</v>
       </c>
       <c r="B86" t="n">
-        <v>91645</v>
+        <v>91646</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>128072277</v>
       </c>
       <c r="B87" t="n">
-        <v>91718</v>
+        <v>91719</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>128076088</v>
       </c>
       <c r="B88" t="n">
-        <v>91718</v>
+        <v>91719</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10424,6 +10424,838 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128173516</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79108</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>864</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>800993</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7497184</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128173149</v>
+      </c>
+      <c r="B93" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>801091</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7497186</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128173462</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57776</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>800993</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7497184</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128174256</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78012</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>801075</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7497265</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128172806</v>
+      </c>
+      <c r="B96" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>801075</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7497265</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128172826</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79029</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>801075</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7497265</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128173279</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91719</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>800953</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7497204</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128172742</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>801075</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7497265</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9209,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128075283</v>
+        <v>128075448</v>
       </c>
       <c r="B81" t="n">
-        <v>91346</v>
+        <v>82870</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,21 +9220,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>800993</v>
+        <v>800955</v>
       </c>
       <c r="R81" t="n">
-        <v>7497195</v>
+        <v>7496889</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128075448</v>
+        <v>128075283</v>
       </c>
       <c r="B82" t="n">
-        <v>82870</v>
+        <v>91346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>800955</v>
+        <v>800993</v>
       </c>
       <c r="R82" t="n">
-        <v>7496889</v>
+        <v>7497195</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9423,10 +9423,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128072442</v>
+        <v>128076540</v>
       </c>
       <c r="B83" t="n">
-        <v>56855</v>
+        <v>57832</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9434,34 +9434,43 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>801008</v>
+        <v>800955</v>
       </c>
       <c r="R83" t="n">
-        <v>7497233</v>
+        <v>7496889</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9493,7 +9502,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9503,7 +9512,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9530,10 +9539,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128076540</v>
+        <v>128072442</v>
       </c>
       <c r="B84" t="n">
-        <v>57832</v>
+        <v>56855</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9541,43 +9550,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>800955</v>
+        <v>801008</v>
       </c>
       <c r="R84" t="n">
-        <v>7496889</v>
+        <v>7497233</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9876,7 +9876,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128072277</v>
+        <v>128076088</v>
       </c>
       <c r="B87" t="n">
         <v>91719</v>
@@ -9911,10 +9911,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>800949</v>
+        <v>800955</v>
       </c>
       <c r="R87" t="n">
-        <v>7497208</v>
+        <v>7496889</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9983,7 +9983,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128076088</v>
+        <v>128072277</v>
       </c>
       <c r="B88" t="n">
         <v>91719</v>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>800955</v>
+        <v>800949</v>
       </c>
       <c r="R88" t="n">
-        <v>7496889</v>
+        <v>7497208</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10955,32 +10955,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>91719</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R97" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11056,32 +11056,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B98" t="n">
-        <v>91719</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R98" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9319,7 +9319,7 @@
         <v>128075283</v>
       </c>
       <c r="B82" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9423,10 +9423,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128076540</v>
+        <v>128072442</v>
       </c>
       <c r="B83" t="n">
-        <v>57832</v>
+        <v>56855</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9434,43 +9434,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>800955</v>
+        <v>801008</v>
       </c>
       <c r="R83" t="n">
-        <v>7496889</v>
+        <v>7497233</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9502,7 +9493,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9512,7 +9503,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9539,10 +9530,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128072442</v>
+        <v>128076540</v>
       </c>
       <c r="B84" t="n">
-        <v>56855</v>
+        <v>57832</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9550,34 +9541,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>801008</v>
+        <v>800955</v>
       </c>
       <c r="R84" t="n">
-        <v>7497233</v>
+        <v>7496889</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9772,7 +9772,7 @@
         <v>128075835</v>
       </c>
       <c r="B86" t="n">
-        <v>91646</v>
+        <v>91647</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9876,10 +9876,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128076088</v>
+        <v>128072277</v>
       </c>
       <c r="B87" t="n">
-        <v>91719</v>
+        <v>91720</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9911,10 +9911,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>800955</v>
+        <v>800949</v>
       </c>
       <c r="R87" t="n">
-        <v>7496889</v>
+        <v>7497208</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9983,10 +9983,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128072277</v>
+        <v>128076088</v>
       </c>
       <c r="B88" t="n">
-        <v>91719</v>
+        <v>91720</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,10 +10018,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>800949</v>
+        <v>800955</v>
       </c>
       <c r="R88" t="n">
-        <v>7497208</v>
+        <v>7496889</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10636,46 +10636,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B94" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10683,10 +10674,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R94" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10727,6 +10718,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10745,37 +10737,46 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B95" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10783,10 +10784,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R95" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10827,7 +10828,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10955,32 +10955,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B97" t="n">
-        <v>91719</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R97" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11056,32 +11056,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>91720</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R98" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11160,7 +11160,7 @@
         <v>128172742</v>
       </c>
       <c r="B99" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9319,7 +9319,7 @@
         <v>128075283</v>
       </c>
       <c r="B82" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>128075835</v>
       </c>
       <c r="B86" t="n">
-        <v>91647</v>
+        <v>91648</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>128072277</v>
       </c>
       <c r="B87" t="n">
-        <v>91720</v>
+        <v>91721</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>128076088</v>
       </c>
       <c r="B88" t="n">
-        <v>91720</v>
+        <v>91721</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10636,37 +10636,46 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B94" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10674,10 +10683,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R94" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10718,7 +10727,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10737,46 +10745,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B95" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10784,10 +10783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R95" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,6 +10827,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10955,32 +10955,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>91721</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R97" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11056,32 +11056,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B98" t="n">
-        <v>91720</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R98" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11160,7 +11160,7 @@
         <v>128172742</v>
       </c>
       <c r="B99" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9423,10 +9423,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128072442</v>
+        <v>128076540</v>
       </c>
       <c r="B83" t="n">
-        <v>56855</v>
+        <v>57832</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9434,34 +9434,43 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>801008</v>
+        <v>800955</v>
       </c>
       <c r="R83" t="n">
-        <v>7497233</v>
+        <v>7496889</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9493,7 +9502,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9503,7 +9512,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9530,10 +9539,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128076540</v>
+        <v>128072442</v>
       </c>
       <c r="B84" t="n">
-        <v>57832</v>
+        <v>56855</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9541,43 +9550,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>800955</v>
+        <v>801008</v>
       </c>
       <c r="R84" t="n">
-        <v>7496889</v>
+        <v>7497233</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10636,46 +10636,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B94" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10683,10 +10674,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R94" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10727,6 +10718,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10745,37 +10737,46 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B95" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10783,10 +10784,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R95" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10827,7 +10828,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10636,37 +10636,46 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B94" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10674,10 +10683,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R94" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10718,7 +10727,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10737,46 +10745,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B95" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10784,10 +10783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R95" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,6 +10827,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10636,46 +10636,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B94" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10683,10 +10674,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R94" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10727,6 +10718,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10745,37 +10737,46 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B95" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10783,10 +10784,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R95" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10827,7 +10828,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10955,32 +10955,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B97" t="n">
-        <v>91721</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R97" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11056,32 +11056,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>91721</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R98" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10636,37 +10636,46 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B94" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10674,10 +10683,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R94" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10718,7 +10727,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10737,46 +10745,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B95" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10784,10 +10783,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R95" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10828,6 +10827,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10955,32 +10955,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>91721</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R97" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11056,32 +11056,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B98" t="n">
-        <v>91721</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R98" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9423,10 +9423,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128076540</v>
+        <v>128072442</v>
       </c>
       <c r="B83" t="n">
-        <v>57832</v>
+        <v>56855</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9434,43 +9434,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>800955</v>
+        <v>801008</v>
       </c>
       <c r="R83" t="n">
-        <v>7496889</v>
+        <v>7497233</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9502,7 +9493,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9512,7 +9503,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9539,10 +9530,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128072442</v>
+        <v>128076540</v>
       </c>
       <c r="B84" t="n">
-        <v>56855</v>
+        <v>57832</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9550,34 +9541,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>801008</v>
+        <v>800955</v>
       </c>
       <c r="R84" t="n">
-        <v>7497233</v>
+        <v>7496889</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10636,46 +10636,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B94" t="n">
-        <v>57776</v>
+        <v>78012</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10683,10 +10674,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R94" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10727,6 +10718,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10745,37 +10737,46 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B95" t="n">
-        <v>78012</v>
+        <v>57776</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10783,10 +10784,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R95" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10827,7 +10828,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10955,32 +10955,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B97" t="n">
-        <v>91721</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10993,10 +10993,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R97" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11056,32 +11056,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>91721</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R98" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9209,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128075448</v>
+        <v>128075283</v>
       </c>
       <c r="B81" t="n">
-        <v>82870</v>
+        <v>91348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9220,21 +9220,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9244,10 +9244,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>800955</v>
+        <v>800993</v>
       </c>
       <c r="R81" t="n">
-        <v>7496889</v>
+        <v>7497195</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128075283</v>
+        <v>128072442</v>
       </c>
       <c r="B82" t="n">
-        <v>91348</v>
+        <v>56855</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9327,21 +9327,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9351,10 +9351,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>800993</v>
+        <v>801008</v>
       </c>
       <c r="R82" t="n">
-        <v>7497195</v>
+        <v>7497233</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9423,7 +9423,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128072442</v>
+        <v>128071713</v>
       </c>
       <c r="B83" t="n">
         <v>56855</v>
@@ -9451,17 +9451,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Isopalo, Isopalo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>801008</v>
+        <v>801071</v>
       </c>
       <c r="R83" t="n">
-        <v>7497233</v>
+        <v>7497222</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9493,7 +9509,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9503,7 +9519,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9530,54 +9546,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128076540</v>
+        <v>128072277</v>
       </c>
       <c r="B84" t="n">
-        <v>57832</v>
+        <v>91721</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>1506</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>800955</v>
+        <v>800949</v>
       </c>
       <c r="R84" t="n">
-        <v>7496889</v>
+        <v>7497208</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9609,7 +9616,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9619,7 +9626,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9646,10 +9653,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128071713</v>
+        <v>128074981</v>
       </c>
       <c r="B85" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9657,16 +9664,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9674,33 +9681,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Isopalo, Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>801071</v>
+        <v>800993</v>
       </c>
       <c r="R85" t="n">
-        <v>7497222</v>
+        <v>7497195</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9732,7 +9723,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9742,7 +9733,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9769,10 +9765,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128075835</v>
+        <v>128074767</v>
       </c>
       <c r="B86" t="n">
-        <v>91648</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9780,21 +9776,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9804,10 +9800,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>800955</v>
+        <v>800993</v>
       </c>
       <c r="R86" t="n">
-        <v>7496889</v>
+        <v>7497195</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9839,7 +9835,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9849,7 +9845,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9876,45 +9877,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128072277</v>
+        <v>128173516</v>
       </c>
       <c r="B87" t="n">
-        <v>91721</v>
+        <v>79108</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1506</v>
+        <v>864</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Isopalo, Isopalo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>800949</v>
+        <v>800993</v>
       </c>
       <c r="R87" t="n">
-        <v>7497208</v>
+        <v>7497184</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9944,27 +9948,18 @@
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9983,45 +9978,57 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128076088</v>
+        <v>128173149</v>
       </c>
       <c r="B88" t="n">
-        <v>91721</v>
+        <v>56855</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1506</v>
+        <v>102612</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Isopalo, Isopalo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>800955</v>
+        <v>801091</v>
       </c>
       <c r="R88" t="n">
-        <v>7496889</v>
+        <v>7497186</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10051,19 +10058,9 @@
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10090,10 +10087,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128074981</v>
+        <v>128174256</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>78012</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10101,34 +10098,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Isopalo, Isopalo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R89" t="n">
-        <v>7497195</v>
+        <v>7497265</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10158,32 +10158,18 @@
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10202,45 +10188,57 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128074767</v>
+        <v>128173462</v>
       </c>
       <c r="B90" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Isopalo, Isopalo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>800993</v>
       </c>
       <c r="R90" t="n">
-        <v>7497195</v>
+        <v>7497184</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10270,24 +10268,9 @@
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt draperade granar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10314,10 +10297,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128075662</v>
+        <v>128172806</v>
       </c>
       <c r="B91" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10325,16 +10308,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10342,17 +10325,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Isopalo, Isopalo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>800955</v>
+        <v>801075</v>
       </c>
       <c r="R91" t="n">
-        <v>7496889</v>
+        <v>7497265</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10382,24 +10377,9 @@
           <t>2025-08-30</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10426,10 +10406,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128173516</v>
+        <v>128172826</v>
       </c>
       <c r="B92" t="n">
-        <v>79108</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10437,21 +10417,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R92" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10527,46 +10507,37 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128173149</v>
+        <v>128173279</v>
       </c>
       <c r="B93" t="n">
-        <v>56855</v>
+        <v>91721</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>102612</v>
+        <v>1506</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10574,10 +10545,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>801091</v>
+        <v>800953</v>
       </c>
       <c r="R93" t="n">
-        <v>7497186</v>
+        <v>7497204</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10618,6 +10589,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10636,10 +10608,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128174256</v>
+        <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>78012</v>
+        <v>91352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10647,21 +10619,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10735,527 +10707,6 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>128173462</v>
-      </c>
-      <c r="B95" t="n">
-        <v>57776</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Isopalo, T lm</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>800993</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7497184</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>128172806</v>
-      </c>
-      <c r="B96" t="n">
-        <v>56855</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Isopalo, T lm</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>801075</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7497265</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>128172826</v>
-      </c>
-      <c r="B97" t="n">
-        <v>79029</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Isopalo, T lm</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>801075</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7497265</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>128173279</v>
-      </c>
-      <c r="B98" t="n">
-        <v>91721</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Skeletocutis odora</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Isopalo, T lm</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>800953</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7497204</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>128172742</v>
-      </c>
-      <c r="B99" t="n">
-        <v>91352</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Isopalo, T lm</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>801075</v>
-      </c>
-      <c r="R99" t="n">
-        <v>7497265</v>
-      </c>
-      <c r="S99" t="n">
-        <v>10</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Kiruna</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Torne lappmark</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Jukkasjärvi</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9212,7 +9212,7 @@
         <v>128075283</v>
       </c>
       <c r="B81" t="n">
-        <v>91348</v>
+        <v>91356</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>128072277</v>
       </c>
       <c r="B84" t="n">
-        <v>91721</v>
+        <v>91729</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>128074981</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>128074767</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>128173516</v>
       </c>
       <c r="B87" t="n">
-        <v>79108</v>
+        <v>79111</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10087,37 +10087,46 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B89" t="n">
-        <v>78012</v>
+        <v>57777</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10125,10 +10134,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R89" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10169,7 +10178,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10188,46 +10196,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B90" t="n">
-        <v>57776</v>
+        <v>78015</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10235,10 +10234,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R90" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10279,6 +10278,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10406,32 +10406,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B92" t="n">
-        <v>79029</v>
+        <v>91729</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R92" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B93" t="n">
-        <v>91721</v>
+        <v>79032</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R93" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10611,7 +10611,7 @@
         <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10087,46 +10087,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B89" t="n">
-        <v>57777</v>
+        <v>78015</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10134,10 +10125,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R89" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10178,6 +10169,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10196,37 +10188,46 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B90" t="n">
-        <v>78015</v>
+        <v>57777</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10234,10 +10235,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R90" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10278,7 +10279,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9212,7 +9212,7 @@
         <v>128075283</v>
       </c>
       <c r="B81" t="n">
-        <v>91356</v>
+        <v>91448</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>128072442</v>
       </c>
       <c r="B82" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>128071713</v>
       </c>
       <c r="B83" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>128072277</v>
       </c>
       <c r="B84" t="n">
-        <v>91729</v>
+        <v>91821</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>128074981</v>
       </c>
       <c r="B85" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>128074767</v>
       </c>
       <c r="B86" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>128173516</v>
       </c>
       <c r="B87" t="n">
-        <v>79111</v>
+        <v>79162</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>128173149</v>
       </c>
       <c r="B88" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10087,37 +10087,46 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B89" t="n">
-        <v>78015</v>
+        <v>57789</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10125,10 +10134,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R89" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10169,7 +10178,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10188,46 +10196,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B90" t="n">
-        <v>57777</v>
+        <v>78060</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10235,10 +10234,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R90" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10279,6 +10278,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>128172806</v>
       </c>
       <c r="B91" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>128173279</v>
       </c>
       <c r="B92" t="n">
-        <v>91729</v>
+        <v>91821</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>128172826</v>
       </c>
       <c r="B93" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10406,32 +10406,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B92" t="n">
-        <v>91821</v>
+        <v>79083</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R92" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B93" t="n">
-        <v>79083</v>
+        <v>91821</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R93" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10406,32 +10406,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B92" t="n">
-        <v>79083</v>
+        <v>91821</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R92" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B93" t="n">
-        <v>91821</v>
+        <v>79083</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R93" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10087,46 +10087,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B89" t="n">
-        <v>57789</v>
+        <v>78060</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10134,10 +10125,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R89" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10178,6 +10169,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10196,37 +10188,46 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B90" t="n">
-        <v>78060</v>
+        <v>57789</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10234,10 +10235,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R90" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10278,7 +10279,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10707,6 +10707,520 @@
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128653574</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>800952</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7497253</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Avbarkad gran med små barkflagor nedanför på marken.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128653600</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91458</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>801148</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7497036</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128653596</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91458</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>801137</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7497058</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128653540</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>800980</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7497390</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128653562</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>800975</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7497369</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9212,7 +9212,7 @@
         <v>128075283</v>
       </c>
       <c r="B81" t="n">
-        <v>91448</v>
+        <v>91460</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>128072442</v>
       </c>
       <c r="B82" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>128071713</v>
       </c>
       <c r="B83" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>128072277</v>
       </c>
       <c r="B84" t="n">
-        <v>91821</v>
+        <v>91833</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>128074981</v>
       </c>
       <c r="B85" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>128074767</v>
       </c>
       <c r="B86" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>128173516</v>
       </c>
       <c r="B87" t="n">
-        <v>79162</v>
+        <v>79166</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>128173149</v>
       </c>
       <c r="B88" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10087,37 +10087,46 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B89" t="n">
-        <v>78060</v>
+        <v>57793</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10125,10 +10134,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R89" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10169,7 +10178,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10188,46 +10196,37 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B90" t="n">
-        <v>57789</v>
+        <v>78064</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10235,10 +10234,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R90" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10279,6 +10278,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>128172806</v>
       </c>
       <c r="B91" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>128173279</v>
       </c>
       <c r="B92" t="n">
-        <v>91821</v>
+        <v>91833</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>128172826</v>
       </c>
       <c r="B93" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>91452</v>
+        <v>91464</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9880,7 +9880,7 @@
         <v>128173516</v>
       </c>
       <c r="B87" t="n">
-        <v>79166</v>
+        <v>79168</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>128174256</v>
       </c>
       <c r="B90" t="n">
-        <v>78064</v>
+        <v>78066</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>128173279</v>
       </c>
       <c r="B92" t="n">
-        <v>91833</v>
+        <v>91835</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>128172826</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9212,7 +9212,7 @@
         <v>128075283</v>
       </c>
       <c r="B81" t="n">
-        <v>91460</v>
+        <v>91462</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>128072277</v>
       </c>
       <c r="B84" t="n">
-        <v>91833</v>
+        <v>91835</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>128074767</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10409,7 +10409,7 @@
         <v>128173279</v>
       </c>
       <c r="B92" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11221,6 +11221,2298 @@
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128801498</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91836</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>801059</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7497178</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128801522</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91467</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>801027</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7497060</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128801553</v>
+      </c>
+      <c r="B102" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>801020</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7496768</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128801754</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>800951</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7496620</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128801536</v>
+      </c>
+      <c r="B104" t="n">
+        <v>56871</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>801011</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7496986</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128801437</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>800998</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7497408</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128801587</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>801017</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7496687</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128801500</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91467</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>801059</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7497178</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128801436</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>800998</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7497408</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128801444</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>801004</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7497371</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128801515</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91763</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>658</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>801013</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7497115</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>128801973</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>800950</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7497251</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>128801555</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>801020</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7496768</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Rikligt draperade granar</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128801446</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>801004</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7497371</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>128801695</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>800974</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7496680</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>128801461</v>
+      </c>
+      <c r="B115" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>801014</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7497332</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128801457</v>
+      </c>
+      <c r="B116" t="n">
+        <v>58059</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>801014</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7497332</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128801463</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>801014</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7497332</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128801558</v>
+      </c>
+      <c r="B118" t="n">
+        <v>91485</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>801005</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7496772</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128801655</v>
+      </c>
+      <c r="B119" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>801027</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7496711</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128801524</v>
+      </c>
+      <c r="B120" t="n">
+        <v>56871</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>801027</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7497060</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128801492</v>
+      </c>
+      <c r="B121" t="n">
+        <v>91763</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>658</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>801059</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7497178</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10712,7 +10712,7 @@
         <v>128653574</v>
       </c>
       <c r="B95" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91836</v>
+        <v>91863</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91467</v>
+        <v>91512</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R101" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91485</v>
+        <v>91494</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R102" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11529,7 +11529,7 @@
         <v>128801754</v>
       </c>
       <c r="B103" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>128801536</v>
       </c>
       <c r="B104" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>128801587</v>
       </c>
       <c r="B106" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B107" t="n">
-        <v>91467</v>
+        <v>91512</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R107" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B108" t="n">
-        <v>91485</v>
+        <v>91494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R108" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>128801695</v>
       </c>
       <c r="B114" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>91485</v>
+        <v>79116</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,42 +12888,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801461</v>
       </c>
       <c r="B116" t="n">
-        <v>58059</v>
+        <v>91512</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12970,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12989,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>79089</v>
+        <v>58086</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13076,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>128801655</v>
       </c>
       <c r="B119" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>128801524</v>
       </c>
       <c r="B120" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91763</v>
+        <v>91790</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -9880,7 +9880,7 @@
         <v>128173516</v>
       </c>
       <c r="B87" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>128173149</v>
       </c>
       <c r="B88" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10087,46 +10087,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128173462</v>
+        <v>128174256</v>
       </c>
       <c r="B89" t="n">
-        <v>57793</v>
+        <v>78093</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103031</v>
+        <v>228579</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10134,10 +10125,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>800993</v>
+        <v>801075</v>
       </c>
       <c r="R89" t="n">
-        <v>7497184</v>
+        <v>7497265</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10178,6 +10169,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10196,37 +10188,46 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128174256</v>
+        <v>128173462</v>
       </c>
       <c r="B90" t="n">
-        <v>78066</v>
+        <v>57820</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>103031</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10234,10 +10235,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>801075</v>
+        <v>800993</v>
       </c>
       <c r="R90" t="n">
-        <v>7497265</v>
+        <v>7497184</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10278,7 +10279,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>128172806</v>
       </c>
       <c r="B91" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10406,32 +10406,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128173279</v>
+        <v>128172826</v>
       </c>
       <c r="B92" t="n">
-        <v>91836</v>
+        <v>79116</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>800953</v>
+        <v>801075</v>
       </c>
       <c r="R92" t="n">
-        <v>7497204</v>
+        <v>7497265</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10507,32 +10507,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128172826</v>
+        <v>128173279</v>
       </c>
       <c r="B93" t="n">
-        <v>79089</v>
+        <v>91863</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>801075</v>
+        <v>800953</v>
       </c>
       <c r="R93" t="n">
-        <v>7497265</v>
+        <v>7497204</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10611,7 +10611,7 @@
         <v>128172742</v>
       </c>
       <c r="B94" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91512</v>
+        <v>91494</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R107" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R108" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>79116</v>
+        <v>91512</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,10 +12888,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>91512</v>
+        <v>79116</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,21 +12899,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91863</v>
+        <v>91868</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B107" t="n">
-        <v>91494</v>
+        <v>91517</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R107" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B108" t="n">
-        <v>91512</v>
+        <v>91499</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R108" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>91512</v>
+        <v>79120</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,37 +12888,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B116" t="n">
-        <v>79116</v>
+        <v>58086</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,7 +12975,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12989,42 +12993,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801457</v>
+        <v>128801461</v>
       </c>
       <c r="B117" t="n">
-        <v>58086</v>
+        <v>91517</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13076,6 +13075,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91790</v>
+        <v>91795</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91868</v>
+        <v>91873</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91517</v>
+        <v>91504</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R101" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91499</v>
+        <v>91522</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R102" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91517</v>
+        <v>91504</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R107" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91499</v>
+        <v>91522</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R108" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12888,42 +12888,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801461</v>
       </c>
       <c r="B116" t="n">
-        <v>58086</v>
+        <v>91522</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12970,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12989,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801461</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>91517</v>
+        <v>58086</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13076,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91795</v>
+        <v>91800</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B107" t="n">
-        <v>91504</v>
+        <v>91522</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R107" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B108" t="n">
-        <v>91522</v>
+        <v>91504</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R108" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>79120</v>
+        <v>91522</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,10 +12888,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>91522</v>
+        <v>79120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,21 +12899,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91522</v>
+        <v>91504</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R107" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91504</v>
+        <v>91522</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R108" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12888,37 +12888,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B116" t="n">
-        <v>79120</v>
+        <v>58086</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,7 +12975,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12989,42 +12993,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B117" t="n">
-        <v>58086</v>
+        <v>79120</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13076,6 +13075,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10712,7 +10712,7 @@
         <v>128653574</v>
       </c>
       <c r="B95" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91873</v>
+        <v>91877</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91504</v>
+        <v>91526</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R101" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91522</v>
+        <v>91508</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R102" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128801754</v>
+        <v>128801536</v>
       </c>
       <c r="B103" t="n">
-        <v>57716</v>
+        <v>56901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11537,16 +11537,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11554,12 +11554,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11569,10 +11573,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>800951</v>
+        <v>801011</v>
       </c>
       <c r="R103" t="n">
-        <v>7496620</v>
+        <v>7496986</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11605,11 +11609,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11636,10 +11635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128801536</v>
+        <v>128801754</v>
       </c>
       <c r="B104" t="n">
-        <v>56898</v>
+        <v>57720</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11647,16 +11646,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11664,16 +11663,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11683,10 +11678,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>801011</v>
+        <v>800951</v>
       </c>
       <c r="R104" t="n">
-        <v>7496986</v>
+        <v>7496620</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11719,6 +11714,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>128801587</v>
       </c>
       <c r="B106" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>128801695</v>
       </c>
       <c r="B114" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12888,42 +12888,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>58086</v>
+        <v>79124</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12970,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12989,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>79120</v>
+        <v>58090</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13076,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>128801655</v>
       </c>
       <c r="B119" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>128801524</v>
       </c>
       <c r="B120" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91526</v>
+        <v>91508</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R101" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91508</v>
+        <v>91526</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R102" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128801536</v>
+        <v>128801754</v>
       </c>
       <c r="B103" t="n">
-        <v>56901</v>
+        <v>57720</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11537,16 +11537,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11554,16 +11554,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11573,10 +11569,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>801011</v>
+        <v>800951</v>
       </c>
       <c r="R103" t="n">
-        <v>7496986</v>
+        <v>7496620</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11609,6 +11605,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11635,10 +11636,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128801754</v>
+        <v>128801536</v>
       </c>
       <c r="B104" t="n">
-        <v>57720</v>
+        <v>56901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11646,16 +11647,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11663,12 +11664,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11678,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>800951</v>
+        <v>801011</v>
       </c>
       <c r="R104" t="n">
-        <v>7496620</v>
+        <v>7496986</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11714,11 +11719,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B110" t="n">
-        <v>91804</v>
+        <v>57720</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,26 +12270,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12297,10 +12302,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R110" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12335,13 +12340,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12360,10 +12369,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B111" t="n">
-        <v>57720</v>
+        <v>91804</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12371,31 +12380,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12403,10 +12407,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R111" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12441,17 +12445,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>57720</v>
+        <v>91804</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,31 +12270,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R110" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12340,17 +12335,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>91804</v>
+        <v>57720</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12380,26 +12371,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12407,10 +12403,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R111" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,13 +12441,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10712,7 +10712,7 @@
         <v>128653574</v>
       </c>
       <c r="B95" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91877</v>
+        <v>91882</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91508</v>
+        <v>91531</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R101" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91526</v>
+        <v>91513</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R102" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128801754</v>
+        <v>128801536</v>
       </c>
       <c r="B103" t="n">
-        <v>57720</v>
+        <v>56904</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11537,16 +11537,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11554,12 +11554,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11569,10 +11573,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>800951</v>
+        <v>801011</v>
       </c>
       <c r="R103" t="n">
-        <v>7496620</v>
+        <v>7496986</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11605,11 +11609,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11636,10 +11635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128801536</v>
+        <v>128801754</v>
       </c>
       <c r="B104" t="n">
-        <v>56901</v>
+        <v>57723</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11647,16 +11646,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11664,16 +11663,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11683,10 +11678,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>801011</v>
+        <v>800951</v>
       </c>
       <c r="R104" t="n">
-        <v>7496986</v>
+        <v>7496620</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11719,6 +11714,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>128801587</v>
       </c>
       <c r="B106" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B107" t="n">
-        <v>91508</v>
+        <v>91531</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R107" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B108" t="n">
-        <v>91526</v>
+        <v>91513</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R108" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>128801695</v>
       </c>
       <c r="B114" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>91526</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,10 +12888,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B116" t="n">
-        <v>79124</v>
+        <v>91531</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,21 +12899,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12992,7 +12992,7 @@
         <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>128801655</v>
       </c>
       <c r="B119" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>128801524</v>
       </c>
       <c r="B120" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>57723</v>
+        <v>91805</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,31 +12270,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R110" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12340,17 +12335,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12380,26 +12371,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12407,10 +12403,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R111" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,13 +12441,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12888,37 +12888,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B116" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,7 +12975,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12989,42 +12993,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B117" t="n">
-        <v>58093</v>
+        <v>79034</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13076,6 +13075,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91520</v>
+        <v>91541</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R101" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91538</v>
+        <v>91523</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R102" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11959,7 +11959,7 @@
         <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,42 +12888,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801461</v>
       </c>
       <c r="B116" t="n">
-        <v>58093</v>
+        <v>91541</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12970,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12989,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>79034</v>
+        <v>58093</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13076,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91893</v>
+        <v>91896</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91541</v>
+        <v>91526</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R101" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91523</v>
+        <v>91544</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R102" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B110" t="n">
-        <v>91808</v>
+        <v>57723</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,26 +12270,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12297,10 +12302,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R110" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12335,13 +12340,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12360,10 +12369,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B111" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12371,31 +12380,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12403,10 +12407,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R111" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12441,17 +12445,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,37 +12888,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801461</v>
+        <v>128801457</v>
       </c>
       <c r="B116" t="n">
-        <v>91541</v>
+        <v>58093</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,7 +12975,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12989,42 +12993,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B117" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13076,6 +13075,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91541</v>
+        <v>56904</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13627,26 +13627,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13654,10 +13659,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13684,12 +13689,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13698,7 +13708,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13717,10 +13726,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13728,31 +13737,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13760,10 +13764,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13790,17 +13794,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13809,6 +13808,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>129088352</v>
       </c>
       <c r="B127" t="n">
-        <v>79113</v>
+        <v>79114</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY130"/>
+  <dimension ref="A1:AY148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,31 +12270,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R110" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12340,17 +12335,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12380,26 +12371,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12407,10 +12403,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R111" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,13 +12441,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12993,10 +12993,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B117" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13004,21 +13004,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14450,6 +14450,1790 @@
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129209501</v>
+      </c>
+      <c r="B131" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>800958</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7496879</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>129214796</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79114</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>864</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>800972</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7496802</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>129214669</v>
+      </c>
+      <c r="B133" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>801036</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7497093</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129209525</v>
+      </c>
+      <c r="B134" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>800971</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7496827</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>129209511</v>
+      </c>
+      <c r="B135" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>658</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>801055</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7497176</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>129214798</v>
+      </c>
+      <c r="B136" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>800972</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7496802</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>129214791</v>
+      </c>
+      <c r="B137" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>800950</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7496863</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>129209507</v>
+      </c>
+      <c r="B138" t="n">
+        <v>91476</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>112</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>801033</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7497194</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129209518</v>
+      </c>
+      <c r="B139" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>800953</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7496877</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129209515</v>
+      </c>
+      <c r="B140" t="n">
+        <v>57827</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>800963</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7496841</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129209519</v>
+      </c>
+      <c r="B141" t="n">
+        <v>91887</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>801040</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7497196</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129214770</v>
+      </c>
+      <c r="B142" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>800985</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7497010</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129209517</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>800962</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7496847</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129209503</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>801025</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7497057</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>129209520</v>
+      </c>
+      <c r="B145" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>801003</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7497371</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>129209510</v>
+      </c>
+      <c r="B146" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>658</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>800990</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7497021</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>129209527</v>
+      </c>
+      <c r="B147" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>801042</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7497198</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>129209526</v>
+      </c>
+      <c r="B148" t="n">
+        <v>91544</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Iso palo, T lm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>801011</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7497039</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13616,10 +13616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13627,31 +13627,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13659,10 +13654,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13689,17 +13684,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13708,6 +13698,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13726,10 +13717,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91544</v>
+        <v>56904</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13737,26 +13728,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13764,10 +13760,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13794,12 +13790,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13808,7 +13809,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14549,10 +14549,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B132" t="n">
-        <v>79114</v>
+        <v>57723</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14560,26 +14560,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14587,10 +14592,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R132" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14617,12 +14622,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14631,7 +14641,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14650,10 +14659,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B133" t="n">
-        <v>57723</v>
+        <v>79114</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14661,31 +14670,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14693,10 +14697,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R133" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14723,17 +14727,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14742,6 +14741,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15156,32 +15156,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209507</v>
+        <v>129209519</v>
       </c>
       <c r="B138" t="n">
-        <v>91476</v>
+        <v>91887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>2063</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801033</v>
+        <v>801040</v>
       </c>
       <c r="R138" t="n">
-        <v>7497194</v>
+        <v>7497196</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15350,32 +15350,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209515</v>
+        <v>129209507</v>
       </c>
       <c r="B140" t="n">
-        <v>57827</v>
+        <v>91476</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103031</v>
+        <v>112</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15385,10 +15385,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800963</v>
+        <v>801033</v>
       </c>
       <c r="R140" t="n">
-        <v>7496841</v>
+        <v>7497194</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15447,45 +15447,53 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209519</v>
+        <v>129214770</v>
       </c>
       <c r="B141" t="n">
-        <v>91887</v>
+        <v>57723</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801040</v>
+        <v>800985</v>
       </c>
       <c r="R141" t="n">
-        <v>7497196</v>
+        <v>7497010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15520,6 +15528,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15532,39 +15545,39 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>57723</v>
+        <v>57827</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15573,24 +15586,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15625,11 +15630,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15642,22 +15642,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209517</v>
+        <v>129209503</v>
       </c>
       <c r="B143" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15665,21 +15665,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800962</v>
+        <v>801025</v>
       </c>
       <c r="R143" t="n">
-        <v>7496847</v>
+        <v>7497057</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15751,10 +15751,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91526</v>
+        <v>91522</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15762,21 +15762,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15848,10 +15848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209520</v>
+        <v>129209510</v>
       </c>
       <c r="B145" t="n">
-        <v>91544</v>
+        <v>91811</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15859,21 +15859,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15883,10 +15883,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801003</v>
+        <v>800990</v>
       </c>
       <c r="R145" t="n">
-        <v>7497371</v>
+        <v>7497021</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15945,10 +15945,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91811</v>
+        <v>91544</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801003</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497371</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B107" t="n">
-        <v>91526</v>
+        <v>91544</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R107" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B108" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R108" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B110" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,26 +12270,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12297,10 +12302,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R110" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12335,13 +12340,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12360,10 +12369,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B111" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12371,31 +12380,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12403,10 +12407,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R111" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12441,17 +12445,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,42 +12888,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>58093</v>
+        <v>79035</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12970,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12989,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801461</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>91544</v>
+        <v>58093</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13076,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91544</v>
+        <v>56904</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13627,26 +13627,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13654,10 +13659,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13684,12 +13689,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13698,7 +13708,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13717,10 +13726,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56904</v>
+        <v>91544</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13728,31 +13737,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13760,10 +13764,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13790,17 +13794,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13809,6 +13808,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15156,32 +15156,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209519</v>
+        <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91887</v>
+        <v>91476</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2063</v>
+        <v>112</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801040</v>
+        <v>801033</v>
       </c>
       <c r="R138" t="n">
-        <v>7497196</v>
+        <v>7497194</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15253,10 +15253,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209518</v>
+        <v>129214770</v>
       </c>
       <c r="B139" t="n">
-        <v>91522</v>
+        <v>57723</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,34 +15264,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800953</v>
+        <v>800985</v>
       </c>
       <c r="R139" t="n">
-        <v>7496877</v>
+        <v>7497010</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15326,6 +15334,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15338,44 +15351,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209507</v>
+        <v>129209515</v>
       </c>
       <c r="B140" t="n">
-        <v>91476</v>
+        <v>57827</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>112</v>
+        <v>103031</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15385,10 +15398,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801033</v>
+        <v>800963</v>
       </c>
       <c r="R140" t="n">
-        <v>7497194</v>
+        <v>7496841</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15447,53 +15460,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129214770</v>
+        <v>129209519</v>
       </c>
       <c r="B141" t="n">
-        <v>57723</v>
+        <v>91887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800985</v>
+        <v>801040</v>
       </c>
       <c r="R141" t="n">
-        <v>7497010</v>
+        <v>7497196</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15528,11 +15533,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15545,44 +15545,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129209518</v>
       </c>
       <c r="B142" t="n">
-        <v>57827</v>
+        <v>91522</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15592,10 +15592,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>800953</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7496877</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -10712,7 +10712,7 @@
         <v>128653574</v>
       </c>
       <c r="B95" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>128653600</v>
       </c>
       <c r="B96" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>128653596</v>
       </c>
       <c r="B97" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>128653540</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11125,7 +11125,7 @@
         <v>128653562</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91896</v>
+        <v>91903</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128801754</v>
+        <v>128801536</v>
       </c>
       <c r="B103" t="n">
-        <v>57723</v>
+        <v>56906</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11537,16 +11537,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11554,12 +11554,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11569,10 +11573,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>800951</v>
+        <v>801011</v>
       </c>
       <c r="R103" t="n">
-        <v>7496620</v>
+        <v>7496986</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11605,11 +11609,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11636,10 +11635,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128801536</v>
+        <v>128801754</v>
       </c>
       <c r="B104" t="n">
-        <v>56904</v>
+        <v>57725</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11647,16 +11646,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11664,16 +11663,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11683,10 +11678,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>801011</v>
+        <v>800951</v>
       </c>
       <c r="R104" t="n">
-        <v>7496986</v>
+        <v>7496620</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11719,6 +11714,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>128801587</v>
       </c>
       <c r="B106" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11956,10 +11956,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128801436</v>
+        <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91544</v>
+        <v>91533</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11967,21 +11967,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11994,10 +11994,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>800998</v>
+        <v>801059</v>
       </c>
       <c r="R107" t="n">
-        <v>7497408</v>
+        <v>7497178</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12057,10 +12057,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128801500</v>
+        <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91526</v>
+        <v>91551</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12068,21 +12068,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12095,10 +12095,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>801059</v>
+        <v>800998</v>
       </c>
       <c r="R108" t="n">
-        <v>7497178</v>
+        <v>7497408</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>57723</v>
+        <v>91818</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,31 +12270,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R110" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12340,17 +12335,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>91811</v>
+        <v>57725</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12380,26 +12371,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12407,10 +12403,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R111" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,13 +12441,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>128801695</v>
       </c>
       <c r="B114" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>128801655</v>
       </c>
       <c r="B119" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>128801524</v>
       </c>
       <c r="B120" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56904</v>
+        <v>91551</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13627,31 +13627,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13659,10 +13654,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13689,17 +13684,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13708,6 +13698,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13726,10 +13717,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91544</v>
+        <v>56906</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13737,26 +13728,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13764,10 +13760,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13794,12 +13790,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13808,7 +13809,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>129088352</v>
       </c>
       <c r="B127" t="n">
-        <v>79114</v>
+        <v>79118</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>129088401</v>
       </c>
       <c r="B128" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>129088378</v>
       </c>
       <c r="B130" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14549,10 +14549,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>57723</v>
+        <v>79118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14560,31 +14560,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14592,10 +14587,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R132" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14622,17 +14617,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14641,6 +14631,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14652,17 +14643,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B133" t="n">
-        <v>79114</v>
+        <v>57725</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14670,26 +14661,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14697,10 +14693,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R133" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14727,12 +14723,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14741,7 +14742,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>129214798</v>
       </c>
       <c r="B136" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -15058,7 +15058,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15149,17 +15149,17 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209507</v>
+        <v>129209518</v>
       </c>
       <c r="B138" t="n">
-        <v>91476</v>
+        <v>91529</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15167,21 +15167,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801033</v>
+        <v>800953</v>
       </c>
       <c r="R138" t="n">
-        <v>7497194</v>
+        <v>7496877</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15256,7 +15256,7 @@
         <v>129214770</v>
       </c>
       <c r="B139" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15356,39 +15356,39 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209515</v>
+        <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>57827</v>
+        <v>91894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103031</v>
+        <v>2063</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15398,10 +15398,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800963</v>
+        <v>801040</v>
       </c>
       <c r="R140" t="n">
-        <v>7496841</v>
+        <v>7497196</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15460,32 +15460,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209519</v>
+        <v>129209507</v>
       </c>
       <c r="B141" t="n">
-        <v>91887</v>
+        <v>91482</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2063</v>
+        <v>112</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15495,10 +15495,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801040</v>
+        <v>801033</v>
       </c>
       <c r="R141" t="n">
-        <v>7497196</v>
+        <v>7497194</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15557,32 +15557,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209518</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>91522</v>
+        <v>57829</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15592,10 +15592,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800953</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7496877</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15654,10 +15654,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B143" t="n">
-        <v>91526</v>
+        <v>91529</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15665,21 +15665,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R143" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15751,10 +15751,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209503</v>
       </c>
       <c r="B144" t="n">
-        <v>91522</v>
+        <v>91533</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15762,21 +15762,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>801025</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497057</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15851,7 +15851,7 @@
         <v>129209510</v>
       </c>
       <c r="B145" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -12888,37 +12888,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B116" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12970,7 +12975,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12989,42 +12993,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B117" t="n">
-        <v>58095</v>
+        <v>79039</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13076,6 +13075,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91903</v>
+        <v>91910</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,42 +12888,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801461</v>
       </c>
       <c r="B116" t="n">
-        <v>58095</v>
+        <v>91558</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12970,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12989,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801463</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>79039</v>
+        <v>58095</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13076,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14549,10 +14549,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B132" t="n">
-        <v>79118</v>
+        <v>57725</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14560,26 +14560,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14587,10 +14592,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R132" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14617,12 +14622,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14631,7 +14641,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14643,17 +14652,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B133" t="n">
-        <v>57725</v>
+        <v>79118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14661,31 +14670,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14693,10 +14697,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R133" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14723,17 +14727,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14742,6 +14741,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14763,7 +14763,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15156,10 +15156,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209518</v>
+        <v>129214770</v>
       </c>
       <c r="B138" t="n">
-        <v>91529</v>
+        <v>57725</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15167,34 +15167,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800953</v>
+        <v>800985</v>
       </c>
       <c r="R138" t="n">
-        <v>7496877</v>
+        <v>7497010</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15229,6 +15237,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15241,22 +15254,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129214770</v>
+        <v>129209507</v>
       </c>
       <c r="B139" t="n">
-        <v>57725</v>
+        <v>91489</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,42 +15277,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800985</v>
+        <v>801033</v>
       </c>
       <c r="R139" t="n">
-        <v>7497010</v>
+        <v>7497194</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15334,11 +15339,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15351,12 +15351,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -15366,7 +15366,7 @@
         <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>91894</v>
+        <v>91901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15460,10 +15460,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209507</v>
+        <v>129209518</v>
       </c>
       <c r="B141" t="n">
-        <v>91482</v>
+        <v>91536</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15471,21 +15471,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15495,10 +15495,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801033</v>
+        <v>800953</v>
       </c>
       <c r="R141" t="n">
-        <v>7497194</v>
+        <v>7496877</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15654,10 +15654,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209517</v>
+        <v>129209520</v>
       </c>
       <c r="B143" t="n">
-        <v>91529</v>
+        <v>91558</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15665,21 +15665,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800962</v>
+        <v>801003</v>
       </c>
       <c r="R143" t="n">
-        <v>7496847</v>
+        <v>7497371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15751,10 +15751,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91533</v>
+        <v>91536</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15762,21 +15762,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15848,10 +15848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15859,21 +15859,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15883,10 +15883,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R145" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15945,10 +15945,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209520</v>
+        <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91551</v>
+        <v>91825</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801003</v>
+        <v>800990</v>
       </c>
       <c r="R146" t="n">
-        <v>7497371</v>
+        <v>7497021</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16045,7 +16045,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>128801536</v>
       </c>
       <c r="B103" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>128801754</v>
       </c>
       <c r="B104" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>128801437</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>128801587</v>
       </c>
       <c r="B106" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>128801444</v>
       </c>
       <c r="B109" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>128801555</v>
       </c>
       <c r="B112" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>128801695</v>
       </c>
       <c r="B114" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,21 +12798,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12888,10 +12888,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801461</v>
+        <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,21 +12899,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12992,7 +12992,7 @@
         <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>128801655</v>
       </c>
       <c r="B119" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>128801524</v>
       </c>
       <c r="B120" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91558</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13627,26 +13627,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13654,10 +13659,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13684,12 +13689,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13698,7 +13708,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13717,10 +13726,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56906</v>
+        <v>91560</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13728,31 +13737,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13760,10 +13764,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13790,17 +13794,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13809,6 +13808,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>129088352</v>
       </c>
       <c r="B127" t="n">
-        <v>79118</v>
+        <v>79120</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>129088401</v>
       </c>
       <c r="B128" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>129088378</v>
       </c>
       <c r="B130" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14542,17 +14542,17 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>57725</v>
+        <v>79120</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14560,31 +14560,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14592,10 +14587,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R132" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14622,17 +14617,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14641,6 +14631,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14652,17 +14643,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B133" t="n">
-        <v>79118</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14670,26 +14661,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14697,10 +14693,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R133" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14727,12 +14723,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14741,7 +14742,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14753,7 +14753,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14763,7 +14763,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14860,7 +14860,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14957,7 +14957,7 @@
         <v>129214798</v>
       </c>
       <c r="B136" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15156,10 +15156,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214770</v>
+        <v>129209518</v>
       </c>
       <c r="B138" t="n">
-        <v>57725</v>
+        <v>91538</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15167,42 +15167,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800985</v>
+        <v>800953</v>
       </c>
       <c r="R138" t="n">
-        <v>7497010</v>
+        <v>7496877</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15237,11 +15229,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15254,12 +15241,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
@@ -15269,7 +15256,7 @@
         <v>129209507</v>
       </c>
       <c r="B139" t="n">
-        <v>91489</v>
+        <v>91491</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15356,39 +15343,39 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209519</v>
+        <v>129209515</v>
       </c>
       <c r="B140" t="n">
-        <v>91901</v>
+        <v>57831</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2063</v>
+        <v>103031</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15398,10 +15385,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801040</v>
+        <v>800963</v>
       </c>
       <c r="R140" t="n">
-        <v>7497196</v>
+        <v>7496841</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15453,39 +15440,39 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B141" t="n">
-        <v>91536</v>
+        <v>91903</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15495,10 +15482,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R141" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15550,34 +15537,34 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B142" t="n">
-        <v>57829</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15586,16 +15573,24 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15630,6 +15625,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15642,22 +15642,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209520</v>
+        <v>129209503</v>
       </c>
       <c r="B143" t="n">
-        <v>91558</v>
+        <v>91542</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15665,21 +15665,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801003</v>
+        <v>801025</v>
       </c>
       <c r="R143" t="n">
-        <v>7497371</v>
+        <v>7497057</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15754,7 +15754,7 @@
         <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15841,17 +15841,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B145" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15859,21 +15859,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15883,10 +15883,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R145" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15938,17 +15938,17 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91825</v>
+        <v>91560</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15956,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15980,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801003</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497371</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16035,7 +16035,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -16045,7 +16045,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -16142,7 +16142,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY148"/>
+  <dimension ref="A1:AY157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R101" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91560</v>
+        <v>91542</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R102" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11526,10 +11526,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128801536</v>
+        <v>128801754</v>
       </c>
       <c r="B103" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11537,16 +11537,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11554,16 +11554,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11573,10 +11569,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>801011</v>
+        <v>800951</v>
       </c>
       <c r="R103" t="n">
-        <v>7496986</v>
+        <v>7496620</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11609,6 +11605,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11635,10 +11636,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128801754</v>
+        <v>128801536</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11646,16 +11647,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11663,12 +11664,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11678,10 +11683,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>800951</v>
+        <v>801011</v>
       </c>
       <c r="R104" t="n">
-        <v>7496620</v>
+        <v>7496986</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11714,11 +11719,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B110" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,26 +12270,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12297,10 +12302,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R110" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12335,13 +12340,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12360,10 +12369,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B111" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12371,31 +12380,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12403,10 +12407,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R111" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12441,17 +12445,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12787,37 +12787,42 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801461</v>
+        <v>128801457</v>
       </c>
       <c r="B115" t="n">
-        <v>91560</v>
+        <v>58097</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12869,7 +12874,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12888,10 +12892,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B116" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12899,21 +12903,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12989,42 +12993,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B117" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13076,6 +13075,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13616,10 +13616,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56908</v>
+        <v>91560</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13627,31 +13627,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13659,10 +13654,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13689,17 +13684,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13708,6 +13698,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13726,10 +13717,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91560</v>
+        <v>56908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13737,26 +13728,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13764,10 +13760,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13794,12 +13790,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13808,7 +13809,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14947,7 +14947,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -15156,32 +15156,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209518</v>
+        <v>129209515</v>
       </c>
       <c r="B138" t="n">
-        <v>91538</v>
+        <v>57831</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800953</v>
+        <v>800963</v>
       </c>
       <c r="R138" t="n">
-        <v>7496877</v>
+        <v>7496841</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15246,17 +15246,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209507</v>
+        <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>91491</v>
+        <v>91538</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,21 +15264,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15288,10 +15288,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>801033</v>
+        <v>800953</v>
       </c>
       <c r="R139" t="n">
-        <v>7497194</v>
+        <v>7496877</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15343,39 +15343,39 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209515</v>
+        <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>57831</v>
+        <v>91903</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103031</v>
+        <v>2063</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15385,10 +15385,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800963</v>
+        <v>801040</v>
       </c>
       <c r="R140" t="n">
-        <v>7496841</v>
+        <v>7497196</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15440,39 +15440,39 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209519</v>
+        <v>129209507</v>
       </c>
       <c r="B141" t="n">
-        <v>91903</v>
+        <v>91491</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2063</v>
+        <v>112</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15482,10 +15482,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801040</v>
+        <v>801033</v>
       </c>
       <c r="R141" t="n">
-        <v>7497196</v>
+        <v>7497194</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15654,10 +15654,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B143" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15665,21 +15665,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15689,10 +15689,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R143" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
@@ -15841,17 +15841,17 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15859,21 +15859,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15883,10 +15883,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R145" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
@@ -16035,7 +16035,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
@@ -16229,10 +16229,977 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Robert Flygare, Åke Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>129350333</v>
+      </c>
+      <c r="B149" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>801095</v>
+      </c>
+      <c r="R149" t="n">
+        <v>7497155</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Flera avbarkade granar</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>129350288</v>
+      </c>
+      <c r="B150" t="n">
+        <v>91538</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>801000</v>
+      </c>
+      <c r="R150" t="n">
+        <v>7496979</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>129350236</v>
+      </c>
+      <c r="B151" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>801021</v>
+      </c>
+      <c r="R151" t="n">
+        <v>7496816</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>129350314</v>
+      </c>
+      <c r="B152" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>801075</v>
+      </c>
+      <c r="R152" t="n">
+        <v>7497157</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>129350294</v>
+      </c>
+      <c r="B153" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>801000</v>
+      </c>
+      <c r="R153" t="n">
+        <v>7496979</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>129350372</v>
+      </c>
+      <c r="B154" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>801123</v>
+      </c>
+      <c r="R154" t="n">
+        <v>7497204</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129350217</v>
+      </c>
+      <c r="B155" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>801018</v>
+      </c>
+      <c r="R155" t="n">
+        <v>7497132</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129350255</v>
+      </c>
+      <c r="B156" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>801047</v>
+      </c>
+      <c r="R156" t="n">
+        <v>7496833</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>129350273</v>
+      </c>
+      <c r="B157" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Isopalo, T lm</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>801000</v>
+      </c>
+      <c r="R157" t="n">
+        <v>7496979</v>
+      </c>
+      <c r="S157" t="n">
+        <v>10</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Robert Flygare</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B101" t="n">
-        <v>91560</v>
+        <v>91542</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R101" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B102" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R102" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12259,10 +12259,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128801973</v>
+        <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12270,31 +12270,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>800950</v>
+        <v>801013</v>
       </c>
       <c r="R110" t="n">
-        <v>7497251</v>
+        <v>7497115</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12340,17 +12335,13 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128801515</v>
+        <v>128801973</v>
       </c>
       <c r="B111" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12380,26 +12371,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12407,10 +12403,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>801013</v>
+        <v>800950</v>
       </c>
       <c r="R111" t="n">
-        <v>7497115</v>
+        <v>7497251</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12445,13 +12441,17 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -12787,42 +12787,37 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B115" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12874,6 +12869,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12892,37 +12888,42 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801461</v>
+        <v>128801457</v>
       </c>
       <c r="B116" t="n">
-        <v>91560</v>
+        <v>58097</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12974,7 +12975,6 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,10 +12993,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B117" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13004,21 +13004,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -15156,32 +15156,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209515</v>
+        <v>129209519</v>
       </c>
       <c r="B138" t="n">
-        <v>57831</v>
+        <v>91903</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103031</v>
+        <v>2063</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800963</v>
+        <v>801040</v>
       </c>
       <c r="R138" t="n">
-        <v>7496841</v>
+        <v>7497196</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15253,10 +15253,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209518</v>
+        <v>129214770</v>
       </c>
       <c r="B139" t="n">
-        <v>91538</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,34 +15264,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800953</v>
+        <v>800985</v>
       </c>
       <c r="R139" t="n">
-        <v>7496877</v>
+        <v>7497010</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15326,6 +15334,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15338,44 +15351,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209519</v>
+        <v>129209518</v>
       </c>
       <c r="B140" t="n">
-        <v>91903</v>
+        <v>91538</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15385,10 +15398,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801040</v>
+        <v>800953</v>
       </c>
       <c r="R140" t="n">
-        <v>7497196</v>
+        <v>7496877</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15544,27 +15557,27 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15573,24 +15586,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15625,11 +15630,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15642,12 +15642,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91912</v>
+        <v>91921</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11324,10 +11324,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128801522</v>
+        <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91542</v>
+        <v>91558</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11335,21 +11335,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11362,10 +11362,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>801027</v>
+        <v>801020</v>
       </c>
       <c r="R101" t="n">
-        <v>7497060</v>
+        <v>7496768</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11425,10 +11425,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128801553</v>
+        <v>128801522</v>
       </c>
       <c r="B102" t="n">
-        <v>91560</v>
+        <v>91540</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11436,21 +11436,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>801020</v>
+        <v>801027</v>
       </c>
       <c r="R102" t="n">
-        <v>7496768</v>
+        <v>7497060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11959,7 +11959,7 @@
         <v>128801500</v>
       </c>
       <c r="B107" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>128801461</v>
       </c>
       <c r="B117" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15156,32 +15156,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209519</v>
+        <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91903</v>
+        <v>91491</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2063</v>
+        <v>112</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15191,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801040</v>
+        <v>801033</v>
       </c>
       <c r="R138" t="n">
-        <v>7497196</v>
+        <v>7497194</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15253,10 +15253,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129214770</v>
+        <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>57727</v>
+        <v>91536</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,42 +15264,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800985</v>
+        <v>800953</v>
       </c>
       <c r="R139" t="n">
-        <v>7497010</v>
+        <v>7496877</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15334,11 +15326,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15351,44 +15338,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>91538</v>
+        <v>91912</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15398,10 +15385,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R140" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15460,10 +15447,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209507</v>
+        <v>129214770</v>
       </c>
       <c r="B141" t="n">
-        <v>91491</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15471,34 +15458,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801033</v>
+        <v>800985</v>
       </c>
       <c r="R141" t="n">
-        <v>7497194</v>
+        <v>7497010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15533,6 +15528,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15545,12 +15545,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15657,7 +15657,7 @@
         <v>129209510</v>
       </c>
       <c r="B143" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15754,7 +15754,7 @@
         <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91538</v>
+        <v>91536</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -11226,7 +11226,7 @@
         <v>128801498</v>
       </c>
       <c r="B100" t="n">
-        <v>91921</v>
+        <v>91922</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>128801553</v>
       </c>
       <c r="B101" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11344,14 +11344,10 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -11526,10 +11522,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128801754</v>
+        <v>128801536</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11537,16 +11533,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -11554,12 +11550,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>800951</v>
+        <v>801011</v>
       </c>
       <c r="R103" t="n">
-        <v>7496620</v>
+        <v>7496986</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11605,11 +11605,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11636,10 +11631,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128801536</v>
+        <v>128801754</v>
       </c>
       <c r="B104" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11647,16 +11642,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11664,16 +11659,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
@@ -11683,10 +11674,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>801011</v>
+        <v>800951</v>
       </c>
       <c r="R104" t="n">
-        <v>7496986</v>
+        <v>7496620</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11719,6 +11710,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12060,7 +12056,7 @@
         <v>128801436</v>
       </c>
       <c r="B108" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12077,14 +12073,10 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -12262,7 +12254,7 @@
         <v>128801515</v>
       </c>
       <c r="B110" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12579,7 +12571,7 @@
         <v>128801446</v>
       </c>
       <c r="B113" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12596,14 +12588,10 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -12787,10 +12775,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128801463</v>
+        <v>128801461</v>
       </c>
       <c r="B115" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12798,23 +12786,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -12888,42 +12872,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128801457</v>
+        <v>128801463</v>
       </c>
       <c r="B116" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12975,6 +12954,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -12993,37 +12973,42 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128801461</v>
+        <v>128801457</v>
       </c>
       <c r="B117" t="n">
-        <v>91558</v>
+        <v>58097</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13075,7 +13060,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13097,7 +13081,7 @@
         <v>128801558</v>
       </c>
       <c r="B118" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13114,14 +13098,10 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -13417,7 +13397,7 @@
         <v>128801492</v>
       </c>
       <c r="B121" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13518,7 +13498,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13535,14 +13515,10 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -13619,7 +13595,7 @@
         <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13636,14 +13612,10 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -13830,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14549,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B132" t="n">
-        <v>79120</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14560,26 +14532,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14587,10 +14564,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R132" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14617,12 +14594,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14631,7 +14613,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14643,17 +14624,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14661,31 +14642,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14693,10 +14669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R133" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14723,17 +14699,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14742,6 +14713,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14753,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14763,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14780,14 +14752,10 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14860,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15058,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15075,14 +15043,10 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -15156,32 +15120,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209507</v>
+        <v>129209519</v>
       </c>
       <c r="B138" t="n">
-        <v>91491</v>
+        <v>91913</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>2063</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15191,10 +15155,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801033</v>
+        <v>801040</v>
       </c>
       <c r="R138" t="n">
-        <v>7497194</v>
+        <v>7497196</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15253,10 +15217,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209518</v>
+        <v>129209507</v>
       </c>
       <c r="B139" t="n">
-        <v>91536</v>
+        <v>91491</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15264,21 +15228,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15288,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800953</v>
+        <v>801033</v>
       </c>
       <c r="R139" t="n">
-        <v>7496877</v>
+        <v>7497194</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15350,32 +15314,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209519</v>
+        <v>129209518</v>
       </c>
       <c r="B140" t="n">
-        <v>91912</v>
+        <v>91536</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15385,10 +15349,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801040</v>
+        <v>800953</v>
       </c>
       <c r="R140" t="n">
-        <v>7497196</v>
+        <v>7496877</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15447,27 +15411,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15476,24 +15440,16 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R141" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15528,11 +15484,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15545,39 +15496,39 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B142" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15586,16 +15537,24 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15630,6 +15589,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15642,22 +15606,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209510</v>
+        <v>129209517</v>
       </c>
       <c r="B143" t="n">
-        <v>91837</v>
+        <v>91536</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15665,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15689,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800990</v>
+        <v>800962</v>
       </c>
       <c r="R143" t="n">
-        <v>7497021</v>
+        <v>7496847</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15751,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209510</v>
       </c>
       <c r="B144" t="n">
-        <v>91536</v>
+        <v>91838</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15762,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15786,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>800990</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497021</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15848,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209503</v>
+        <v>129209520</v>
       </c>
       <c r="B145" t="n">
-        <v>91540</v>
+        <v>91560</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15859,23 +15823,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15883,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801025</v>
+        <v>801003</v>
       </c>
       <c r="R145" t="n">
-        <v>7497057</v>
+        <v>7497371</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15945,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209520</v>
+        <v>129209503</v>
       </c>
       <c r="B146" t="n">
-        <v>91558</v>
+        <v>91540</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15956,21 +15916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15980,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801003</v>
+        <v>801025</v>
       </c>
       <c r="R146" t="n">
-        <v>7497371</v>
+        <v>7497057</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16045,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16062,14 +16022,10 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -16142,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16159,14 +16115,10 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91560</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,22 +13603,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13626,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13656,12 +13665,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13670,7 +13684,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13689,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56908</v>
+        <v>91560</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13700,31 +13713,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13732,10 +13736,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13762,17 +13766,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13781,6 +13780,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>57727</v>
+        <v>79120</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,31 +14532,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14564,10 +14559,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R132" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14594,17 +14589,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14613,6 +14603,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14624,17 +14615,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B133" t="n">
-        <v>79120</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14642,26 +14633,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14669,10 +14665,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R133" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14699,12 +14695,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14713,7 +14714,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15120,32 +15120,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209519</v>
+        <v>129209518</v>
       </c>
       <c r="B138" t="n">
-        <v>91913</v>
+        <v>91536</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15155,10 +15155,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801040</v>
+        <v>800953</v>
       </c>
       <c r="R138" t="n">
-        <v>7497196</v>
+        <v>7496877</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15217,32 +15217,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209507</v>
+        <v>129209519</v>
       </c>
       <c r="B139" t="n">
-        <v>91491</v>
+        <v>91913</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>112</v>
+        <v>2063</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>801033</v>
+        <v>801040</v>
       </c>
       <c r="R139" t="n">
-        <v>7497194</v>
+        <v>7497196</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209518</v>
+        <v>129214770</v>
       </c>
       <c r="B140" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15325,34 +15325,42 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800953</v>
+        <v>800985</v>
       </c>
       <c r="R140" t="n">
-        <v>7496877</v>
+        <v>7497010</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15387,6 +15395,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15399,12 +15412,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15508,10 +15521,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214770</v>
+        <v>129209507</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>91491</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15519,42 +15532,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800985</v>
+        <v>801033</v>
       </c>
       <c r="R142" t="n">
-        <v>7497010</v>
+        <v>7497194</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15589,11 +15594,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15606,22 +15606,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209517</v>
+        <v>129209510</v>
       </c>
       <c r="B143" t="n">
-        <v>91536</v>
+        <v>91838</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800962</v>
+        <v>800990</v>
       </c>
       <c r="R143" t="n">
-        <v>7496847</v>
+        <v>7497021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15715,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209510</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91838</v>
+        <v>91536</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800990</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497021</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15812,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209520</v>
+        <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91560</v>
+        <v>91540</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15823,19 +15823,23 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15843,10 +15847,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801003</v>
+        <v>801025</v>
       </c>
       <c r="R145" t="n">
-        <v>7497371</v>
+        <v>7497057</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15905,10 +15909,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209503</v>
+        <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91540</v>
+        <v>91560</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,23 +15920,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801025</v>
+        <v>801003</v>
       </c>
       <c r="R146" t="n">
-        <v>7497057</v>
+        <v>7497371</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13498,7 +13498,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56908</v>
+        <v>91563</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,31 +13603,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13635,10 +13626,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13665,17 +13656,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13684,6 +13670,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13702,10 +13689,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91560</v>
+        <v>56908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13713,22 +13700,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13736,10 +13732,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,12 +13762,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13780,7 +13781,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>129088352</v>
       </c>
       <c r="B127" t="n">
-        <v>79120</v>
+        <v>79122</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>79120</v>
+        <v>79122</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>129214798</v>
       </c>
       <c r="B136" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209518</v>
+        <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91536</v>
+        <v>91494</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15131,21 +15131,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15155,10 +15155,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800953</v>
+        <v>801033</v>
       </c>
       <c r="R138" t="n">
-        <v>7496877</v>
+        <v>7497194</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15220,7 +15220,7 @@
         <v>129209519</v>
       </c>
       <c r="B139" t="n">
-        <v>91913</v>
+        <v>91916</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129214770</v>
+        <v>129209518</v>
       </c>
       <c r="B140" t="n">
-        <v>57727</v>
+        <v>91539</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15325,42 +15325,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800985</v>
+        <v>800953</v>
       </c>
       <c r="R140" t="n">
-        <v>7497010</v>
+        <v>7496877</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15395,11 +15387,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15412,12 +15399,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15521,10 +15508,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209507</v>
+        <v>129214770</v>
       </c>
       <c r="B142" t="n">
-        <v>91491</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15532,34 +15519,42 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>801033</v>
+        <v>800985</v>
       </c>
       <c r="R142" t="n">
-        <v>7497194</v>
+        <v>7497010</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15594,6 +15589,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15606,12 +15606,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15621,7 +15621,7 @@
         <v>129209510</v>
       </c>
       <c r="B143" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15715,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209503</v>
       </c>
       <c r="B144" t="n">
-        <v>91536</v>
+        <v>91543</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>801025</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497057</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15812,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B145" t="n">
-        <v>91540</v>
+        <v>91539</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15823,21 +15823,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15847,10 +15847,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R145" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15912,7 +15912,7 @@
         <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B150" t="n">
-        <v>91536</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,26 +16309,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16336,10 +16341,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R150" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16374,13 +16379,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16399,10 +16408,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B151" t="n">
-        <v>57727</v>
+        <v>91539</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16410,31 +16419,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16442,10 +16446,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R151" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16480,17 +16484,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16622,7 +16622,7 @@
         <v>129350294</v>
       </c>
       <c r="B153" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -15411,27 +15411,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B141" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15440,16 +15440,24 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R141" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15484,6 +15492,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15496,39 +15509,39 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15537,24 +15550,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15589,11 +15594,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15606,22 +15606,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B143" t="n">
-        <v>91841</v>
+        <v>91543</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R143" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15715,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91543</v>
+        <v>91539</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15812,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209517</v>
+        <v>129209520</v>
       </c>
       <c r="B145" t="n">
-        <v>91539</v>
+        <v>91563</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15823,23 +15823,19 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15847,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>800962</v>
+        <v>801003</v>
       </c>
       <c r="R145" t="n">
-        <v>7496847</v>
+        <v>7497371</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15909,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209520</v>
+        <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91563</v>
+        <v>91841</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15920,19 +15916,23 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801003</v>
+        <v>800990</v>
       </c>
       <c r="R146" t="n">
-        <v>7497371</v>
+        <v>7497021</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>91539</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,31 +16309,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16341,10 +16336,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R150" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16379,17 +16374,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16408,10 +16399,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B151" t="n">
-        <v>91539</v>
+        <v>57727</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16419,26 +16410,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16446,10 +16442,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R151" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16484,13 +16480,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13498,7 +13498,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91563</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,22 +13603,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13626,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13656,12 +13665,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13670,7 +13684,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13689,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56908</v>
+        <v>91565</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13700,31 +13713,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13732,10 +13736,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13762,17 +13766,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13781,6 +13780,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>129088352</v>
       </c>
       <c r="B127" t="n">
-        <v>79122</v>
+        <v>79123</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>79122</v>
+        <v>79123</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>129214798</v>
       </c>
       <c r="B136" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15217,32 +15217,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209519</v>
+        <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>91916</v>
+        <v>91541</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>801040</v>
+        <v>800953</v>
       </c>
       <c r="R139" t="n">
-        <v>7497196</v>
+        <v>7496877</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15314,32 +15314,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>91539</v>
+        <v>91918</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15349,10 +15349,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R140" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B143" t="n">
-        <v>91543</v>
+        <v>91541</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R143" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15715,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209510</v>
       </c>
       <c r="B144" t="n">
-        <v>91539</v>
+        <v>91843</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>800990</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497021</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15815,7 +15815,7 @@
         <v>129209520</v>
       </c>
       <c r="B145" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15905,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B146" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,21 +15916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16005,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>129350294</v>
       </c>
       <c r="B153" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13498,7 +13498,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56908</v>
+        <v>91569</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,31 +13603,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13635,10 +13626,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13665,17 +13656,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13684,6 +13670,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13702,10 +13689,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91565</v>
+        <v>56908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13713,22 +13700,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13736,10 +13732,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,12 +13762,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13780,7 +13781,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>91918</v>
+        <v>91922</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15411,27 +15411,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15440,24 +15440,16 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R141" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15492,11 +15484,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15509,39 +15496,39 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B142" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15550,16 +15537,24 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15594,6 +15589,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15606,22 +15606,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209517</v>
+        <v>129209520</v>
       </c>
       <c r="B143" t="n">
-        <v>91541</v>
+        <v>91569</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,23 +15629,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15653,10 +15649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800962</v>
+        <v>801003</v>
       </c>
       <c r="R143" t="n">
-        <v>7496847</v>
+        <v>7497371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15715,10 +15711,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209510</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91843</v>
+        <v>91545</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,21 +15722,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800990</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497021</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15812,10 +15808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209520</v>
+        <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91565</v>
+        <v>91549</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15823,19 +15819,23 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -15843,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801003</v>
+        <v>801025</v>
       </c>
       <c r="R145" t="n">
-        <v>7497371</v>
+        <v>7497057</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15905,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,21 +15916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R146" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16005,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91541</v>
+        <v>91545</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13498,7 +13498,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B132" t="n">
-        <v>79123</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,26 +14532,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14559,10 +14564,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R132" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14589,12 +14594,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14603,7 +14613,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14615,17 +14624,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>79123</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14633,31 +14642,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14665,10 +14669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R133" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14695,17 +14699,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14714,6 +14713,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>91922</v>
+        <v>91923</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15411,27 +15411,27 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B141" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15440,16 +15440,24 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R141" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15484,6 +15492,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15496,39 +15509,39 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15537,24 +15550,16 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15589,11 +15594,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15606,12 +15606,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
@@ -15621,7 +15621,7 @@
         <v>129209520</v>
       </c>
       <c r="B143" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15811,7 +15811,7 @@
         <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>57727</v>
+        <v>79123</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,31 +14532,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14564,10 +14559,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R132" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14594,17 +14589,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14613,6 +14603,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14624,17 +14615,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B133" t="n">
-        <v>79123</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14642,26 +14633,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14669,10 +14665,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R133" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14699,12 +14695,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14713,7 +14714,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209507</v>
+        <v>129209518</v>
       </c>
       <c r="B138" t="n">
-        <v>91501</v>
+        <v>91546</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15131,21 +15131,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15155,10 +15155,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801033</v>
+        <v>800953</v>
       </c>
       <c r="R138" t="n">
-        <v>7497194</v>
+        <v>7496877</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15217,32 +15217,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B139" t="n">
-        <v>91546</v>
+        <v>91923</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R139" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15314,45 +15314,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209519</v>
+        <v>129214770</v>
       </c>
       <c r="B140" t="n">
-        <v>91923</v>
+        <v>57727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801040</v>
+        <v>800985</v>
       </c>
       <c r="R140" t="n">
-        <v>7497196</v>
+        <v>7497010</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15387,6 +15395,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15399,39 +15412,39 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -15440,24 +15453,16 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R141" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15492,11 +15497,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15509,44 +15509,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129209507</v>
       </c>
       <c r="B142" t="n">
-        <v>57831</v>
+        <v>91501</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>112</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>801033</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7497194</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209520</v>
+        <v>129209517</v>
       </c>
       <c r="B143" t="n">
-        <v>91570</v>
+        <v>91546</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,19 +15629,23 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15649,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801003</v>
+        <v>800962</v>
       </c>
       <c r="R143" t="n">
-        <v>7497371</v>
+        <v>7496847</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15711,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209510</v>
       </c>
       <c r="B144" t="n">
-        <v>91546</v>
+        <v>91848</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15722,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15746,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>800990</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497021</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15905,10 +15909,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91848</v>
+        <v>91570</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,23 +15920,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801003</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497371</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B150" t="n">
-        <v>91546</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,26 +16309,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16336,10 +16341,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R150" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16374,13 +16379,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16399,10 +16408,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B151" t="n">
-        <v>57727</v>
+        <v>91546</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16410,31 +16419,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16442,10 +16446,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R151" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16480,17 +16484,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91570</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,22 +13603,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13626,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13656,12 +13665,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13670,7 +13684,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13689,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56908</v>
+        <v>91570</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13700,31 +13713,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13732,10 +13736,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13762,17 +13766,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13781,6 +13780,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209517</v>
+        <v>129209520</v>
       </c>
       <c r="B143" t="n">
-        <v>91546</v>
+        <v>91570</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,23 +15629,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15653,10 +15649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800962</v>
+        <v>801003</v>
       </c>
       <c r="R143" t="n">
-        <v>7496847</v>
+        <v>7497371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15715,10 +15711,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209510</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91848</v>
+        <v>91546</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,21 +15722,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15750,10 +15746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800990</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497021</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15812,10 +15808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B145" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15823,21 +15819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15847,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R145" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15909,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209520</v>
+        <v>129209503</v>
       </c>
       <c r="B146" t="n">
-        <v>91570</v>
+        <v>91550</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15920,19 +15916,23 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801003</v>
+        <v>801025</v>
       </c>
       <c r="R146" t="n">
-        <v>7497371</v>
+        <v>7497057</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13498,7 +13498,7 @@
         <v>129088394</v>
       </c>
       <c r="B122" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56908</v>
+        <v>91573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,31 +13603,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13635,10 +13626,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13665,17 +13656,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13684,6 +13670,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13702,10 +13689,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91570</v>
+        <v>56908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13713,22 +13700,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13736,10 +13732,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,12 +13762,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13780,7 +13781,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>129088398</v>
       </c>
       <c r="B125" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>129088389</v>
       </c>
       <c r="B126" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>129088385</v>
       </c>
       <c r="B129" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209518</v>
+        <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>91546</v>
+        <v>91504</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15131,21 +15131,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15155,10 +15155,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800953</v>
+        <v>801033</v>
       </c>
       <c r="R138" t="n">
-        <v>7496877</v>
+        <v>7497194</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15217,45 +15217,53 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209519</v>
+        <v>129214770</v>
       </c>
       <c r="B139" t="n">
-        <v>91923</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>801040</v>
+        <v>800985</v>
       </c>
       <c r="R139" t="n">
-        <v>7497196</v>
+        <v>7497010</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15290,6 +15298,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15302,39 +15315,39 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B140" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15343,24 +15356,16 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R140" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15395,11 +15400,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15412,44 +15412,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209515</v>
+        <v>129209518</v>
       </c>
       <c r="B141" t="n">
-        <v>57831</v>
+        <v>91549</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800963</v>
+        <v>800953</v>
       </c>
       <c r="R141" t="n">
-        <v>7496841</v>
+        <v>7496877</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15521,32 +15521,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209507</v>
+        <v>129209519</v>
       </c>
       <c r="B142" t="n">
-        <v>91501</v>
+        <v>91926</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>112</v>
+        <v>2063</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>801033</v>
+        <v>801040</v>
       </c>
       <c r="R142" t="n">
-        <v>7497194</v>
+        <v>7497196</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15621,7 +15621,7 @@
         <v>129209520</v>
       </c>
       <c r="B143" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15808,10 +15808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15819,21 +15819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15843,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R145" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15905,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,21 +15916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R146" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16005,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>129350288</v>
       </c>
       <c r="B151" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91573</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,22 +13603,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13626,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13656,12 +13665,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13670,7 +13684,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13689,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56908</v>
+        <v>91573</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13700,31 +13713,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13732,10 +13736,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13762,17 +13766,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13781,6 +13780,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B132" t="n">
-        <v>79123</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,26 +14532,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14559,10 +14564,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R132" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14589,12 +14594,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14603,7 +14613,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14615,17 +14624,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>79123</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14633,31 +14642,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14665,10 +14669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R133" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14695,17 +14699,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14714,6 +14713,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129214770</v>
+        <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15228,42 +15228,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800985</v>
+        <v>800953</v>
       </c>
       <c r="R139" t="n">
-        <v>7497010</v>
+        <v>7496877</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15298,11 +15290,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15315,39 +15302,39 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B140" t="n">
-        <v>57831</v>
+        <v>57727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -15356,16 +15343,24 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R140" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15400,6 +15395,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15412,44 +15412,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B141" t="n">
-        <v>91549</v>
+        <v>91926</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R141" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15521,32 +15521,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209519</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>91926</v>
+        <v>57831</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2063</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>801040</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7497196</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209520</v>
+        <v>129209510</v>
       </c>
       <c r="B143" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,19 +15629,23 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15649,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801003</v>
+        <v>800990</v>
       </c>
       <c r="R143" t="n">
-        <v>7497371</v>
+        <v>7497021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15711,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209520</v>
       </c>
       <c r="B144" t="n">
-        <v>91549</v>
+        <v>91573</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15722,23 +15726,19 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -15746,10 +15746,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>801003</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497371</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15808,10 +15808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B145" t="n">
-        <v>91553</v>
+        <v>91549</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15819,21 +15819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15843,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R145" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15905,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B146" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,21 +15916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,31 +16309,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16341,10 +16336,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R150" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16379,17 +16374,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16408,10 +16399,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B151" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16419,26 +16410,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16446,10 +16442,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R151" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16484,13 +16480,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B123" t="n">
-        <v>56908</v>
+        <v>91573</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,31 +13603,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13635,10 +13626,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R123" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13665,17 +13656,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13684,6 +13670,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13702,10 +13689,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B124" t="n">
-        <v>91573</v>
+        <v>56908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13713,22 +13700,31 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13736,10 +13732,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R124" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13766,12 +13762,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13780,7 +13781,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>57727</v>
+        <v>79123</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,31 +14532,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14564,10 +14559,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R132" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14594,17 +14589,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14613,6 +14603,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14624,17 +14615,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B133" t="n">
-        <v>79123</v>
+        <v>57727</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14642,26 +14633,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14669,10 +14665,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R133" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14699,12 +14695,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14713,7 +14714,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209518</v>
+        <v>129214770</v>
       </c>
       <c r="B139" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15228,34 +15228,42 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800953</v>
+        <v>800985</v>
       </c>
       <c r="R139" t="n">
-        <v>7496877</v>
+        <v>7497010</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15290,6 +15298,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15302,65 +15315,57 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129214770</v>
+        <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>57727</v>
+        <v>91926</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800985</v>
+        <v>801040</v>
       </c>
       <c r="R140" t="n">
-        <v>7497010</v>
+        <v>7497196</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15395,11 +15400,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15412,44 +15412,44 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209519</v>
+        <v>129209515</v>
       </c>
       <c r="B141" t="n">
-        <v>91926</v>
+        <v>57831</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2063</v>
+        <v>103031</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801040</v>
+        <v>800963</v>
       </c>
       <c r="R141" t="n">
-        <v>7497196</v>
+        <v>7496841</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15521,32 +15521,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129209518</v>
       </c>
       <c r="B142" t="n">
-        <v>57831</v>
+        <v>91549</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>800953</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7496877</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209510</v>
+        <v>129209503</v>
       </c>
       <c r="B143" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800990</v>
+        <v>801025</v>
       </c>
       <c r="R143" t="n">
-        <v>7497021</v>
+        <v>7497057</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15905,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,21 +15916,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R146" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B150" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,26 +16309,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16336,10 +16341,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R150" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16374,13 +16379,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16399,10 +16408,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B151" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16410,31 +16419,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16442,10 +16446,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R151" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16480,17 +16484,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -15120,10 +15120,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209507</v>
+        <v>129214770</v>
       </c>
       <c r="B138" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15131,34 +15131,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801033</v>
+        <v>800985</v>
       </c>
       <c r="R138" t="n">
-        <v>7497194</v>
+        <v>7497010</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15193,6 +15201,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15205,39 +15218,39 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129214770</v>
+        <v>129209515</v>
       </c>
       <c r="B139" t="n">
-        <v>57727</v>
+        <v>57831</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -15246,24 +15259,16 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800985</v>
+        <v>800963</v>
       </c>
       <c r="R139" t="n">
-        <v>7497010</v>
+        <v>7496841</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15298,11 +15303,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
@@ -15315,44 +15315,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209519</v>
+        <v>129209518</v>
       </c>
       <c r="B140" t="n">
-        <v>91926</v>
+        <v>91549</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2063</v>
+        <v>1108</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15362,10 +15362,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801040</v>
+        <v>800953</v>
       </c>
       <c r="R140" t="n">
-        <v>7497196</v>
+        <v>7496877</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15424,32 +15424,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209515</v>
+        <v>129209507</v>
       </c>
       <c r="B141" t="n">
-        <v>57831</v>
+        <v>91504</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103031</v>
+        <v>112</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15459,10 +15459,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800963</v>
+        <v>801033</v>
       </c>
       <c r="R141" t="n">
-        <v>7496841</v>
+        <v>7497194</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15521,32 +15521,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B142" t="n">
-        <v>91549</v>
+        <v>91926</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R142" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209503</v>
+        <v>129209517</v>
       </c>
       <c r="B143" t="n">
-        <v>91553</v>
+        <v>91549</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801025</v>
+        <v>800962</v>
       </c>
       <c r="R143" t="n">
-        <v>7497057</v>
+        <v>7496847</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15808,10 +15808,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209517</v>
+        <v>129209503</v>
       </c>
       <c r="B145" t="n">
-        <v>91549</v>
+        <v>91553</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15819,21 +15819,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15843,10 +15843,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>800962</v>
+        <v>801025</v>
       </c>
       <c r="R145" t="n">
-        <v>7496847</v>
+        <v>7497057</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,31 +16309,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16341,10 +16336,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R150" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16379,17 +16374,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16408,10 +16399,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B151" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16419,26 +16410,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16446,10 +16442,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R151" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16484,13 +16480,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -13592,10 +13592,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129088381</v>
+        <v>129086580</v>
       </c>
       <c r="B123" t="n">
-        <v>91573</v>
+        <v>56908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13603,22 +13603,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13626,10 +13635,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>801196</v>
+        <v>800972</v>
       </c>
       <c r="R123" t="n">
-        <v>7497188</v>
+        <v>7497324</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13656,12 +13665,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Äggskal i en liten grop invid en björkstam.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13670,7 +13684,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13689,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129086580</v>
+        <v>129088381</v>
       </c>
       <c r="B124" t="n">
-        <v>56908</v>
+        <v>91573</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13700,31 +13713,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -13732,10 +13736,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>800972</v>
+        <v>801196</v>
       </c>
       <c r="R124" t="n">
-        <v>7497324</v>
+        <v>7497188</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13762,17 +13766,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äggskal i en liten grop invid en björkstam.</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13781,6 +13780,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -15120,10 +15120,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214770</v>
+        <v>129209507</v>
       </c>
       <c r="B138" t="n">
-        <v>57727</v>
+        <v>91504</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15131,42 +15131,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>800985</v>
+        <v>801033</v>
       </c>
       <c r="R138" t="n">
-        <v>7497010</v>
+        <v>7497194</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15201,11 +15193,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
@@ -15218,44 +15205,44 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209515</v>
+        <v>129209518</v>
       </c>
       <c r="B139" t="n">
-        <v>57831</v>
+        <v>91549</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15265,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800963</v>
+        <v>800953</v>
       </c>
       <c r="R139" t="n">
-        <v>7496841</v>
+        <v>7496877</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15327,32 +15314,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209518</v>
+        <v>129209519</v>
       </c>
       <c r="B140" t="n">
-        <v>91549</v>
+        <v>91926</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1108</v>
+        <v>2063</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15362,10 +15349,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800953</v>
+        <v>801040</v>
       </c>
       <c r="R140" t="n">
-        <v>7496877</v>
+        <v>7497196</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15424,10 +15411,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129209507</v>
+        <v>129214770</v>
       </c>
       <c r="B141" t="n">
-        <v>91504</v>
+        <v>57727</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15435,34 +15422,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>801033</v>
+        <v>800985</v>
       </c>
       <c r="R141" t="n">
-        <v>7497194</v>
+        <v>7497010</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15497,6 +15492,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15509,44 +15509,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209519</v>
+        <v>129209515</v>
       </c>
       <c r="B142" t="n">
-        <v>91926</v>
+        <v>57831</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2063</v>
+        <v>103031</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15556,10 +15556,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>801040</v>
+        <v>800963</v>
       </c>
       <c r="R142" t="n">
-        <v>7497196</v>
+        <v>7496841</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209517</v>
+        <v>129209510</v>
       </c>
       <c r="B143" t="n">
-        <v>91549</v>
+        <v>91851</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,21 +15629,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15653,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800962</v>
+        <v>800990</v>
       </c>
       <c r="R143" t="n">
-        <v>7496847</v>
+        <v>7497021</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15715,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209520</v>
+        <v>129209517</v>
       </c>
       <c r="B144" t="n">
-        <v>91573</v>
+        <v>91549</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15726,19 +15726,23 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -15746,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>801003</v>
+        <v>800962</v>
       </c>
       <c r="R144" t="n">
-        <v>7497371</v>
+        <v>7496847</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15905,10 +15909,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,23 +15920,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801003</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497371</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B132" t="n">
-        <v>79123</v>
+        <v>57727</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,26 +14532,31 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14559,10 +14564,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R132" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14589,12 +14594,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14603,7 +14613,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14615,17 +14624,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B133" t="n">
-        <v>57727</v>
+        <v>79123</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14633,31 +14642,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14665,10 +14669,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R133" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14695,17 +14699,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14714,6 +14713,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -15120,10 +15120,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129209507</v>
+        <v>129209518</v>
       </c>
       <c r="B138" t="n">
-        <v>91504</v>
+        <v>91549</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15131,21 +15131,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15155,10 +15155,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>801033</v>
+        <v>800953</v>
       </c>
       <c r="R138" t="n">
-        <v>7497194</v>
+        <v>7496877</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15217,10 +15217,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209518</v>
+        <v>129209507</v>
       </c>
       <c r="B139" t="n">
-        <v>91549</v>
+        <v>91504</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15228,21 +15228,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1108</v>
+        <v>112</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>800953</v>
+        <v>801033</v>
       </c>
       <c r="R139" t="n">
-        <v>7496877</v>
+        <v>7497194</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15314,45 +15314,53 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129209519</v>
+        <v>129214770</v>
       </c>
       <c r="B140" t="n">
-        <v>91926</v>
+        <v>57727</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2063</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>801040</v>
+        <v>800985</v>
       </c>
       <c r="R140" t="n">
-        <v>7497196</v>
+        <v>7497010</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15387,6 +15395,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15399,65 +15412,57 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129214770</v>
+        <v>129209519</v>
       </c>
       <c r="B141" t="n">
-        <v>57727</v>
+        <v>91926</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>2063</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>800985</v>
+        <v>801040</v>
       </c>
       <c r="R141" t="n">
-        <v>7497010</v>
+        <v>7497196</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15492,11 +15497,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
@@ -15509,12 +15509,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -15618,10 +15618,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209510</v>
+        <v>129209520</v>
       </c>
       <c r="B143" t="n">
-        <v>91851</v>
+        <v>91573</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,23 +15629,19 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15653,10 +15649,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>800990</v>
+        <v>801003</v>
       </c>
       <c r="R143" t="n">
-        <v>7497021</v>
+        <v>7497371</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15909,10 +15905,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209520</v>
+        <v>129209510</v>
       </c>
       <c r="B146" t="n">
-        <v>91573</v>
+        <v>91851</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15920,19 +15916,23 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr"/>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>801003</v>
+        <v>800990</v>
       </c>
       <c r="R146" t="n">
-        <v>7497371</v>
+        <v>7497021</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B150" t="n">
-        <v>91549</v>
+        <v>57727</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,26 +16309,31 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16336,10 +16341,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R150" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16374,13 +16379,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16399,10 +16408,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B151" t="n">
-        <v>57727</v>
+        <v>91549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16410,31 +16419,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16442,10 +16446,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R151" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16480,17 +16484,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -14427,7 +14427,7 @@
         <v>129209501</v>
       </c>
       <c r="B131" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14521,10 +14521,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129214669</v>
+        <v>129214796</v>
       </c>
       <c r="B132" t="n">
-        <v>57727</v>
+        <v>79149</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14532,31 +14532,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14564,10 +14559,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>801036</v>
+        <v>800972</v>
       </c>
       <c r="R132" t="n">
-        <v>7497093</v>
+        <v>7496802</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14594,17 +14589,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Två nya bohål på lite olika höjd i samma gran.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14613,6 +14603,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14624,17 +14615,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129214796</v>
+        <v>129214669</v>
       </c>
       <c r="B133" t="n">
-        <v>79123</v>
+        <v>57730</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14642,26 +14633,31 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14669,10 +14665,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>800972</v>
+        <v>801036</v>
       </c>
       <c r="R133" t="n">
-        <v>7496802</v>
+        <v>7497093</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14699,12 +14695,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Två nya bohål på lite olika höjd i samma gran.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14713,7 +14714,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -14735,7 +14735,7 @@
         <v>129209525</v>
       </c>
       <c r="B134" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>129209511</v>
       </c>
       <c r="B135" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>129214798</v>
       </c>
       <c r="B136" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>129214791</v>
       </c>
       <c r="B137" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>129209518</v>
       </c>
       <c r="B138" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15217,32 +15217,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129209507</v>
+        <v>129209515</v>
       </c>
       <c r="B139" t="n">
-        <v>91504</v>
+        <v>57834</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>112</v>
+        <v>103031</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>801033</v>
+        <v>800963</v>
       </c>
       <c r="R139" t="n">
-        <v>7497194</v>
+        <v>7496841</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129214770</v>
+        <v>129209507</v>
       </c>
       <c r="B140" t="n">
-        <v>57727</v>
+        <v>91532</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15325,42 +15325,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Isopalo, T lm</t>
+          <t>Iso palo, T lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>800985</v>
+        <v>801033</v>
       </c>
       <c r="R140" t="n">
-        <v>7497010</v>
+        <v>7497194</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15395,11 +15387,6 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
@@ -15412,12 +15399,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Robert Flygare, per-erik mukka</t>
+          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
@@ -15427,7 +15414,7 @@
         <v>129209519</v>
       </c>
       <c r="B141" t="n">
-        <v>91926</v>
+        <v>91954</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15521,27 +15508,27 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129209515</v>
+        <v>129214770</v>
       </c>
       <c r="B142" t="n">
-        <v>57831</v>
+        <v>57730</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -15550,16 +15537,24 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Iso palo, T lm</t>
+          <t>Isopalo, T lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>800963</v>
+        <v>800985</v>
       </c>
       <c r="R142" t="n">
-        <v>7496841</v>
+        <v>7497010</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15594,6 +15589,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
@@ -15606,22 +15606,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>per-erik mukka, Robert Flygare, Åke Flygare</t>
+          <t>Robert Flygare, per-erik mukka</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129209520</v>
+        <v>129209517</v>
       </c>
       <c r="B143" t="n">
-        <v>91573</v>
+        <v>91577</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15629,19 +15629,23 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
@@ -15649,10 +15653,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>801003</v>
+        <v>800962</v>
       </c>
       <c r="R143" t="n">
-        <v>7497371</v>
+        <v>7496847</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15711,10 +15715,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129209517</v>
+        <v>129209503</v>
       </c>
       <c r="B144" t="n">
-        <v>91549</v>
+        <v>91581</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15722,21 +15726,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15746,10 +15750,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>800962</v>
+        <v>801025</v>
       </c>
       <c r="R144" t="n">
-        <v>7496847</v>
+        <v>7497057</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15808,10 +15812,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129209503</v>
+        <v>129209510</v>
       </c>
       <c r="B145" t="n">
-        <v>91553</v>
+        <v>91879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15819,21 +15823,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15843,10 +15847,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>801025</v>
+        <v>800990</v>
       </c>
       <c r="R145" t="n">
-        <v>7497057</v>
+        <v>7497021</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15905,10 +15909,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129209510</v>
+        <v>129209520</v>
       </c>
       <c r="B146" t="n">
-        <v>91851</v>
+        <v>91601</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15916,23 +15920,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
@@ -15940,10 +15940,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>800990</v>
+        <v>801003</v>
       </c>
       <c r="R146" t="n">
-        <v>7497021</v>
+        <v>7497371</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16005,7 +16005,7 @@
         <v>129209527</v>
       </c>
       <c r="B147" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>129209526</v>
       </c>
       <c r="B148" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>129350333</v>
       </c>
       <c r="B149" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16298,10 +16298,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129350236</v>
+        <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>57727</v>
+        <v>91577</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16309,31 +16309,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16341,10 +16336,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>801021</v>
+        <v>801000</v>
       </c>
       <c r="R150" t="n">
-        <v>7496816</v>
+        <v>7496979</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16379,17 +16374,13 @@
           <t>2025-10-25</t>
         </is>
       </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Avbarkad gran.</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16408,10 +16399,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129350288</v>
+        <v>129350236</v>
       </c>
       <c r="B151" t="n">
-        <v>91549</v>
+        <v>57730</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16419,26 +16410,31 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16446,10 +16442,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>801000</v>
+        <v>801021</v>
       </c>
       <c r="R151" t="n">
-        <v>7496979</v>
+        <v>7496816</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16484,13 +16480,17 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Avbarkad gran.</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>129350314</v>
       </c>
       <c r="B152" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>129350294</v>
       </c>
       <c r="B153" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>129350372</v>
       </c>
       <c r="B154" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>129350217</v>
       </c>
       <c r="B155" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>129350255</v>
       </c>
       <c r="B156" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>129350273</v>
       </c>
       <c r="B157" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -16191,7 +16191,7 @@
         <v>129350333</v>
       </c>
       <c r="B149" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>129350236</v>
       </c>
       <c r="B151" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>129350314</v>
       </c>
       <c r="B152" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>129350294</v>
       </c>
       <c r="B153" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>129350372</v>
       </c>
       <c r="B154" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>129350217</v>
       </c>
       <c r="B155" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>129350255</v>
       </c>
       <c r="B156" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>129350273</v>
       </c>
       <c r="B157" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -16191,7 +16191,7 @@
         <v>129350333</v>
       </c>
       <c r="B149" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>129350236</v>
       </c>
       <c r="B151" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>129350314</v>
       </c>
       <c r="B152" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>129350294</v>
       </c>
       <c r="B153" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>129350372</v>
       </c>
       <c r="B154" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>129350217</v>
       </c>
       <c r="B155" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>129350255</v>
       </c>
       <c r="B156" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>129350273</v>
       </c>
       <c r="B157" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>

--- a/artfynd/A 42495-2024 artfynd.xlsx
+++ b/artfynd/A 42495-2024 artfynd.xlsx
@@ -16301,7 +16301,7 @@
         <v>129350288</v>
       </c>
       <c r="B150" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>129350294</v>
       </c>
       <c r="B153" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
